--- a/docs/data/jp/xlsx/4519.xlsx
+++ b/docs/data/jp/xlsx/4519.xlsx
@@ -5616,7 +5616,7 @@
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>매출수익</t>
         </is>
       </c>
       <c r="C78" s="12" t="n">
@@ -5674,7 +5674,7 @@
     <row r="79">
       <c r="A79" s="20" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>제품·상품 매출액</t>
         </is>
       </c>
       <c r="C79" s="22" t="n">
@@ -5732,7 +5732,7 @@
     <row r="80">
       <c r="A80" s="20" t="inlineStr">
         <is>
-          <t>Royalties And Other Operating Income</t>
+          <t>로열티 등 수입 및 기타 영업수입</t>
         </is>
       </c>
       <c r="T80" s="22" t="n">
@@ -5758,7 +5758,7 @@
     <row r="82">
       <c r="A82" s="20" t="inlineStr">
         <is>
-          <t>Other Revenues Revenue</t>
+          <t>기타 매출수익</t>
         </is>
       </c>
       <c r="C82" s="22" t="n">
@@ -5929,7 +5929,7 @@
     <row r="85">
       <c r="A85" s="20" t="inlineStr">
         <is>
-          <t>Selling Expenses</t>
+          <t>판매비</t>
         </is>
       </c>
       <c r="T85" s="22" t="n">
@@ -6000,7 +6000,7 @@
     <row r="87">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>General And Administrative Expenses</t>
+          <t>일반관리비 등</t>
         </is>
       </c>
       <c r="T87" s="22" t="n">
@@ -6068,7 +6068,7 @@
     <row r="89">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>Other Operating Income Expense</t>
+          <t>기타영업수익(비용)</t>
         </is>
       </c>
       <c r="C89" s="22" t="n">
@@ -6181,7 +6181,7 @@
     <row r="91">
       <c r="A91" s="20" t="inlineStr">
         <is>
-          <t>Finance Costs</t>
+          <t>금융비용</t>
         </is>
       </c>
       <c r="C91" s="22" t="n">
@@ -6239,7 +6239,7 @@
     <row r="92">
       <c r="A92" s="20" t="inlineStr">
         <is>
-          <t>Other Financial Income Expense</t>
+          <t>기타금융수익(비용)</t>
         </is>
       </c>
       <c r="C92" s="22" t="n">
@@ -6297,7 +6297,7 @@
     <row r="93">
       <c r="A93" s="20" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>기타비용</t>
         </is>
       </c>
       <c r="C93" s="22" t="n">
@@ -6319,7 +6319,7 @@
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>Profit Loss Before Tax</t>
+          <t>법인세비용차감전 중간이익</t>
         </is>
       </c>
       <c r="C94" s="12" t="n">
@@ -6377,7 +6377,7 @@
     <row r="95">
       <c r="A95" s="20" t="inlineStr">
         <is>
-          <t>Income Tax Expense</t>
+          <t>법인소득세</t>
         </is>
       </c>
       <c r="C95" s="22" t="n">
@@ -6435,7 +6435,7 @@
     <row r="96">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>Profit Loss</t>
+          <t>중간이익</t>
         </is>
       </c>
       <c r="C96" s="12" t="n">
@@ -6493,7 +6493,7 @@
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>Profit Loss Attributable To Owners Of Parent</t>
+          <t>지배기업 소유주 지분</t>
         </is>
       </c>
       <c r="C97" s="12" t="n">
@@ -6551,7 +6551,7 @@
     <row r="98">
       <c r="A98" s="20" t="inlineStr">
         <is>
-          <t>Basic Earnings Loss Per Share</t>
+          <t>기본 주당 중간이익(엔)</t>
         </is>
       </c>
       <c r="C98" s="22" t="n">
@@ -6609,7 +6609,7 @@
     <row r="99">
       <c r="A99" s="20" t="inlineStr">
         <is>
-          <t>Diluted Earnings Loss Per Share</t>
+          <t>희석 주당 중간이익(엔)</t>
         </is>
       </c>
       <c r="C99" s="22" t="n">
@@ -6853,7 +6853,7 @@
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>Profit Loss</t>
+          <t>중간이익</t>
         </is>
       </c>
       <c r="C103" s="12" t="n">
@@ -6911,7 +6911,7 @@
     <row r="104">
       <c r="A104" s="20" t="inlineStr">
         <is>
-          <t>Remeasurements Of Defined Benefit Plans Net Of Tax Items That Will Not Be Reclassified To Profit Or Loss OCI</t>
+          <t>확정급여제도 재측정</t>
         </is>
       </c>
       <c r="C104" s="22" t="n">
@@ -6963,7 +6963,7 @@
     <row r="105">
       <c r="A105" s="20" t="inlineStr">
         <is>
-          <t>Net Change In Fair Value Of Equity Instruments Designated As Measured At Fair Value Through Other Comprehensive Income Net Of Tax Items That Will Not Be Reclassified To Profit Or Loss OCI</t>
+          <t>기타포괄손익-공정가치 측정 금융자산</t>
         </is>
       </c>
       <c r="C105" s="22" t="n">
@@ -7021,7 +7021,7 @@
     <row r="106">
       <c r="A106" s="20" t="inlineStr">
         <is>
-          <t>Total Of Items That Will Not Be Reclassified To Profit Or Loss OCI</t>
+          <t>당기손익으로 재분류되지 않는 항목 합계</t>
         </is>
       </c>
       <c r="C106" s="22" t="n">
@@ -7079,7 +7079,7 @@
     <row r="107">
       <c r="A107" s="20" t="inlineStr">
         <is>
-          <t>Financial Assets Measured At Fair Value Through Other Comprehensive Income Net Of Tax Items That May Be Reclassified To Profit Or Loss OCI</t>
+          <t>기타포괄손익-공정가치 측정 금융자산</t>
         </is>
       </c>
       <c r="C107" s="22" t="n">
@@ -7137,7 +7137,7 @@
     <row r="108">
       <c r="A108" s="20" t="inlineStr">
         <is>
-          <t>Effective Portion Of Cash Flow Hedges Net Of Tax Items That May Be Reclassified To Profit Or Loss OCI</t>
+          <t>현금흐름 위험회피</t>
         </is>
       </c>
       <c r="C108" s="22" t="n">
@@ -7195,7 +7195,7 @@
     <row r="109">
       <c r="A109" s="20" t="inlineStr">
         <is>
-          <t>Exchange Differences On Translation Of Foreign Operations Net Of Tax Items That May Be Reclassified To Profit Or Loss OCI</t>
+          <t>해외 종속기업 등 외화환산차이</t>
         </is>
       </c>
       <c r="C109" s="22" t="n">
@@ -7253,7 +7253,7 @@
     <row r="110">
       <c r="A110" s="20" t="inlineStr">
         <is>
-          <t>Total Of Items That May Be Reclassified To Profit Or Loss OCI</t>
+          <t>후에 당기손익으로 재분류될 수 있는 항목 합계</t>
         </is>
       </c>
       <c r="C110" s="22" t="n">
@@ -7427,7 +7427,7 @@
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>Comprehensive Income Attributable To Owners Of Parent</t>
+          <t>지배기업 소유주 지분</t>
         </is>
       </c>
       <c r="C113" s="12" t="n">
@@ -7671,7 +7671,7 @@
     <row r="117">
       <c r="A117" s="20" t="inlineStr">
         <is>
-          <t>Cash Generated From Operations Ope CF</t>
+          <t>영업활동 현금창출</t>
         </is>
       </c>
       <c r="C117" s="22" t="n">
@@ -7738,7 +7738,7 @@
     <row r="118">
       <c r="A118" s="20" t="inlineStr">
         <is>
-          <t>Increase Decrease In Working Capital Ope CF</t>
+          <t>운전자본 감소</t>
         </is>
       </c>
       <c r="C118" s="22" t="n">
@@ -7805,7 +7805,7 @@
     <row r="119">
       <c r="A119" s="20" t="inlineStr">
         <is>
-          <t>Payments Made For Defined Benefit Plans Ope CF</t>
+          <t>확정급여제도 출연</t>
         </is>
       </c>
       <c r="C119" s="22" t="n">
@@ -7872,7 +7872,7 @@
     <row r="120">
       <c r="A120" s="20" t="inlineStr">
         <is>
-          <t>Utilization Of Provisions Ope CF</t>
+          <t>충당금 지급</t>
         </is>
       </c>
       <c r="C120" s="22" t="n">
@@ -7939,7 +7939,7 @@
     <row r="121">
       <c r="A121" s="20" t="inlineStr">
         <is>
-          <t>Other Changes In Working Capital Ope CF</t>
+          <t>기타영업활동</t>
         </is>
       </c>
       <c r="C121" s="22" t="n">
@@ -8073,7 +8073,7 @@
     <row r="123">
       <c r="A123" s="20" t="inlineStr">
         <is>
-          <t>Income Taxes Paid Ope CF</t>
+          <t>법인소득세 지급</t>
         </is>
       </c>
       <c r="C123" s="22" t="n">
@@ -8207,7 +8207,7 @@
     <row r="125">
       <c r="A125" s="20" t="inlineStr">
         <is>
-          <t>Purchase Of Property Plant And Equipment Inv CF</t>
+          <t>유형자산 취득</t>
         </is>
       </c>
       <c r="C125" s="22" t="n">
@@ -8274,7 +8274,7 @@
     <row r="126">
       <c r="A126" s="20" t="inlineStr">
         <is>
-          <t>Purchase Of Intangible Assets Inv CF</t>
+          <t>무형자산 취득</t>
         </is>
       </c>
       <c r="C126" s="22" t="n">
@@ -8341,7 +8341,7 @@
     <row r="127">
       <c r="A127" s="20" t="inlineStr">
         <is>
-          <t>Proceeds From Sale Of Property Plant And Equipment Inv CF</t>
+          <t>유형자산 처분</t>
         </is>
       </c>
       <c r="C127" s="22" t="n">
@@ -8408,7 +8408,7 @@
     <row r="128">
       <c r="A128" s="20" t="inlineStr">
         <is>
-          <t>Proceeds From Sale Of Intangible Assets Inv CF</t>
+          <t>무형자산 처분</t>
         </is>
       </c>
       <c r="C128" s="22" t="n">
@@ -8463,7 +8463,7 @@
     <row r="129">
       <c r="A129" s="20" t="inlineStr">
         <is>
-          <t>Interest And Dividends Received Inv CF</t>
+          <t>이자 및 배당금 수취</t>
         </is>
       </c>
       <c r="C129" s="22" t="n">
@@ -8530,7 +8530,7 @@
     <row r="130">
       <c r="A130" s="20" t="inlineStr">
         <is>
-          <t>Purchase Of Marketable Securities Inv CF</t>
+          <t>유가증권 취득</t>
         </is>
       </c>
       <c r="C130" s="22" t="n">
@@ -8597,7 +8597,7 @@
     <row r="131">
       <c r="A131" s="20" t="inlineStr">
         <is>
-          <t>Proceeds From Sale Of Marketable Securities Inv CF</t>
+          <t>유가증권 처분</t>
         </is>
       </c>
       <c r="C131" s="22" t="n">
@@ -8664,7 +8664,7 @@
     <row r="132">
       <c r="A132" s="20" t="inlineStr">
         <is>
-          <t>Purchase Of Investment Securities Inv CF</t>
+          <t>투자유가증권 취득</t>
         </is>
       </c>
       <c r="C132" s="22" t="n">
@@ -8731,7 +8731,7 @@
     <row r="133">
       <c r="A133" s="20" t="inlineStr">
         <is>
-          <t>Proceeds From Sale Of Investment Securities Inv CF</t>
+          <t>투자유가증권 처분</t>
         </is>
       </c>
       <c r="C133" s="22" t="n">
@@ -8795,7 +8795,7 @@
     <row r="134">
       <c r="A134" s="20" t="inlineStr">
         <is>
-          <t>Other Inv CF</t>
+          <t>기타투자활동</t>
         </is>
       </c>
       <c r="I134" s="22" t="n">
@@ -8884,7 +8884,7 @@
     <row r="136">
       <c r="A136" s="20" t="inlineStr">
         <is>
-          <t>Purchase Of Non Controlling Interests Fin CF</t>
+          <t>비지배지분 취득</t>
         </is>
       </c>
       <c r="Q136" s="22" t="n">
@@ -8900,7 +8900,7 @@
     <row r="137">
       <c r="A137" s="20" t="inlineStr">
         <is>
-          <t>Interest Paid Fin CF</t>
+          <t>이자 지급</t>
         </is>
       </c>
       <c r="C137" s="22" t="n">
@@ -8967,7 +8967,7 @@
     <row r="138">
       <c r="A138" s="20" t="inlineStr">
         <is>
-          <t>Lease Liabilities Paid Fin CF</t>
+          <t>리스부채 지급</t>
         </is>
       </c>
       <c r="C138" s="22" t="n">
@@ -9034,7 +9034,7 @@
     <row r="139">
       <c r="A139" s="20" t="inlineStr">
         <is>
-          <t>Dividends Paid To Owners Of Parent Fin CF</t>
+          <t>배당금 지급 - 지배기업 지분</t>
         </is>
       </c>
       <c r="C139" s="22" t="n">
@@ -9101,7 +9101,7 @@
     <row r="140">
       <c r="A140" s="20" t="inlineStr">
         <is>
-          <t>Dividends Paid To Non Controlling Interests Fin CF</t>
+          <t>배당금 지급 - 비지배지분</t>
         </is>
       </c>
       <c r="Q140" s="22" t="n">
@@ -9114,7 +9114,7 @@
     <row r="141">
       <c r="A141" s="20" t="inlineStr">
         <is>
-          <t>Proceeds From Exercise Of Employee Share Options Fin CF</t>
+          <t>스톡옵션 행사</t>
         </is>
       </c>
       <c r="C141" s="22" t="n">
@@ -9181,7 +9181,7 @@
     <row r="142">
       <c r="A142" s="20" t="inlineStr">
         <is>
-          <t>Net Decrease Increase In Treasury Shares Fin CF</t>
+          <t>자기주식 감소</t>
         </is>
       </c>
       <c r="C142" s="22" t="n">
@@ -9248,7 +9248,7 @@
     <row r="143">
       <c r="A143" s="20" t="inlineStr">
         <is>
-          <t>Other Fin CF</t>
+          <t>기타재무활동</t>
         </is>
       </c>
       <c r="D143" s="22" t="n">
@@ -9416,7 +9416,7 @@
     <row r="146">
       <c r="A146" s="20" t="inlineStr">
         <is>
-          <t>Net Increase Decrease In Cash And Cash Equivalents</t>
+          <t>현금및현금성자산 증감액</t>
         </is>
       </c>
       <c r="C146" s="22" t="n">
@@ -12139,7 +12139,7 @@
     <row r="73">
       <c r="A73" s="20" t="inlineStr">
         <is>
-          <t>Intangible Assets</t>
+          <t>무형자산</t>
         </is>
       </c>
       <c r="C73" s="22" t="n">
@@ -12167,7 +12167,7 @@
     <row r="74">
       <c r="A74" s="20" t="inlineStr">
         <is>
-          <t>Long Term Financial Assets</t>
+          <t>장기금융자산</t>
         </is>
       </c>
       <c r="H74" s="22" t="n">
@@ -12208,7 +12208,7 @@
     <row r="76">
       <c r="A76" s="20" t="inlineStr">
         <is>
-          <t>Retirement Benefit Asset NCA</t>
+          <t>퇴직후급여자산</t>
         </is>
       </c>
       <c r="C76" s="22" t="n">
@@ -12236,7 +12236,7 @@
     <row r="77">
       <c r="A77" s="20" t="inlineStr">
         <is>
-          <t>Other Non Current Assets NCA</t>
+          <t>기타비유동자산</t>
         </is>
       </c>
       <c r="C77" s="22" t="n">
@@ -12264,7 +12264,7 @@
     <row r="78">
       <c r="A78" s="20" t="inlineStr">
         <is>
-          <t>Non Current Assets</t>
+          <t>비유동자산 합계</t>
         </is>
       </c>
       <c r="C78" s="22" t="n">
@@ -12320,7 +12320,7 @@
     <row r="80">
       <c r="A80" s="20" t="inlineStr">
         <is>
-          <t>Trade And Other Receivables CA</t>
+          <t>영업채권 및 기타채권</t>
         </is>
       </c>
       <c r="C80" s="22" t="n">
@@ -12348,7 +12348,7 @@
     <row r="81">
       <c r="A81" s="20" t="inlineStr">
         <is>
-          <t>Income Taxes Receivable CA</t>
+          <t>미수법인세</t>
         </is>
       </c>
       <c r="C81" s="22" t="n">
@@ -12404,7 +12404,7 @@
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>Cash And Cash Equivalents</t>
+          <t>현금및현금성자산</t>
         </is>
       </c>
       <c r="C83" s="22" t="n">
@@ -12432,7 +12432,7 @@
     <row r="84">
       <c r="A84" s="20" t="inlineStr">
         <is>
-          <t>Other Current Assets CA</t>
+          <t>기타유동자산</t>
         </is>
       </c>
       <c r="C84" s="22" t="n">
@@ -12544,7 +12544,7 @@
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>Retirement Benefit Liability NCL</t>
+          <t>퇴직후급여부채</t>
         </is>
       </c>
       <c r="C88" s="22" t="n">
@@ -12572,7 +12572,7 @@
     <row r="89">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>Provisions NCL</t>
+          <t>장기충당금</t>
         </is>
       </c>
       <c r="C89" s="22" t="n">
@@ -12600,7 +12600,7 @@
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>Other Non Current Liabilities NCL</t>
+          <t>기타비유동부채</t>
         </is>
       </c>
       <c r="C90" s="22" t="n">
@@ -12628,7 +12628,7 @@
     <row r="91">
       <c r="A91" s="20" t="inlineStr">
         <is>
-          <t>Non Current Labilities</t>
+          <t>비유동부채 합계</t>
         </is>
       </c>
       <c r="C91" s="22" t="n">
@@ -12656,7 +12656,7 @@
     <row r="92">
       <c r="A92" s="20" t="inlineStr">
         <is>
-          <t>Income Taxes Payable CL</t>
+          <t>미지급법인세</t>
         </is>
       </c>
       <c r="C92" s="22" t="n">
@@ -12684,7 +12684,7 @@
     <row r="93">
       <c r="A93" s="20" t="inlineStr">
         <is>
-          <t>Provisions CL</t>
+          <t>단기충당금</t>
         </is>
       </c>
       <c r="C93" s="22" t="n">
@@ -12712,7 +12712,7 @@
     <row r="94">
       <c r="A94" s="20" t="inlineStr">
         <is>
-          <t>Trade And Other Payables CL</t>
+          <t>영업채무 및 기타채무</t>
         </is>
       </c>
       <c r="C94" s="22" t="n">
@@ -12740,7 +12740,7 @@
     <row r="95">
       <c r="A95" s="20" t="inlineStr">
         <is>
-          <t>Other Current Liabilities CL</t>
+          <t>기타유동부채</t>
         </is>
       </c>
       <c r="C95" s="22" t="n">
@@ -12852,7 +12852,7 @@
     <row r="99">
       <c r="A99" s="20" t="inlineStr">
         <is>
-          <t>Equity Attributable To Owners Of Parent</t>
+          <t>지배기업 소유주 지분</t>
         </is>
       </c>
       <c r="C99" s="22" t="n">
@@ -12880,7 +12880,7 @@
     <row r="100">
       <c r="A100" s="20" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>자본 합계</t>
         </is>
       </c>
       <c r="C100" s="22" t="n">
@@ -12908,7 +12908,7 @@
     <row r="101">
       <c r="A101" s="20" t="inlineStr">
         <is>
-          <t>Liabilities And Equity</t>
+          <t>부채및자본 합계</t>
         </is>
       </c>
       <c r="C101" s="22" t="n">

--- a/docs/data/jp/xlsx/4519.xlsx
+++ b/docs/data/jp/xlsx/4519.xlsx
@@ -201,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -323,6 +323,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -717,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC146"/>
+  <dimension ref="A1:AC151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4183,10 +4186,12 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>현재 주가 ()</t>
-        </is>
-      </c>
-      <c r="B47" s="29" t="n"/>
+          <t>현재 주가 (2026.10.26)</t>
+        </is>
+      </c>
+      <c r="B47" s="29" t="n">
+        <v>6897</v>
+      </c>
       <c r="C47" s="30" t="n"/>
       <c r="D47" s="31" t="n"/>
       <c r="E47" s="31" t="n"/>
@@ -4221,7 +4226,9 @@
           <t>발행주식수 (보통주)</t>
         </is>
       </c>
-      <c r="B48" s="29" t="n"/>
+      <c r="B48" s="29" t="n">
+        <v>1679057667</v>
+      </c>
       <c r="C48" s="30" t="n"/>
       <c r="D48" s="31" t="n"/>
       <c r="E48" s="31" t="n"/>
@@ -5420,7 +5427,7 @@
     <row r="74">
       <c r="A74" s="43" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C74" s="41" t="n"/>
@@ -5672,3811 +5679,4147 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="inlineStr">
-        <is>
-          <t>제품·상품 매출액</t>
-        </is>
-      </c>
-      <c r="C79" s="22" t="n">
-        <v>219027</v>
-      </c>
-      <c r="D79" s="22" t="n">
-        <v>232417</v>
-      </c>
-      <c r="E79" s="22" t="n">
-        <v>204480</v>
-      </c>
-      <c r="F79" s="22" t="n">
-        <v>281052</v>
-      </c>
-      <c r="G79" s="22" t="n">
-        <v>264794</v>
-      </c>
-      <c r="H79" s="22" t="n">
-        <v>247575</v>
-      </c>
-      <c r="I79" s="22" t="n">
-        <v>259722</v>
-      </c>
-      <c r="J79" s="22" t="n">
-        <v>251717</v>
-      </c>
-      <c r="K79" s="22" t="n">
-        <v>283147</v>
-      </c>
-      <c r="L79" s="22" t="n">
-        <v>283217</v>
-      </c>
-      <c r="M79" s="22" t="n">
-        <v>291577</v>
-      </c>
-      <c r="N79" s="22" t="n">
-        <v>274910</v>
-      </c>
-      <c r="T79" s="22" t="n">
-        <v>264142</v>
-      </c>
-      <c r="U79" s="22" t="n">
-        <v>394574</v>
-      </c>
-      <c r="V79" s="22" t="n">
-        <v>232417</v>
-      </c>
-      <c r="W79" s="22" t="n">
-        <v>247575</v>
-      </c>
-      <c r="X79" s="22" t="n">
-        <v>283217</v>
+      <c r="A79" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G79" s="17">
+        <f>IF(OR(G78="",C78=""),"",IF(C78&lt;=0,"",IFERROR(G78/C78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H79" s="17">
+        <f>IF(OR(H78="",D78=""),"",IF(D78&lt;=0,"",IFERROR(H78/D78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I79" s="17">
+        <f>IF(OR(I78="",E78=""),"",IF(E78&lt;=0,"",IFERROR(I78/E78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J79" s="17">
+        <f>IF(OR(J78="",F78=""),"",IF(F78&lt;=0,"",IFERROR(J78/F78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K79" s="17">
+        <f>IF(OR(K78="",G78=""),"",IF(G78&lt;=0,"",IFERROR(K78/G78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L79" s="17">
+        <f>IF(OR(L78="",H78=""),"",IF(H78&lt;=0,"",IFERROR(L78/H78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M79" s="17">
+        <f>IF(OR(M78="",I78=""),"",IF(I78&lt;=0,"",IFERROR(M78/I78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N79" s="17">
+        <f>IF(OR(N78="",J78=""),"",IF(J78&lt;=0,"",IFERROR(N78/J78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T79" s="17">
+        <f>IF(OR(T78="",S78=""),"",IF(S78&lt;=0,"",IFERROR(T78/S78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U79" s="17">
+        <f>IF(OR(U78="",T78=""),"",IF(T78&lt;=0,"",IFERROR(U78/T78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V79" s="17">
+        <f>IF(OR(V78="",U78=""),"",IF(U78&lt;=0,"",IFERROR(V78/U78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W79" s="17">
+        <f>IF(OR(W78="",V78=""),"",IF(V78&lt;=0,"",IFERROR(W78/V78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X79" s="17">
+        <f>IF(OR(X78="",W78=""),"",IF(W78&lt;=0,"",IFERROR(X78/W78-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="20" t="inlineStr">
         <is>
-          <t>로열티 등 수입 및 기타 영업수입</t>
-        </is>
+          <t>제품·상품 매출액</t>
+        </is>
+      </c>
+      <c r="C80" s="22" t="n">
+        <v>219027</v>
+      </c>
+      <c r="D80" s="22" t="n">
+        <v>232417</v>
+      </c>
+      <c r="E80" s="22" t="n">
+        <v>204480</v>
+      </c>
+      <c r="F80" s="22" t="n">
+        <v>281052</v>
+      </c>
+      <c r="G80" s="22" t="n">
+        <v>264794</v>
+      </c>
+      <c r="H80" s="22" t="n">
+        <v>247575</v>
+      </c>
+      <c r="I80" s="22" t="n">
+        <v>259722</v>
+      </c>
+      <c r="J80" s="22" t="n">
+        <v>251717</v>
+      </c>
+      <c r="K80" s="22" t="n">
+        <v>283147</v>
+      </c>
+      <c r="L80" s="22" t="n">
+        <v>283217</v>
+      </c>
+      <c r="M80" s="22" t="n">
+        <v>291577</v>
+      </c>
+      <c r="N80" s="22" t="n">
+        <v>274910</v>
       </c>
       <c r="T80" s="22" t="n">
-        <v>58123</v>
+        <v>264142</v>
       </c>
       <c r="U80" s="22" t="n">
-        <v>43922</v>
+        <v>394574</v>
+      </c>
+      <c r="V80" s="22" t="n">
+        <v>232417</v>
+      </c>
+      <c r="W80" s="22" t="n">
+        <v>247575</v>
+      </c>
+      <c r="X80" s="22" t="n">
+        <v>283217</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="20" t="inlineStr">
         <is>
-          <t>기타 수입</t>
+          <t>로열티 등 수입 및 기타 영업수입</t>
         </is>
       </c>
       <c r="T81" s="22" t="n">
-        <v>0</v>
+        <v>58123</v>
       </c>
       <c r="U81" s="22" t="n">
-        <v>0</v>
+        <v>43922</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="20" t="inlineStr">
         <is>
-          <t>기타 매출수익</t>
-        </is>
-      </c>
-      <c r="C82" s="22" t="n">
-        <v>38871</v>
-      </c>
-      <c r="D82" s="22" t="n">
-        <v>41395</v>
-      </c>
-      <c r="E82" s="22" t="n">
-        <v>32469</v>
-      </c>
-      <c r="F82" s="22" t="n">
-        <v>34859</v>
-      </c>
-      <c r="G82" s="22" t="n">
-        <v>50884</v>
-      </c>
-      <c r="H82" s="22" t="n">
-        <v>54498</v>
-      </c>
-      <c r="I82" s="22" t="n">
-        <v>28737</v>
-      </c>
-      <c r="J82" s="22" t="n">
-        <v>38288</v>
-      </c>
-      <c r="K82" s="22" t="n">
-        <v>50029</v>
-      </c>
-      <c r="L82" s="22" t="n">
-        <v>63084</v>
-      </c>
-      <c r="M82" s="22" t="n">
-        <v>30170</v>
-      </c>
-      <c r="N82" s="22" t="n">
-        <v>66674</v>
+          <t>기타 수입</t>
+        </is>
+      </c>
+      <c r="T82" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="U82" s="22" t="n">
-        <v>43922</v>
-      </c>
-      <c r="V82" s="22" t="n">
-        <v>41395</v>
-      </c>
-      <c r="W82" s="22" t="n">
-        <v>54498</v>
-      </c>
-      <c r="X82" s="22" t="n">
-        <v>63084</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
+          <t>기타 매출수익</t>
+        </is>
+      </c>
+      <c r="C83" s="22" t="n">
+        <v>38871</v>
+      </c>
+      <c r="D83" s="22" t="n">
+        <v>41395</v>
+      </c>
+      <c r="E83" s="22" t="n">
+        <v>32469</v>
+      </c>
+      <c r="F83" s="22" t="n">
+        <v>34859</v>
+      </c>
+      <c r="G83" s="22" t="n">
+        <v>50884</v>
+      </c>
+      <c r="H83" s="22" t="n">
+        <v>54498</v>
+      </c>
+      <c r="I83" s="22" t="n">
+        <v>28737</v>
+      </c>
+      <c r="J83" s="22" t="n">
+        <v>38288</v>
+      </c>
+      <c r="K83" s="22" t="n">
+        <v>50029</v>
+      </c>
+      <c r="L83" s="22" t="n">
+        <v>63084</v>
+      </c>
+      <c r="M83" s="22" t="n">
+        <v>30170</v>
+      </c>
+      <c r="N83" s="22" t="n">
+        <v>66674</v>
+      </c>
+      <c r="U83" s="22" t="n">
+        <v>43922</v>
+      </c>
+      <c r="V83" s="22" t="n">
+        <v>41395</v>
+      </c>
+      <c r="W83" s="22" t="n">
+        <v>54498</v>
+      </c>
+      <c r="X83" s="22" t="n">
+        <v>63084</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="20" t="inlineStr">
+        <is>
           <t>매출원가</t>
         </is>
       </c>
-      <c r="C83" s="22" t="n">
+      <c r="C84" s="22" t="n">
         <v>78256</v>
       </c>
-      <c r="D83" s="22" t="n">
+      <c r="D84" s="22" t="n">
         <v>92060</v>
       </c>
-      <c r="E83" s="22" t="n">
+      <c r="E84" s="22" t="n">
         <v>72950</v>
       </c>
-      <c r="F83" s="22" t="n">
+      <c r="F84" s="22" t="n">
         <v>87940</v>
       </c>
-      <c r="G83" s="22" t="n">
+      <c r="G84" s="22" t="n">
         <v>84218</v>
       </c>
-      <c r="H83" s="22" t="n">
+      <c r="H84" s="22" t="n">
         <v>94301</v>
       </c>
-      <c r="I83" s="22" t="n">
+      <c r="I84" s="22" t="n">
         <v>87823</v>
       </c>
-      <c r="J83" s="22" t="n">
+      <c r="J84" s="22" t="n">
         <v>88068</v>
       </c>
-      <c r="K83" s="22" t="n">
+      <c r="K84" s="22" t="n">
         <v>100240</v>
       </c>
-      <c r="L83" s="22" t="n">
+      <c r="L84" s="22" t="n">
         <v>87559</v>
       </c>
-      <c r="M83" s="22" t="n">
+      <c r="M84" s="22" t="n">
         <v>92790</v>
       </c>
-      <c r="N83" s="22" t="n">
+      <c r="N84" s="22" t="n">
         <v>104218</v>
       </c>
-      <c r="T83" s="22" t="n">
+      <c r="T84" s="22" t="n">
         <v>110556</v>
       </c>
-      <c r="U83" s="22" t="n">
+      <c r="U84" s="22" t="n">
         <v>212908</v>
       </c>
-      <c r="V83" s="22" t="n">
+      <c r="V84" s="22" t="n">
         <v>92060</v>
       </c>
-      <c r="W83" s="22" t="n">
+      <c r="W84" s="22" t="n">
         <v>94301</v>
       </c>
-      <c r="X83" s="22" t="n">
+      <c r="X84" s="22" t="n">
         <v>87559</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="9" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
         <is>
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="C84" s="12" t="n">
+      <c r="C85" s="12" t="n">
         <v>179642</v>
       </c>
-      <c r="D84" s="12" t="n">
+      <c r="D85" s="12" t="n">
         <v>181752</v>
       </c>
-      <c r="E84" s="12" t="n">
+      <c r="E85" s="12" t="n">
         <v>163999</v>
       </c>
-      <c r="F84" s="12" t="n">
+      <c r="F85" s="12" t="n">
         <v>227971</v>
       </c>
-      <c r="G84" s="12" t="n">
+      <c r="G85" s="12" t="n">
         <v>231460</v>
       </c>
-      <c r="H84" s="12" t="n">
+      <c r="H85" s="12" t="n">
         <v>207771</v>
       </c>
-      <c r="I84" s="12" t="n">
+      <c r="I85" s="12" t="n">
         <v>200636</v>
       </c>
-      <c r="J84" s="12" t="n">
+      <c r="J85" s="12" t="n">
         <v>201937</v>
       </c>
-      <c r="K84" s="12" t="n">
+      <c r="K85" s="12" t="n">
         <v>232936</v>
       </c>
-      <c r="L84" s="12" t="n">
+      <c r="L85" s="12" t="n">
         <v>258742</v>
       </c>
-      <c r="M84" s="12" t="n">
+      <c r="M85" s="12" t="n">
         <v>228957</v>
       </c>
-      <c r="N84" s="12" t="n">
+      <c r="N85" s="12" t="n">
         <v>237366</v>
       </c>
-      <c r="T84" s="12" t="n">
+      <c r="T85" s="12" t="n">
         <v>211710</v>
       </c>
-      <c r="U84" s="12" t="n">
+      <c r="U85" s="12" t="n">
         <v>225587</v>
       </c>
-      <c r="V84" s="12" t="n">
+      <c r="V85" s="12" t="n">
         <v>181752</v>
       </c>
-      <c r="W84" s="12" t="n">
+      <c r="W85" s="12" t="n">
         <v>207771</v>
       </c>
-      <c r="X84" s="12" t="n">
+      <c r="X85" s="12" t="n">
         <v>258742</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="20" t="inlineStr">
-        <is>
-          <t>판매비</t>
-        </is>
-      </c>
-      <c r="T85" s="22" t="n">
-        <v>24346</v>
-      </c>
-      <c r="U85" s="22" t="n">
-        <v>23037</v>
-      </c>
-    </row>
     <row r="86">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>연구개발비</t>
-        </is>
-      </c>
-      <c r="C86" s="22" t="n">
-        <v>45574</v>
-      </c>
-      <c r="D86" s="22" t="n">
-        <v>41856</v>
-      </c>
-      <c r="E86" s="22" t="n">
-        <v>41355</v>
-      </c>
-      <c r="F86" s="22" t="n">
-        <v>42937</v>
-      </c>
-      <c r="G86" s="22" t="n">
-        <v>44920</v>
-      </c>
-      <c r="H86" s="22" t="n">
-        <v>52228</v>
-      </c>
-      <c r="I86" s="22" t="n">
-        <v>40927</v>
-      </c>
-      <c r="J86" s="22" t="n">
-        <v>45664</v>
-      </c>
-      <c r="K86" s="22" t="n">
-        <v>48601</v>
-      </c>
-      <c r="L86" s="22" t="n">
-        <v>52406</v>
-      </c>
-      <c r="M86" s="22" t="n">
-        <v>41887</v>
-      </c>
-      <c r="N86" s="22" t="n">
-        <v>47755</v>
-      </c>
-      <c r="T86" s="22" t="n">
-        <v>37807</v>
-      </c>
-      <c r="U86" s="22" t="n">
-        <v>45232</v>
-      </c>
-      <c r="V86" s="22" t="n">
-        <v>41856</v>
-      </c>
-      <c r="W86" s="22" t="n">
-        <v>52228</v>
-      </c>
-      <c r="X86" s="22" t="n">
-        <v>52406</v>
+      <c r="A86" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G86" s="17">
+        <f>IF(OR(G85="",C85=""),"",IF(C85&lt;=0,"",IFERROR(G85/C85-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H86" s="17">
+        <f>IF(OR(H85="",D85=""),"",IF(D85&lt;=0,"",IFERROR(H85/D85-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I86" s="17">
+        <f>IF(OR(I85="",E85=""),"",IF(E85&lt;=0,"",IFERROR(I85/E85-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J86" s="17">
+        <f>IF(OR(J85="",F85=""),"",IF(F85&lt;=0,"",IFERROR(J85/F85-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K86" s="17">
+        <f>IF(OR(K85="",G85=""),"",IF(G85&lt;=0,"",IFERROR(K85/G85-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L86" s="17">
+        <f>IF(OR(L85="",H85=""),"",IF(H85&lt;=0,"",IFERROR(L85/H85-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M86" s="17">
+        <f>IF(OR(M85="",I85=""),"",IF(I85&lt;=0,"",IFERROR(M85/I85-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N86" s="17">
+        <f>IF(OR(N85="",J85=""),"",IF(J85&lt;=0,"",IFERROR(N85/J85-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T86" s="17">
+        <f>IF(OR(T85="",S85=""),"",IF(S85&lt;=0,"",IFERROR(T85/S85-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U86" s="17">
+        <f>IF(OR(U85="",T85=""),"",IF(T85&lt;=0,"",IFERROR(U85/T85-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V86" s="17">
+        <f>IF(OR(V85="",U85=""),"",IF(U85&lt;=0,"",IFERROR(V85/U85-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W86" s="17">
+        <f>IF(OR(W85="",V85=""),"",IF(V85&lt;=0,"",IFERROR(W85/V85-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X86" s="17">
+        <f>IF(OR(X85="",W85=""),"",IF(W85&lt;=0,"",IFERROR(X85/W85-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>일반관리비 등</t>
+          <t>판매비</t>
         </is>
       </c>
       <c r="T87" s="22" t="n">
-        <v>10495</v>
+        <v>24346</v>
       </c>
       <c r="U87" s="22" t="n">
-        <v>7844</v>
+        <v>23037</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>판매비와 관리비</t>
+          <t>연구개발비</t>
         </is>
       </c>
       <c r="C88" s="22" t="n">
-        <v>27541</v>
+        <v>45574</v>
       </c>
       <c r="D88" s="22" t="n">
-        <v>30759</v>
+        <v>41856</v>
       </c>
       <c r="E88" s="22" t="n">
-        <v>22586</v>
+        <v>41355</v>
       </c>
       <c r="F88" s="22" t="n">
-        <v>27315</v>
+        <v>42937</v>
       </c>
       <c r="G88" s="22" t="n">
-        <v>27779</v>
+        <v>44920</v>
       </c>
       <c r="H88" s="22" t="n">
-        <v>32418</v>
+        <v>52228</v>
       </c>
       <c r="I88" s="22" t="n">
-        <v>23237</v>
+        <v>40927</v>
       </c>
       <c r="J88" s="22" t="n">
-        <v>28411</v>
+        <v>45664</v>
       </c>
       <c r="K88" s="22" t="n">
-        <v>27888</v>
+        <v>48601</v>
       </c>
       <c r="L88" s="22" t="n">
-        <v>36925</v>
+        <v>52406</v>
       </c>
       <c r="M88" s="22" t="n">
-        <v>28901</v>
+        <v>41887</v>
       </c>
       <c r="N88" s="22" t="n">
-        <v>29044</v>
+        <v>47755</v>
+      </c>
+      <c r="T88" s="22" t="n">
+        <v>37807</v>
       </c>
       <c r="U88" s="22" t="n">
-        <v>30753</v>
+        <v>45232</v>
       </c>
       <c r="V88" s="22" t="n">
-        <v>30759</v>
+        <v>41856</v>
       </c>
       <c r="W88" s="22" t="n">
-        <v>32418</v>
+        <v>52228</v>
       </c>
       <c r="X88" s="22" t="n">
-        <v>36925</v>
+        <v>52406</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>기타영업수익(비용)</t>
-        </is>
-      </c>
-      <c r="C89" s="22" t="n">
-        <v>160</v>
-      </c>
-      <c r="D89" s="22" t="n">
-        <v>12439</v>
-      </c>
-      <c r="E89" s="22" t="n">
-        <v>-185</v>
-      </c>
-      <c r="F89" s="22" t="n">
-        <v>604</v>
-      </c>
-      <c r="G89" s="22" t="n">
-        <v>1645</v>
-      </c>
-      <c r="H89" s="22" t="n">
-        <v>275</v>
-      </c>
-      <c r="I89" s="22" t="n">
-        <v>178</v>
-      </c>
-      <c r="J89" s="22" t="n">
-        <v>8830</v>
-      </c>
-      <c r="K89" s="22" t="n">
-        <v>38</v>
-      </c>
-      <c r="L89" s="22" t="n">
-        <v>-405</v>
-      </c>
-      <c r="M89" s="22" t="n">
-        <v>596</v>
-      </c>
-      <c r="N89" s="22" t="n">
-        <v>291</v>
+          <t>일반관리비 등</t>
+        </is>
+      </c>
+      <c r="T89" s="22" t="n">
+        <v>10495</v>
       </c>
       <c r="U89" s="22" t="n">
-        <v>-128</v>
-      </c>
-      <c r="V89" s="22" t="n">
-        <v>12439</v>
-      </c>
-      <c r="W89" s="22" t="n">
-        <v>275</v>
-      </c>
-      <c r="X89" s="22" t="n">
-        <v>-405</v>
+        <v>7844</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>영업이익</t>
+          <t>판매비와 관리비</t>
         </is>
       </c>
       <c r="C90" s="22" t="n">
-        <v>106688</v>
+        <v>27541</v>
       </c>
       <c r="D90" s="22" t="n">
-        <v>121576</v>
+        <v>30759</v>
       </c>
       <c r="E90" s="22" t="n">
-        <v>99874</v>
+        <v>22586</v>
       </c>
       <c r="F90" s="22" t="n">
-        <v>158321</v>
+        <v>27315</v>
       </c>
       <c r="G90" s="22" t="n">
-        <v>160407</v>
+        <v>27779</v>
       </c>
       <c r="H90" s="22" t="n">
-        <v>123400</v>
+        <v>32418</v>
       </c>
       <c r="I90" s="22" t="n">
-        <v>136651</v>
+        <v>23237</v>
       </c>
       <c r="J90" s="22" t="n">
-        <v>136691</v>
+        <v>28411</v>
       </c>
       <c r="K90" s="22" t="n">
-        <v>156485</v>
+        <v>27888</v>
       </c>
       <c r="L90" s="22" t="n">
-        <v>169006</v>
+        <v>36925</v>
       </c>
       <c r="M90" s="22" t="n">
-        <v>158765</v>
+        <v>28901</v>
       </c>
       <c r="N90" s="22" t="n">
-        <v>160858</v>
-      </c>
-      <c r="T90" s="22" t="n">
-        <v>139062</v>
+        <v>29044</v>
       </c>
       <c r="U90" s="22" t="n">
-        <v>149474</v>
+        <v>30753</v>
       </c>
       <c r="V90" s="22" t="n">
-        <v>121576</v>
+        <v>30759</v>
       </c>
       <c r="W90" s="22" t="n">
-        <v>123400</v>
+        <v>32418</v>
       </c>
       <c r="X90" s="22" t="n">
-        <v>169006</v>
+        <v>36925</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="20" t="inlineStr">
         <is>
-          <t>금융비용</t>
+          <t>기타영업수익(비용)</t>
         </is>
       </c>
       <c r="C91" s="22" t="n">
-        <v>8</v>
+        <v>160</v>
       </c>
       <c r="D91" s="22" t="n">
-        <v>8</v>
+        <v>12439</v>
       </c>
       <c r="E91" s="22" t="n">
-        <v>-3</v>
+        <v>-185</v>
       </c>
       <c r="F91" s="22" t="n">
-        <v>-1</v>
+        <v>604</v>
       </c>
       <c r="G91" s="22" t="n">
-        <v>-1</v>
+        <v>1645</v>
       </c>
       <c r="H91" s="22" t="n">
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="I91" s="22" t="n">
-        <v>-3</v>
+        <v>178</v>
       </c>
       <c r="J91" s="22" t="n">
-        <v>57</v>
+        <v>8830</v>
       </c>
       <c r="K91" s="22" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="L91" s="22" t="n">
-        <v>95</v>
+        <v>-405</v>
       </c>
       <c r="M91" s="22" t="n">
-        <v>-42</v>
+        <v>596</v>
       </c>
       <c r="N91" s="22" t="n">
-        <v>-44</v>
-      </c>
-      <c r="T91" s="22" t="n">
-        <v>12</v>
+        <v>291</v>
       </c>
       <c r="U91" s="22" t="n">
-        <v>16</v>
+        <v>-128</v>
       </c>
       <c r="V91" s="22" t="n">
-        <v>8</v>
+        <v>12439</v>
       </c>
       <c r="W91" s="22" t="n">
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="X91" s="22" t="n">
-        <v>95</v>
+        <v>-405</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="20" t="inlineStr">
         <is>
-          <t>기타금융수익(비용)</t>
+          <t>영업이익</t>
         </is>
       </c>
       <c r="C92" s="22" t="n">
-        <v>795</v>
+        <v>106688</v>
       </c>
       <c r="D92" s="22" t="n">
-        <v>1122</v>
+        <v>121576</v>
       </c>
       <c r="E92" s="22" t="n">
-        <v>12</v>
+        <v>99874</v>
       </c>
       <c r="F92" s="22" t="n">
-        <v>479</v>
+        <v>158321</v>
       </c>
       <c r="G92" s="22" t="n">
-        <v>-1571</v>
+        <v>160407</v>
       </c>
       <c r="H92" s="22" t="n">
-        <v>2107</v>
+        <v>123400</v>
       </c>
       <c r="I92" s="22" t="n">
-        <v>-825</v>
+        <v>136651</v>
       </c>
       <c r="J92" s="22" t="n">
-        <v>-633</v>
+        <v>136691</v>
       </c>
       <c r="K92" s="22" t="n">
-        <v>-355</v>
+        <v>156485</v>
       </c>
       <c r="L92" s="22" t="n">
-        <v>994</v>
+        <v>169006</v>
       </c>
       <c r="M92" s="22" t="n">
-        <v>1390</v>
+        <v>158765</v>
       </c>
       <c r="N92" s="22" t="n">
-        <v>3655</v>
+        <v>160858</v>
       </c>
       <c r="T92" s="22" t="n">
-        <v>-869</v>
+        <v>139062</v>
       </c>
       <c r="U92" s="22" t="n">
-        <v>-510</v>
+        <v>149474</v>
       </c>
       <c r="V92" s="22" t="n">
-        <v>1122</v>
+        <v>121576</v>
       </c>
       <c r="W92" s="22" t="n">
-        <v>2107</v>
+        <v>123400</v>
       </c>
       <c r="X92" s="22" t="n">
-        <v>994</v>
+        <v>169006</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="20" t="inlineStr">
-        <is>
-          <t>기타비용</t>
-        </is>
-      </c>
-      <c r="C93" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D93" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T93" s="22" t="n">
-        <v>-259</v>
-      </c>
-      <c r="U93" s="22" t="n">
-        <v>-267</v>
-      </c>
-      <c r="V93" s="22" t="n">
-        <v>0</v>
+      <c r="A93" s="45" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C93" s="17">
+        <f>IF(OR(C92="",C78=""),"",IF(C78&lt;=0,"",IFERROR(C92/C78,"")))</f>
+        <v/>
+      </c>
+      <c r="D93" s="17">
+        <f>IF(OR(D92="",D78=""),"",IF(D78&lt;=0,"",IFERROR(D92/D78,"")))</f>
+        <v/>
+      </c>
+      <c r="E93" s="17">
+        <f>IF(OR(E92="",E78=""),"",IF(E78&lt;=0,"",IFERROR(E92/E78,"")))</f>
+        <v/>
+      </c>
+      <c r="F93" s="17">
+        <f>IF(OR(F92="",F78=""),"",IF(F78&lt;=0,"",IFERROR(F92/F78,"")))</f>
+        <v/>
+      </c>
+      <c r="G93" s="17">
+        <f>IF(OR(G92="",G78=""),"",IF(G78&lt;=0,"",IFERROR(G92/G78,"")))</f>
+        <v/>
+      </c>
+      <c r="H93" s="17">
+        <f>IF(OR(H92="",H78=""),"",IF(H78&lt;=0,"",IFERROR(H92/H78,"")))</f>
+        <v/>
+      </c>
+      <c r="I93" s="17">
+        <f>IF(OR(I92="",I78=""),"",IF(I78&lt;=0,"",IFERROR(I92/I78,"")))</f>
+        <v/>
+      </c>
+      <c r="J93" s="17">
+        <f>IF(OR(J92="",J78=""),"",IF(J78&lt;=0,"",IFERROR(J92/J78,"")))</f>
+        <v/>
+      </c>
+      <c r="K93" s="17">
+        <f>IF(OR(K92="",K78=""),"",IF(K78&lt;=0,"",IFERROR(K92/K78,"")))</f>
+        <v/>
+      </c>
+      <c r="L93" s="17">
+        <f>IF(OR(L92="",L78=""),"",IF(L78&lt;=0,"",IFERROR(L92/L78,"")))</f>
+        <v/>
+      </c>
+      <c r="M93" s="17">
+        <f>IF(OR(M92="",M78=""),"",IF(M78&lt;=0,"",IFERROR(M92/M78,"")))</f>
+        <v/>
+      </c>
+      <c r="N93" s="17">
+        <f>IF(OR(N92="",N78=""),"",IF(N78&lt;=0,"",IFERROR(N92/N78,"")))</f>
+        <v/>
+      </c>
+      <c r="T93" s="17">
+        <f>IF(OR(T92="",T78=""),"",IF(T78&lt;=0,"",IFERROR(T92/T78,"")))</f>
+        <v/>
+      </c>
+      <c r="U93" s="17">
+        <f>IF(OR(U92="",U78=""),"",IF(U78&lt;=0,"",IFERROR(U92/U78,"")))</f>
+        <v/>
+      </c>
+      <c r="V93" s="17">
+        <f>IF(OR(V92="",V78=""),"",IF(V78&lt;=0,"",IFERROR(V92/V78,"")))</f>
+        <v/>
+      </c>
+      <c r="W93" s="17">
+        <f>IF(OR(W92="",W78=""),"",IF(W78&lt;=0,"",IFERROR(W92/W78,"")))</f>
+        <v/>
+      </c>
+      <c r="X93" s="17">
+        <f>IF(OR(X92="",X78=""),"",IF(X78&lt;=0,"",IFERROR(X92/X78,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="9" t="inlineStr">
-        <is>
-          <t>법인세비용차감전 중간이익</t>
-        </is>
-      </c>
-      <c r="C94" s="12" t="n">
-        <v>107475</v>
-      </c>
-      <c r="D94" s="12" t="n">
-        <v>122690</v>
-      </c>
-      <c r="E94" s="12" t="n">
-        <v>99889</v>
-      </c>
-      <c r="F94" s="12" t="n">
-        <v>158801</v>
-      </c>
-      <c r="G94" s="12" t="n">
-        <v>158837</v>
-      </c>
-      <c r="H94" s="12" t="n">
-        <v>125507</v>
-      </c>
-      <c r="I94" s="12" t="n">
-        <v>135829</v>
-      </c>
-      <c r="J94" s="12" t="n">
-        <v>136001</v>
-      </c>
-      <c r="K94" s="12" t="n">
-        <v>156072</v>
-      </c>
-      <c r="L94" s="12" t="n">
-        <v>169905</v>
-      </c>
-      <c r="M94" s="12" t="n">
-        <v>160197</v>
-      </c>
-      <c r="N94" s="12" t="n">
-        <v>169023</v>
-      </c>
-      <c r="T94" s="12" t="n">
-        <v>138440</v>
-      </c>
-      <c r="U94" s="12" t="n">
-        <v>149216</v>
-      </c>
-      <c r="V94" s="12" t="n">
-        <v>122690</v>
-      </c>
-      <c r="W94" s="12" t="n">
-        <v>125507</v>
-      </c>
-      <c r="X94" s="12" t="n">
-        <v>169905</v>
+      <c r="A94" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G94" s="17">
+        <f>IF(OR(G92="",C92=""),"",IF(C92&lt;=0,"",IFERROR(G92/C92-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H94" s="17">
+        <f>IF(OR(H92="",D92=""),"",IF(D92&lt;=0,"",IFERROR(H92/D92-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I94" s="17">
+        <f>IF(OR(I92="",E92=""),"",IF(E92&lt;=0,"",IFERROR(I92/E92-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J94" s="17">
+        <f>IF(OR(J92="",F92=""),"",IF(F92&lt;=0,"",IFERROR(J92/F92-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K94" s="17">
+        <f>IF(OR(K92="",G92=""),"",IF(G92&lt;=0,"",IFERROR(K92/G92-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L94" s="17">
+        <f>IF(OR(L92="",H92=""),"",IF(H92&lt;=0,"",IFERROR(L92/H92-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M94" s="17">
+        <f>IF(OR(M92="",I92=""),"",IF(I92&lt;=0,"",IFERROR(M92/I92-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N94" s="17">
+        <f>IF(OR(N92="",J92=""),"",IF(J92&lt;=0,"",IFERROR(N92/J92-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T94" s="17">
+        <f>IF(OR(T92="",S92=""),"",IF(S92&lt;=0,"",IFERROR(T92/S92-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U94" s="17">
+        <f>IF(OR(U92="",T92=""),"",IF(T92&lt;=0,"",IFERROR(U92/T92-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V94" s="17">
+        <f>IF(OR(V92="",U92=""),"",IF(U92&lt;=0,"",IFERROR(V92/U92-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W94" s="17">
+        <f>IF(OR(W92="",V92=""),"",IF(V92&lt;=0,"",IFERROR(W92/V92-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X94" s="17">
+        <f>IF(OR(X92="",W92=""),"",IF(W92&lt;=0,"",IFERROR(X92/W92-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="20" t="inlineStr">
         <is>
-          <t>법인소득세</t>
+          <t>금융비용</t>
         </is>
       </c>
       <c r="C95" s="22" t="n">
-        <v>29902</v>
+        <v>8</v>
       </c>
       <c r="D95" s="22" t="n">
-        <v>31484</v>
+        <v>8</v>
       </c>
       <c r="E95" s="22" t="n">
-        <v>25488</v>
+        <v>-3</v>
       </c>
       <c r="F95" s="22" t="n">
-        <v>46940</v>
+        <v>-1</v>
       </c>
       <c r="G95" s="22" t="n">
-        <v>49341</v>
+        <v>-1</v>
       </c>
       <c r="H95" s="22" t="n">
-        <v>33948</v>
+        <v>0</v>
       </c>
       <c r="I95" s="22" t="n">
-        <v>38595</v>
+        <v>-3</v>
       </c>
       <c r="J95" s="22" t="n">
-        <v>38846</v>
+        <v>57</v>
       </c>
       <c r="K95" s="22" t="n">
-        <v>44858</v>
+        <v>58</v>
       </c>
       <c r="L95" s="22" t="n">
-        <v>41495</v>
+        <v>95</v>
       </c>
       <c r="M95" s="22" t="n">
-        <v>44779</v>
+        <v>-42</v>
       </c>
       <c r="N95" s="22" t="n">
-        <v>52693</v>
+        <v>-44</v>
       </c>
       <c r="T95" s="22" t="n">
-        <v>39599</v>
+        <v>12</v>
       </c>
       <c r="U95" s="22" t="n">
-        <v>46737</v>
+        <v>16</v>
       </c>
       <c r="V95" s="22" t="n">
-        <v>31484</v>
+        <v>8</v>
       </c>
       <c r="W95" s="22" t="n">
-        <v>33948</v>
+        <v>0</v>
       </c>
       <c r="X95" s="22" t="n">
-        <v>41495</v>
+        <v>95</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="9" t="inlineStr">
-        <is>
-          <t>중간이익</t>
-        </is>
-      </c>
-      <c r="C96" s="12" t="n">
-        <v>77573</v>
-      </c>
-      <c r="D96" s="12" t="n">
-        <v>91206</v>
-      </c>
-      <c r="E96" s="12" t="n">
-        <v>74401</v>
-      </c>
-      <c r="F96" s="12" t="n">
-        <v>111861</v>
-      </c>
-      <c r="G96" s="12" t="n">
-        <v>109496</v>
-      </c>
-      <c r="H96" s="12" t="n">
-        <v>91559</v>
-      </c>
-      <c r="I96" s="12" t="n">
-        <v>97234</v>
-      </c>
-      <c r="J96" s="12" t="n">
-        <v>97155</v>
-      </c>
-      <c r="K96" s="12" t="n">
-        <v>111213</v>
-      </c>
-      <c r="L96" s="12" t="n">
-        <v>128410</v>
-      </c>
-      <c r="M96" s="12" t="n">
-        <v>115418</v>
-      </c>
-      <c r="N96" s="12" t="n">
-        <v>116331</v>
-      </c>
-      <c r="T96" s="12" t="n">
-        <v>98841</v>
-      </c>
-      <c r="U96" s="12" t="n">
-        <v>102479</v>
-      </c>
-      <c r="V96" s="12" t="n">
-        <v>91206</v>
-      </c>
-      <c r="W96" s="12" t="n">
-        <v>91559</v>
-      </c>
-      <c r="X96" s="12" t="n">
-        <v>128410</v>
+      <c r="A96" s="20" t="inlineStr">
+        <is>
+          <t>기타금융수익(비용)</t>
+        </is>
+      </c>
+      <c r="C96" s="22" t="n">
+        <v>795</v>
+      </c>
+      <c r="D96" s="22" t="n">
+        <v>1122</v>
+      </c>
+      <c r="E96" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="F96" s="22" t="n">
+        <v>479</v>
+      </c>
+      <c r="G96" s="22" t="n">
+        <v>-1571</v>
+      </c>
+      <c r="H96" s="22" t="n">
+        <v>2107</v>
+      </c>
+      <c r="I96" s="22" t="n">
+        <v>-825</v>
+      </c>
+      <c r="J96" s="22" t="n">
+        <v>-633</v>
+      </c>
+      <c r="K96" s="22" t="n">
+        <v>-355</v>
+      </c>
+      <c r="L96" s="22" t="n">
+        <v>994</v>
+      </c>
+      <c r="M96" s="22" t="n">
+        <v>1390</v>
+      </c>
+      <c r="N96" s="22" t="n">
+        <v>3655</v>
+      </c>
+      <c r="T96" s="22" t="n">
+        <v>-869</v>
+      </c>
+      <c r="U96" s="22" t="n">
+        <v>-510</v>
+      </c>
+      <c r="V96" s="22" t="n">
+        <v>1122</v>
+      </c>
+      <c r="W96" s="22" t="n">
+        <v>2107</v>
+      </c>
+      <c r="X96" s="22" t="n">
+        <v>994</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="9" t="inlineStr">
-        <is>
-          <t>지배기업 소유주 지분</t>
-        </is>
-      </c>
-      <c r="C97" s="12" t="n">
-        <v>77573</v>
-      </c>
-      <c r="D97" s="12" t="n">
-        <v>91206</v>
-      </c>
-      <c r="E97" s="12" t="n">
-        <v>74401</v>
-      </c>
-      <c r="F97" s="12" t="n">
-        <v>111861</v>
-      </c>
-      <c r="G97" s="12" t="n">
-        <v>109496</v>
-      </c>
-      <c r="H97" s="12" t="n">
-        <v>91559</v>
-      </c>
-      <c r="I97" s="12" t="n">
-        <v>97234</v>
-      </c>
-      <c r="J97" s="12" t="n">
-        <v>97155</v>
-      </c>
-      <c r="K97" s="12" t="n">
-        <v>111213</v>
-      </c>
-      <c r="L97" s="12" t="n">
-        <v>128410</v>
-      </c>
-      <c r="M97" s="12" t="n">
-        <v>115418</v>
-      </c>
-      <c r="N97" s="12" t="n">
-        <v>116331</v>
-      </c>
-      <c r="T97" s="12" t="n">
-        <v>98841</v>
-      </c>
-      <c r="U97" s="12" t="n">
-        <v>102479</v>
-      </c>
-      <c r="V97" s="12" t="n">
-        <v>91206</v>
-      </c>
-      <c r="W97" s="12" t="n">
-        <v>91559</v>
-      </c>
-      <c r="X97" s="12" t="n">
-        <v>128410</v>
+      <c r="A97" s="20" t="inlineStr">
+        <is>
+          <t>기타비용</t>
+        </is>
+      </c>
+      <c r="C97" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T97" s="22" t="n">
+        <v>-259</v>
+      </c>
+      <c r="U97" s="22" t="n">
+        <v>-267</v>
+      </c>
+      <c r="V97" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="20" t="inlineStr">
-        <is>
-          <t>기본 주당 중간이익(엔)</t>
-        </is>
-      </c>
-      <c r="C98" s="22" t="n">
-        <v>4.715000000000001e-05</v>
-      </c>
-      <c r="D98" s="22" t="n">
-        <v>5.543000000000001e-05</v>
-      </c>
-      <c r="E98" s="22" t="n">
-        <v>4.522e-05</v>
-      </c>
-      <c r="F98" s="22" t="n">
-        <v>6.798000000000001e-05</v>
-      </c>
-      <c r="G98" s="22" t="n">
-        <v>6.654999999999999e-05</v>
-      </c>
-      <c r="H98" s="22" t="n">
-        <v>5.563999999999999e-05</v>
-      </c>
-      <c r="I98" s="22" t="n">
-        <v>5.909000000000001e-05</v>
-      </c>
-      <c r="J98" s="22" t="n">
-        <v>5.903999999999999e-05</v>
-      </c>
-      <c r="K98" s="22" t="n">
-        <v>6.756999999999999e-05</v>
-      </c>
-      <c r="L98" s="22" t="n">
-        <v>7.803000000000002e-05</v>
-      </c>
-      <c r="M98" s="22" t="n">
-        <v>7.012999999999999e-05</v>
-      </c>
-      <c r="N98" s="22" t="n">
-        <v>7.069e-05</v>
-      </c>
-      <c r="T98" s="22" t="n">
-        <v>6.011999999999999e-05</v>
-      </c>
-      <c r="U98" s="22" t="n">
-        <v>6.228999999999999e-05</v>
-      </c>
-      <c r="V98" s="22" t="n">
-        <v>5.543000000000001e-05</v>
-      </c>
-      <c r="W98" s="22" t="n">
-        <v>5.563999999999999e-05</v>
-      </c>
-      <c r="X98" s="22" t="n">
-        <v>7.803000000000002e-05</v>
+      <c r="A98" s="9" t="inlineStr">
+        <is>
+          <t>법인세비용차감전 중간이익</t>
+        </is>
+      </c>
+      <c r="C98" s="12" t="n">
+        <v>107475</v>
+      </c>
+      <c r="D98" s="12" t="n">
+        <v>122690</v>
+      </c>
+      <c r="E98" s="12" t="n">
+        <v>99889</v>
+      </c>
+      <c r="F98" s="12" t="n">
+        <v>158801</v>
+      </c>
+      <c r="G98" s="12" t="n">
+        <v>158837</v>
+      </c>
+      <c r="H98" s="12" t="n">
+        <v>125507</v>
+      </c>
+      <c r="I98" s="12" t="n">
+        <v>135829</v>
+      </c>
+      <c r="J98" s="12" t="n">
+        <v>136001</v>
+      </c>
+      <c r="K98" s="12" t="n">
+        <v>156072</v>
+      </c>
+      <c r="L98" s="12" t="n">
+        <v>169905</v>
+      </c>
+      <c r="M98" s="12" t="n">
+        <v>160197</v>
+      </c>
+      <c r="N98" s="12" t="n">
+        <v>169023</v>
+      </c>
+      <c r="T98" s="12" t="n">
+        <v>138440</v>
+      </c>
+      <c r="U98" s="12" t="n">
+        <v>149216</v>
+      </c>
+      <c r="V98" s="12" t="n">
+        <v>122690</v>
+      </c>
+      <c r="W98" s="12" t="n">
+        <v>125507</v>
+      </c>
+      <c r="X98" s="12" t="n">
+        <v>169905</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="20" t="inlineStr">
         <is>
-          <t>희석 주당 중간이익(엔)</t>
+          <t>법인소득세</t>
         </is>
       </c>
       <c r="C99" s="22" t="n">
-        <v>4.714e-05</v>
+        <v>29902</v>
       </c>
       <c r="D99" s="22" t="n">
+        <v>31484</v>
+      </c>
+      <c r="E99" s="22" t="n">
+        <v>25488</v>
+      </c>
+      <c r="F99" s="22" t="n">
+        <v>46940</v>
+      </c>
+      <c r="G99" s="22" t="n">
+        <v>49341</v>
+      </c>
+      <c r="H99" s="22" t="n">
+        <v>33948</v>
+      </c>
+      <c r="I99" s="22" t="n">
+        <v>38595</v>
+      </c>
+      <c r="J99" s="22" t="n">
+        <v>38846</v>
+      </c>
+      <c r="K99" s="22" t="n">
+        <v>44858</v>
+      </c>
+      <c r="L99" s="22" t="n">
+        <v>41495</v>
+      </c>
+      <c r="M99" s="22" t="n">
+        <v>44779</v>
+      </c>
+      <c r="N99" s="22" t="n">
+        <v>52693</v>
+      </c>
+      <c r="T99" s="22" t="n">
+        <v>39599</v>
+      </c>
+      <c r="U99" s="22" t="n">
+        <v>46737</v>
+      </c>
+      <c r="V99" s="22" t="n">
+        <v>31484</v>
+      </c>
+      <c r="W99" s="22" t="n">
+        <v>33948</v>
+      </c>
+      <c r="X99" s="22" t="n">
+        <v>41495</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="inlineStr">
+        <is>
+          <t>중간이익</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="n">
+        <v>77573</v>
+      </c>
+      <c r="D100" s="12" t="n">
+        <v>91206</v>
+      </c>
+      <c r="E100" s="12" t="n">
+        <v>74401</v>
+      </c>
+      <c r="F100" s="12" t="n">
+        <v>111861</v>
+      </c>
+      <c r="G100" s="12" t="n">
+        <v>109496</v>
+      </c>
+      <c r="H100" s="12" t="n">
+        <v>91559</v>
+      </c>
+      <c r="I100" s="12" t="n">
+        <v>97234</v>
+      </c>
+      <c r="J100" s="12" t="n">
+        <v>97155</v>
+      </c>
+      <c r="K100" s="12" t="n">
+        <v>111213</v>
+      </c>
+      <c r="L100" s="12" t="n">
+        <v>128410</v>
+      </c>
+      <c r="M100" s="12" t="n">
+        <v>115418</v>
+      </c>
+      <c r="N100" s="12" t="n">
+        <v>116331</v>
+      </c>
+      <c r="T100" s="12" t="n">
+        <v>98841</v>
+      </c>
+      <c r="U100" s="12" t="n">
+        <v>102479</v>
+      </c>
+      <c r="V100" s="12" t="n">
+        <v>91206</v>
+      </c>
+      <c r="W100" s="12" t="n">
+        <v>91559</v>
+      </c>
+      <c r="X100" s="12" t="n">
+        <v>128410</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr">
+        <is>
+          <t>지배기업 소유주 지분</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="n">
+        <v>77573</v>
+      </c>
+      <c r="D101" s="12" t="n">
+        <v>91206</v>
+      </c>
+      <c r="E101" s="12" t="n">
+        <v>74401</v>
+      </c>
+      <c r="F101" s="12" t="n">
+        <v>111861</v>
+      </c>
+      <c r="G101" s="12" t="n">
+        <v>109496</v>
+      </c>
+      <c r="H101" s="12" t="n">
+        <v>91559</v>
+      </c>
+      <c r="I101" s="12" t="n">
+        <v>97234</v>
+      </c>
+      <c r="J101" s="12" t="n">
+        <v>97155</v>
+      </c>
+      <c r="K101" s="12" t="n">
+        <v>111213</v>
+      </c>
+      <c r="L101" s="12" t="n">
+        <v>128410</v>
+      </c>
+      <c r="M101" s="12" t="n">
+        <v>115418</v>
+      </c>
+      <c r="N101" s="12" t="n">
+        <v>116331</v>
+      </c>
+      <c r="T101" s="12" t="n">
+        <v>98841</v>
+      </c>
+      <c r="U101" s="12" t="n">
+        <v>102479</v>
+      </c>
+      <c r="V101" s="12" t="n">
+        <v>91206</v>
+      </c>
+      <c r="W101" s="12" t="n">
+        <v>91559</v>
+      </c>
+      <c r="X101" s="12" t="n">
+        <v>128410</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G102" s="17">
+        <f>IF(OR(G101="",C101=""),"",IF(C101&lt;=0,"",IFERROR(G101/C101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H102" s="17">
+        <f>IF(OR(H101="",D101=""),"",IF(D101&lt;=0,"",IFERROR(H101/D101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I102" s="17">
+        <f>IF(OR(I101="",E101=""),"",IF(E101&lt;=0,"",IFERROR(I101/E101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J102" s="17">
+        <f>IF(OR(J101="",F101=""),"",IF(F101&lt;=0,"",IFERROR(J101/F101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K102" s="17">
+        <f>IF(OR(K101="",G101=""),"",IF(G101&lt;=0,"",IFERROR(K101/G101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L102" s="17">
+        <f>IF(OR(L101="",H101=""),"",IF(H101&lt;=0,"",IFERROR(L101/H101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M102" s="17">
+        <f>IF(OR(M101="",I101=""),"",IF(I101&lt;=0,"",IFERROR(M101/I101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N102" s="17">
+        <f>IF(OR(N101="",J101=""),"",IF(J101&lt;=0,"",IFERROR(N101/J101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T102" s="17">
+        <f>IF(OR(T101="",S101=""),"",IF(S101&lt;=0,"",IFERROR(T101/S101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U102" s="17">
+        <f>IF(OR(U101="",T101=""),"",IF(T101&lt;=0,"",IFERROR(U101/T101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V102" s="17">
+        <f>IF(OR(V101="",U101=""),"",IF(U101&lt;=0,"",IFERROR(V101/U101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W102" s="17">
+        <f>IF(OR(W101="",V101=""),"",IF(V101&lt;=0,"",IFERROR(W101/V101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X102" s="17">
+        <f>IF(OR(X101="",W101=""),"",IF(W101&lt;=0,"",IFERROR(X101/W101-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="20" t="inlineStr">
+        <is>
+          <t>기본 주당 중간이익(엔)</t>
+        </is>
+      </c>
+      <c r="C103" s="22" t="n">
+        <v>4.715000000000001e-05</v>
+      </c>
+      <c r="D103" s="22" t="n">
         <v>5.543000000000001e-05</v>
       </c>
-      <c r="E99" s="22" t="n">
-        <v>4.521e-05</v>
-      </c>
-      <c r="F99" s="22" t="n">
-        <v>6.798e-05</v>
-      </c>
-      <c r="G99" s="22" t="n">
-        <v>6.653e-05</v>
-      </c>
-      <c r="H99" s="22" t="n">
-        <v>5.564000000000002e-05</v>
-      </c>
-      <c r="I99" s="22" t="n">
-        <v>5.908e-05</v>
-      </c>
-      <c r="J99" s="22" t="n">
-        <v>5.904e-05</v>
-      </c>
-      <c r="K99" s="22" t="n">
-        <v>6.757999999999999e-05</v>
-      </c>
-      <c r="L99" s="22" t="n">
-        <v>7.802000000000004e-05</v>
-      </c>
-      <c r="M99" s="22" t="n">
+      <c r="E103" s="22" t="n">
+        <v>4.522e-05</v>
+      </c>
+      <c r="F103" s="22" t="n">
+        <v>6.798000000000001e-05</v>
+      </c>
+      <c r="G103" s="22" t="n">
+        <v>6.654999999999999e-05</v>
+      </c>
+      <c r="H103" s="22" t="n">
+        <v>5.563999999999999e-05</v>
+      </c>
+      <c r="I103" s="22" t="n">
+        <v>5.909000000000001e-05</v>
+      </c>
+      <c r="J103" s="22" t="n">
+        <v>5.903999999999999e-05</v>
+      </c>
+      <c r="K103" s="22" t="n">
+        <v>6.756999999999999e-05</v>
+      </c>
+      <c r="L103" s="22" t="n">
+        <v>7.803000000000002e-05</v>
+      </c>
+      <c r="M103" s="22" t="n">
         <v>7.012999999999999e-05</v>
       </c>
-      <c r="N99" s="22" t="n">
+      <c r="N103" s="22" t="n">
         <v>7.069e-05</v>
       </c>
-      <c r="T99" s="22" t="n">
-        <v>6.007999999999999e-05</v>
-      </c>
-      <c r="U99" s="22" t="n">
-        <v>6.228000000000001e-05</v>
-      </c>
-      <c r="V99" s="22" t="n">
+      <c r="T103" s="22" t="n">
+        <v>6.011999999999999e-05</v>
+      </c>
+      <c r="U103" s="22" t="n">
+        <v>6.228999999999999e-05</v>
+      </c>
+      <c r="V103" s="22" t="n">
         <v>5.543000000000001e-05</v>
       </c>
-      <c r="W99" s="22" t="n">
-        <v>5.564000000000002e-05</v>
-      </c>
-      <c r="X99" s="22" t="n">
-        <v>7.802000000000004e-05</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="18" t="inlineStr">
-        <is>
-          <t>포괄손익 · 전 항목</t>
-        </is>
-      </c>
-      <c r="B101" s="44" t="inlineStr">
-        <is>
-          <t>분기 = 3개월 단독</t>
-        </is>
-      </c>
-      <c r="C101" s="18" t="n"/>
-      <c r="D101" s="18" t="n"/>
-      <c r="E101" s="18" t="n"/>
-      <c r="F101" s="18" t="n"/>
-      <c r="G101" s="18" t="n"/>
-      <c r="H101" s="18" t="n"/>
-      <c r="I101" s="18" t="n"/>
-      <c r="J101" s="18" t="n"/>
-      <c r="K101" s="18" t="n"/>
-      <c r="L101" s="18" t="n"/>
-      <c r="M101" s="18" t="n"/>
-      <c r="N101" s="18" t="n"/>
-      <c r="O101" s="18" t="n"/>
-      <c r="P101" s="18" t="n"/>
-      <c r="Q101" s="18" t="n"/>
-      <c r="R101" s="18" t="n"/>
-      <c r="S101" s="18" t="n"/>
-      <c r="T101" s="18" t="n"/>
-      <c r="U101" s="18" t="n"/>
-      <c r="V101" s="18" t="n"/>
-      <c r="W101" s="18" t="n"/>
-      <c r="X101" s="18" t="n"/>
-      <c r="Y101" s="18" t="n"/>
-      <c r="Z101" s="18" t="n"/>
-      <c r="AA101" s="18" t="n"/>
-      <c r="AB101" s="18" t="n"/>
-      <c r="AC101" s="18" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B102" s="5" t="inlineStr">
-        <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="C102" s="5" t="inlineStr">
-        <is>
-          <t>2023.3Q</t>
-        </is>
-      </c>
-      <c r="D102" s="5" t="inlineStr">
-        <is>
-          <t>2023.4Q</t>
-        </is>
-      </c>
-      <c r="E102" s="5" t="inlineStr">
-        <is>
-          <t>2024.1Q</t>
-        </is>
-      </c>
-      <c r="F102" s="5" t="inlineStr">
-        <is>
-          <t>2024.2Q</t>
-        </is>
-      </c>
-      <c r="G102" s="5" t="inlineStr">
-        <is>
-          <t>2024.3Q</t>
-        </is>
-      </c>
-      <c r="H102" s="5" t="inlineStr">
-        <is>
-          <t>2024.4Q</t>
-        </is>
-      </c>
-      <c r="I102" s="5" t="inlineStr">
-        <is>
-          <t>2025.1Q</t>
-        </is>
-      </c>
-      <c r="J102" s="5" t="inlineStr">
-        <is>
-          <t>2025.2Q</t>
-        </is>
-      </c>
-      <c r="K102" s="5" t="inlineStr">
-        <is>
-          <t>2025.3Q</t>
-        </is>
-      </c>
-      <c r="L102" s="5" t="inlineStr">
-        <is>
-          <t>2025.4Q</t>
-        </is>
-      </c>
-      <c r="M102" s="5" t="inlineStr">
-        <is>
-          <t>2026.1Q</t>
-        </is>
-      </c>
-      <c r="N102" s="5" t="inlineStr">
-        <is>
-          <t>2026.2Q</t>
-        </is>
-      </c>
-      <c r="O102" s="5" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="P102" s="5" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="Q102" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="R102" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="S102" s="5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="T102" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="U102" s="5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="V102" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="W102" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="X102" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="Y102" s="5" t="inlineStr">
-        <is>
-          <t>2026(MW)</t>
-        </is>
-      </c>
-      <c r="Z102" s="5" t="inlineStr">
-        <is>
-          <t>2027(MW)</t>
-        </is>
-      </c>
-      <c r="AA102" s="5" t="inlineStr">
-        <is>
-          <t>2028(MW)</t>
-        </is>
-      </c>
-      <c r="AB102" s="5" t="inlineStr">
-        <is>
-          <t>2029(MW)</t>
-        </is>
-      </c>
-      <c r="AC102" s="5" t="inlineStr">
-        <is>
-          <t>2030(MW)</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="9" t="inlineStr">
-        <is>
-          <t>중간이익</t>
-        </is>
-      </c>
-      <c r="C103" s="12" t="n">
-        <v>77573</v>
-      </c>
-      <c r="D103" s="12" t="n">
-        <v>91206</v>
-      </c>
-      <c r="E103" s="12" t="n">
-        <v>74401</v>
-      </c>
-      <c r="F103" s="12" t="n">
-        <v>111861</v>
-      </c>
-      <c r="G103" s="12" t="n">
-        <v>109496</v>
-      </c>
-      <c r="H103" s="12" t="n">
-        <v>91559</v>
-      </c>
-      <c r="I103" s="12" t="n">
-        <v>97234</v>
-      </c>
-      <c r="J103" s="12" t="n">
-        <v>97155</v>
-      </c>
-      <c r="K103" s="12" t="n">
-        <v>111213</v>
-      </c>
-      <c r="L103" s="12" t="n">
-        <v>128410</v>
-      </c>
-      <c r="M103" s="12" t="n">
-        <v>115418</v>
-      </c>
-      <c r="N103" s="12" t="n">
-        <v>116331</v>
-      </c>
-      <c r="T103" s="12" t="n">
-        <v>98841</v>
-      </c>
-      <c r="U103" s="12" t="n">
-        <v>102479</v>
-      </c>
-      <c r="V103" s="12" t="n">
-        <v>91206</v>
-      </c>
-      <c r="W103" s="12" t="n">
-        <v>91559</v>
-      </c>
-      <c r="X103" s="12" t="n">
-        <v>128410</v>
+      <c r="W103" s="22" t="n">
+        <v>5.563999999999999e-05</v>
+      </c>
+      <c r="X103" s="22" t="n">
+        <v>7.803000000000002e-05</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="20" t="inlineStr">
         <is>
-          <t>확정급여제도 재측정</t>
+          <t>희석 주당 중간이익(엔)</t>
         </is>
       </c>
       <c r="C104" s="22" t="n">
-        <v>0</v>
+        <v>4.714e-05</v>
       </c>
       <c r="D104" s="22" t="n">
-        <v>2055</v>
+        <v>5.543000000000001e-05</v>
       </c>
       <c r="E104" s="22" t="n">
-        <v>0</v>
+        <v>4.521e-05</v>
       </c>
       <c r="F104" s="22" t="n">
-        <v>37</v>
+        <v>6.798e-05</v>
       </c>
       <c r="G104" s="22" t="n">
-        <v>0</v>
+        <v>6.653e-05</v>
       </c>
       <c r="H104" s="22" t="n">
-        <v>4133</v>
+        <v>5.564000000000002e-05</v>
       </c>
       <c r="I104" s="22" t="n">
-        <v>-12</v>
+        <v>5.908e-05</v>
       </c>
       <c r="J104" s="22" t="n">
-        <v>0</v>
+        <v>5.904e-05</v>
       </c>
       <c r="K104" s="22" t="n">
-        <v>0</v>
+        <v>6.757999999999999e-05</v>
       </c>
       <c r="L104" s="22" t="n">
-        <v>8615</v>
+        <v>7.802000000000004e-05</v>
       </c>
       <c r="M104" s="22" t="n">
-        <v>0</v>
+        <v>7.012999999999999e-05</v>
       </c>
       <c r="N104" s="22" t="n">
-        <v>0</v>
+        <v>7.069e-05</v>
+      </c>
+      <c r="T104" s="22" t="n">
+        <v>6.007999999999999e-05</v>
+      </c>
+      <c r="U104" s="22" t="n">
+        <v>6.228000000000001e-05</v>
       </c>
       <c r="V104" s="22" t="n">
-        <v>2055</v>
+        <v>5.543000000000001e-05</v>
       </c>
       <c r="W104" s="22" t="n">
-        <v>4133</v>
+        <v>5.564000000000002e-05</v>
       </c>
       <c r="X104" s="22" t="n">
-        <v>8615</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="20" t="inlineStr">
-        <is>
-          <t>기타포괄손익-공정가치 측정 금융자산</t>
-        </is>
-      </c>
-      <c r="C105" s="22" t="n">
-        <v>-12</v>
-      </c>
-      <c r="D105" s="22" t="n">
-        <v>-10</v>
-      </c>
-      <c r="E105" s="22" t="n">
-        <v>-48</v>
-      </c>
-      <c r="F105" s="22" t="n">
-        <v>26</v>
-      </c>
-      <c r="G105" s="22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H105" s="22" t="n">
-        <v>-307</v>
-      </c>
-      <c r="I105" s="22" t="n">
-        <v>20</v>
-      </c>
-      <c r="J105" s="22" t="n">
-        <v>45</v>
-      </c>
-      <c r="K105" s="22" t="n">
-        <v>-10</v>
-      </c>
-      <c r="L105" s="22" t="n">
-        <v>158</v>
-      </c>
-      <c r="M105" s="22" t="n">
-        <v>-126</v>
-      </c>
-      <c r="N105" s="22" t="n">
-        <v>15</v>
-      </c>
-      <c r="T105" s="22" t="n">
-        <v>-181</v>
-      </c>
-      <c r="U105" s="22" t="n">
-        <v>11</v>
-      </c>
-      <c r="V105" s="22" t="n">
-        <v>-10</v>
-      </c>
-      <c r="W105" s="22" t="n">
-        <v>-307</v>
-      </c>
-      <c r="X105" s="22" t="n">
-        <v>158</v>
+        <v>7.802000000000004e-05</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="20" t="inlineStr">
-        <is>
-          <t>당기손익으로 재분류되지 않는 항목 합계</t>
-        </is>
-      </c>
-      <c r="C106" s="22" t="n">
-        <v>-12</v>
-      </c>
-      <c r="D106" s="22" t="n">
-        <v>2044</v>
-      </c>
-      <c r="E106" s="22" t="n">
-        <v>-48</v>
-      </c>
-      <c r="F106" s="22" t="n">
-        <v>63</v>
-      </c>
-      <c r="G106" s="22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H106" s="22" t="n">
-        <v>3826</v>
-      </c>
-      <c r="I106" s="22" t="n">
-        <v>9</v>
-      </c>
-      <c r="J106" s="22" t="n">
-        <v>45</v>
-      </c>
-      <c r="K106" s="22" t="n">
-        <v>-10</v>
-      </c>
-      <c r="L106" s="22" t="n">
-        <v>8772</v>
-      </c>
-      <c r="M106" s="22" t="n">
-        <v>-126</v>
-      </c>
-      <c r="N106" s="22" t="n">
-        <v>15</v>
-      </c>
-      <c r="T106" s="22" t="n">
-        <v>402</v>
-      </c>
-      <c r="U106" s="22" t="n">
-        <v>3032</v>
-      </c>
-      <c r="V106" s="22" t="n">
-        <v>2044</v>
-      </c>
-      <c r="W106" s="22" t="n">
-        <v>3826</v>
-      </c>
-      <c r="X106" s="22" t="n">
-        <v>8772</v>
-      </c>
+      <c r="A106" s="18" t="inlineStr">
+        <is>
+          <t>포괄손익 · 전 항목</t>
+        </is>
+      </c>
+      <c r="B106" s="44" t="inlineStr">
+        <is>
+          <t>분기 = 3개월 단독</t>
+        </is>
+      </c>
+      <c r="C106" s="18" t="n"/>
+      <c r="D106" s="18" t="n"/>
+      <c r="E106" s="18" t="n"/>
+      <c r="F106" s="18" t="n"/>
+      <c r="G106" s="18" t="n"/>
+      <c r="H106" s="18" t="n"/>
+      <c r="I106" s="18" t="n"/>
+      <c r="J106" s="18" t="n"/>
+      <c r="K106" s="18" t="n"/>
+      <c r="L106" s="18" t="n"/>
+      <c r="M106" s="18" t="n"/>
+      <c r="N106" s="18" t="n"/>
+      <c r="O106" s="18" t="n"/>
+      <c r="P106" s="18" t="n"/>
+      <c r="Q106" s="18" t="n"/>
+      <c r="R106" s="18" t="n"/>
+      <c r="S106" s="18" t="n"/>
+      <c r="T106" s="18" t="n"/>
+      <c r="U106" s="18" t="n"/>
+      <c r="V106" s="18" t="n"/>
+      <c r="W106" s="18" t="n"/>
+      <c r="X106" s="18" t="n"/>
+      <c r="Y106" s="18" t="n"/>
+      <c r="Z106" s="18" t="n"/>
+      <c r="AA106" s="18" t="n"/>
+      <c r="AB106" s="18" t="n"/>
+      <c r="AC106" s="18" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="20" t="inlineStr">
-        <is>
-          <t>기타포괄손익-공정가치 측정 금융자산</t>
-        </is>
-      </c>
-      <c r="C107" s="22" t="n">
-        <v>-2</v>
-      </c>
-      <c r="D107" s="22" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E107" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F107" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="G107" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H107" s="22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I107" s="22" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J107" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K107" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="L107" s="22" t="n">
-        <v>-5</v>
-      </c>
-      <c r="M107" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="N107" s="22" t="n">
-        <v>-3</v>
-      </c>
-      <c r="T107" s="22" t="n">
-        <v>-3</v>
-      </c>
-      <c r="U107" s="22" t="n">
-        <v>-3</v>
-      </c>
-      <c r="V107" s="22" t="n">
-        <v>-2</v>
-      </c>
-      <c r="W107" s="22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X107" s="22" t="n">
-        <v>-5</v>
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>2023.3Q</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>2023.4Q</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>2024.1Q</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>2024.2Q</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>2024.3Q</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>2024.4Q</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>2025.1Q</t>
+        </is>
+      </c>
+      <c r="J107" s="5" t="inlineStr">
+        <is>
+          <t>2025.2Q</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="inlineStr">
+        <is>
+          <t>2025.3Q</t>
+        </is>
+      </c>
+      <c r="L107" s="5" t="inlineStr">
+        <is>
+          <t>2025.4Q</t>
+        </is>
+      </c>
+      <c r="M107" s="5" t="inlineStr">
+        <is>
+          <t>2026.1Q</t>
+        </is>
+      </c>
+      <c r="N107" s="5" t="inlineStr">
+        <is>
+          <t>2026.2Q</t>
+        </is>
+      </c>
+      <c r="O107" s="5" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="P107" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q107" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="R107" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="S107" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="T107" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="U107" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="V107" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="W107" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="X107" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Y107" s="5" t="inlineStr">
+        <is>
+          <t>2026(MW)</t>
+        </is>
+      </c>
+      <c r="Z107" s="5" t="inlineStr">
+        <is>
+          <t>2027(MW)</t>
+        </is>
+      </c>
+      <c r="AA107" s="5" t="inlineStr">
+        <is>
+          <t>2028(MW)</t>
+        </is>
+      </c>
+      <c r="AB107" s="5" t="inlineStr">
+        <is>
+          <t>2029(MW)</t>
+        </is>
+      </c>
+      <c r="AC107" s="5" t="inlineStr">
+        <is>
+          <t>2030(MW)</t>
+        </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="20" t="inlineStr">
-        <is>
-          <t>현금흐름 위험회피</t>
-        </is>
-      </c>
-      <c r="C108" s="22" t="n">
-        <v>9305</v>
-      </c>
-      <c r="D108" s="22" t="n">
-        <v>-1752</v>
-      </c>
-      <c r="E108" s="22" t="n">
-        <v>3854</v>
-      </c>
-      <c r="F108" s="22" t="n">
-        <v>-7392</v>
-      </c>
-      <c r="G108" s="22" t="n">
-        <v>15275</v>
-      </c>
-      <c r="H108" s="22" t="n">
-        <v>1169</v>
-      </c>
-      <c r="I108" s="22" t="n">
-        <v>3660</v>
-      </c>
-      <c r="J108" s="22" t="n">
-        <v>-23022</v>
-      </c>
-      <c r="K108" s="22" t="n">
-        <v>-3008</v>
-      </c>
-      <c r="L108" s="22" t="n">
-        <v>-7471</v>
-      </c>
-      <c r="M108" s="22" t="n">
-        <v>8171</v>
-      </c>
-      <c r="N108" s="22" t="n">
-        <v>5768</v>
-      </c>
-      <c r="T108" s="22" t="n">
-        <v>-2836</v>
-      </c>
-      <c r="U108" s="22" t="n">
-        <v>11271</v>
-      </c>
-      <c r="V108" s="22" t="n">
-        <v>-1752</v>
-      </c>
-      <c r="W108" s="22" t="n">
-        <v>1169</v>
-      </c>
-      <c r="X108" s="22" t="n">
-        <v>-7471</v>
+      <c r="A108" s="9" t="inlineStr">
+        <is>
+          <t>중간이익</t>
+        </is>
+      </c>
+      <c r="C108" s="12" t="n">
+        <v>77573</v>
+      </c>
+      <c r="D108" s="12" t="n">
+        <v>91206</v>
+      </c>
+      <c r="E108" s="12" t="n">
+        <v>74401</v>
+      </c>
+      <c r="F108" s="12" t="n">
+        <v>111861</v>
+      </c>
+      <c r="G108" s="12" t="n">
+        <v>109496</v>
+      </c>
+      <c r="H108" s="12" t="n">
+        <v>91559</v>
+      </c>
+      <c r="I108" s="12" t="n">
+        <v>97234</v>
+      </c>
+      <c r="J108" s="12" t="n">
+        <v>97155</v>
+      </c>
+      <c r="K108" s="12" t="n">
+        <v>111213</v>
+      </c>
+      <c r="L108" s="12" t="n">
+        <v>128410</v>
+      </c>
+      <c r="M108" s="12" t="n">
+        <v>115418</v>
+      </c>
+      <c r="N108" s="12" t="n">
+        <v>116331</v>
+      </c>
+      <c r="T108" s="12" t="n">
+        <v>98841</v>
+      </c>
+      <c r="U108" s="12" t="n">
+        <v>102479</v>
+      </c>
+      <c r="V108" s="12" t="n">
+        <v>91206</v>
+      </c>
+      <c r="W108" s="12" t="n">
+        <v>91559</v>
+      </c>
+      <c r="X108" s="12" t="n">
+        <v>128410</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="20" t="inlineStr">
         <is>
-          <t>해외 종속기업 등 외화환산차이</t>
+          <t>확정급여제도 재측정</t>
         </is>
       </c>
       <c r="C109" s="22" t="n">
-        <v>513</v>
+        <v>0</v>
       </c>
       <c r="D109" s="22" t="n">
-        <v>-1050</v>
+        <v>2055</v>
       </c>
       <c r="E109" s="22" t="n">
-        <v>3907</v>
+        <v>0</v>
       </c>
       <c r="F109" s="22" t="n">
-        <v>4995</v>
+        <v>37</v>
       </c>
       <c r="G109" s="22" t="n">
-        <v>-7780</v>
+        <v>0</v>
       </c>
       <c r="H109" s="22" t="n">
-        <v>3465</v>
+        <v>4133</v>
       </c>
       <c r="I109" s="22" t="n">
-        <v>-1629</v>
+        <v>-12</v>
       </c>
       <c r="J109" s="22" t="n">
-        <v>3596</v>
+        <v>0</v>
       </c>
       <c r="K109" s="22" t="n">
-        <v>2378</v>
+        <v>0</v>
       </c>
       <c r="L109" s="22" t="n">
-        <v>5792</v>
+        <v>8615</v>
       </c>
       <c r="M109" s="22" t="n">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="N109" s="22" t="n">
-        <v>1635</v>
-      </c>
-      <c r="T109" s="22" t="n">
-        <v>825</v>
-      </c>
-      <c r="U109" s="22" t="n">
-        <v>-1092</v>
+        <v>0</v>
       </c>
       <c r="V109" s="22" t="n">
-        <v>-1050</v>
+        <v>2055</v>
       </c>
       <c r="W109" s="22" t="n">
-        <v>3465</v>
+        <v>4133</v>
       </c>
       <c r="X109" s="22" t="n">
-        <v>5792</v>
+        <v>8615</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="20" t="inlineStr">
         <is>
-          <t>후에 당기손익으로 재분류될 수 있는 항목 합계</t>
+          <t>기타포괄손익-공정가치 측정 금융자산</t>
         </is>
       </c>
       <c r="C110" s="22" t="n">
-        <v>9818</v>
+        <v>-12</v>
       </c>
       <c r="D110" s="22" t="n">
-        <v>-2805</v>
+        <v>-10</v>
       </c>
       <c r="E110" s="22" t="n">
-        <v>7761</v>
+        <v>-48</v>
       </c>
       <c r="F110" s="22" t="n">
-        <v>-2392</v>
+        <v>26</v>
       </c>
       <c r="G110" s="22" t="n">
-        <v>7495</v>
+        <v>-1</v>
       </c>
       <c r="H110" s="22" t="n">
-        <v>4635</v>
+        <v>-307</v>
       </c>
       <c r="I110" s="22" t="n">
-        <v>2028</v>
+        <v>20</v>
       </c>
       <c r="J110" s="22" t="n">
-        <v>-19423</v>
+        <v>45</v>
       </c>
       <c r="K110" s="22" t="n">
-        <v>-628</v>
+        <v>-10</v>
       </c>
       <c r="L110" s="22" t="n">
-        <v>-1684</v>
+        <v>158</v>
       </c>
       <c r="M110" s="22" t="n">
-        <v>8430</v>
+        <v>-126</v>
       </c>
       <c r="N110" s="22" t="n">
-        <v>7400</v>
+        <v>15</v>
       </c>
       <c r="T110" s="22" t="n">
-        <v>-2014</v>
+        <v>-181</v>
       </c>
       <c r="U110" s="22" t="n">
-        <v>10174</v>
+        <v>11</v>
       </c>
       <c r="V110" s="22" t="n">
-        <v>-2805</v>
+        <v>-10</v>
       </c>
       <c r="W110" s="22" t="n">
-        <v>4635</v>
+        <v>-307</v>
       </c>
       <c r="X110" s="22" t="n">
-        <v>-1684</v>
+        <v>158</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="20" t="inlineStr">
         <is>
+          <t>당기손익으로 재분류되지 않는 항목 합계</t>
+        </is>
+      </c>
+      <c r="C111" s="22" t="n">
+        <v>-12</v>
+      </c>
+      <c r="D111" s="22" t="n">
+        <v>2044</v>
+      </c>
+      <c r="E111" s="22" t="n">
+        <v>-48</v>
+      </c>
+      <c r="F111" s="22" t="n">
+        <v>63</v>
+      </c>
+      <c r="G111" s="22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H111" s="22" t="n">
+        <v>3826</v>
+      </c>
+      <c r="I111" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="J111" s="22" t="n">
+        <v>45</v>
+      </c>
+      <c r="K111" s="22" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L111" s="22" t="n">
+        <v>8772</v>
+      </c>
+      <c r="M111" s="22" t="n">
+        <v>-126</v>
+      </c>
+      <c r="N111" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T111" s="22" t="n">
+        <v>402</v>
+      </c>
+      <c r="U111" s="22" t="n">
+        <v>3032</v>
+      </c>
+      <c r="V111" s="22" t="n">
+        <v>2044</v>
+      </c>
+      <c r="W111" s="22" t="n">
+        <v>3826</v>
+      </c>
+      <c r="X111" s="22" t="n">
+        <v>8772</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="20" t="inlineStr">
+        <is>
+          <t>기타포괄손익-공정가치 측정 금융자산</t>
+        </is>
+      </c>
+      <c r="C112" s="22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D112" s="22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E112" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="G112" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" s="22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I112" s="22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J112" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K112" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L112" s="22" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M112" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N112" s="22" t="n">
+        <v>-3</v>
+      </c>
+      <c r="T112" s="22" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U112" s="22" t="n">
+        <v>-3</v>
+      </c>
+      <c r="V112" s="22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W112" s="22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X112" s="22" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="20" t="inlineStr">
+        <is>
+          <t>현금흐름 위험회피</t>
+        </is>
+      </c>
+      <c r="C113" s="22" t="n">
+        <v>9305</v>
+      </c>
+      <c r="D113" s="22" t="n">
+        <v>-1752</v>
+      </c>
+      <c r="E113" s="22" t="n">
+        <v>3854</v>
+      </c>
+      <c r="F113" s="22" t="n">
+        <v>-7392</v>
+      </c>
+      <c r="G113" s="22" t="n">
+        <v>15275</v>
+      </c>
+      <c r="H113" s="22" t="n">
+        <v>1169</v>
+      </c>
+      <c r="I113" s="22" t="n">
+        <v>3660</v>
+      </c>
+      <c r="J113" s="22" t="n">
+        <v>-23022</v>
+      </c>
+      <c r="K113" s="22" t="n">
+        <v>-3008</v>
+      </c>
+      <c r="L113" s="22" t="n">
+        <v>-7471</v>
+      </c>
+      <c r="M113" s="22" t="n">
+        <v>8171</v>
+      </c>
+      <c r="N113" s="22" t="n">
+        <v>5768</v>
+      </c>
+      <c r="T113" s="22" t="n">
+        <v>-2836</v>
+      </c>
+      <c r="U113" s="22" t="n">
+        <v>11271</v>
+      </c>
+      <c r="V113" s="22" t="n">
+        <v>-1752</v>
+      </c>
+      <c r="W113" s="22" t="n">
+        <v>1169</v>
+      </c>
+      <c r="X113" s="22" t="n">
+        <v>-7471</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="20" t="inlineStr">
+        <is>
+          <t>해외 종속기업 등 외화환산차이</t>
+        </is>
+      </c>
+      <c r="C114" s="22" t="n">
+        <v>513</v>
+      </c>
+      <c r="D114" s="22" t="n">
+        <v>-1050</v>
+      </c>
+      <c r="E114" s="22" t="n">
+        <v>3907</v>
+      </c>
+      <c r="F114" s="22" t="n">
+        <v>4995</v>
+      </c>
+      <c r="G114" s="22" t="n">
+        <v>-7780</v>
+      </c>
+      <c r="H114" s="22" t="n">
+        <v>3465</v>
+      </c>
+      <c r="I114" s="22" t="n">
+        <v>-1629</v>
+      </c>
+      <c r="J114" s="22" t="n">
+        <v>3596</v>
+      </c>
+      <c r="K114" s="22" t="n">
+        <v>2378</v>
+      </c>
+      <c r="L114" s="22" t="n">
+        <v>5792</v>
+      </c>
+      <c r="M114" s="22" t="n">
+        <v>254</v>
+      </c>
+      <c r="N114" s="22" t="n">
+        <v>1635</v>
+      </c>
+      <c r="T114" s="22" t="n">
+        <v>825</v>
+      </c>
+      <c r="U114" s="22" t="n">
+        <v>-1092</v>
+      </c>
+      <c r="V114" s="22" t="n">
+        <v>-1050</v>
+      </c>
+      <c r="W114" s="22" t="n">
+        <v>3465</v>
+      </c>
+      <c r="X114" s="22" t="n">
+        <v>5792</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="20" t="inlineStr">
+        <is>
+          <t>후에 당기손익으로 재분류될 수 있는 항목 합계</t>
+        </is>
+      </c>
+      <c r="C115" s="22" t="n">
+        <v>9818</v>
+      </c>
+      <c r="D115" s="22" t="n">
+        <v>-2805</v>
+      </c>
+      <c r="E115" s="22" t="n">
+        <v>7761</v>
+      </c>
+      <c r="F115" s="22" t="n">
+        <v>-2392</v>
+      </c>
+      <c r="G115" s="22" t="n">
+        <v>7495</v>
+      </c>
+      <c r="H115" s="22" t="n">
+        <v>4635</v>
+      </c>
+      <c r="I115" s="22" t="n">
+        <v>2028</v>
+      </c>
+      <c r="J115" s="22" t="n">
+        <v>-19423</v>
+      </c>
+      <c r="K115" s="22" t="n">
+        <v>-628</v>
+      </c>
+      <c r="L115" s="22" t="n">
+        <v>-1684</v>
+      </c>
+      <c r="M115" s="22" t="n">
+        <v>8430</v>
+      </c>
+      <c r="N115" s="22" t="n">
+        <v>7400</v>
+      </c>
+      <c r="T115" s="22" t="n">
+        <v>-2014</v>
+      </c>
+      <c r="U115" s="22" t="n">
+        <v>10174</v>
+      </c>
+      <c r="V115" s="22" t="n">
+        <v>-2805</v>
+      </c>
+      <c r="W115" s="22" t="n">
+        <v>4635</v>
+      </c>
+      <c r="X115" s="22" t="n">
+        <v>-1684</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="20" t="inlineStr">
+        <is>
           <t>기타포괄손익 합계</t>
         </is>
       </c>
-      <c r="C111" s="22" t="n">
+      <c r="C116" s="22" t="n">
         <v>9806</v>
       </c>
-      <c r="D111" s="22" t="n">
+      <c r="D116" s="22" t="n">
         <v>-761</v>
       </c>
-      <c r="E111" s="22" t="n">
+      <c r="E116" s="22" t="n">
         <v>7712</v>
       </c>
-      <c r="F111" s="22" t="n">
+      <c r="F116" s="22" t="n">
         <v>-2328</v>
       </c>
-      <c r="G111" s="22" t="n">
+      <c r="G116" s="22" t="n">
         <v>7494</v>
       </c>
-      <c r="H111" s="22" t="n">
+      <c r="H116" s="22" t="n">
         <v>8460</v>
       </c>
-      <c r="I111" s="22" t="n">
+      <c r="I116" s="22" t="n">
         <v>2037</v>
       </c>
-      <c r="J111" s="22" t="n">
+      <c r="J116" s="22" t="n">
         <v>-19378</v>
       </c>
-      <c r="K111" s="22" t="n">
+      <c r="K116" s="22" t="n">
         <v>-638</v>
       </c>
-      <c r="L111" s="22" t="n">
+      <c r="L116" s="22" t="n">
         <v>7088</v>
       </c>
-      <c r="M111" s="22" t="n">
+      <c r="M116" s="22" t="n">
         <v>8305</v>
       </c>
-      <c r="N111" s="22" t="n">
+      <c r="N116" s="22" t="n">
         <v>7413</v>
       </c>
-      <c r="T111" s="22" t="n">
+      <c r="T116" s="22" t="n">
         <v>-1612</v>
       </c>
-      <c r="U111" s="22" t="n">
+      <c r="U116" s="22" t="n">
         <v>13206</v>
       </c>
-      <c r="V111" s="22" t="n">
+      <c r="V116" s="22" t="n">
         <v>-761</v>
       </c>
-      <c r="W111" s="22" t="n">
+      <c r="W116" s="22" t="n">
         <v>8460</v>
       </c>
-      <c r="X111" s="22" t="n">
+      <c r="X116" s="22" t="n">
         <v>7088</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="9" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="9" t="inlineStr">
         <is>
           <t>포괄이익</t>
         </is>
       </c>
-      <c r="C112" s="12" t="n">
+      <c r="C117" s="12" t="n">
         <v>87378</v>
       </c>
-      <c r="D112" s="12" t="n">
+      <c r="D117" s="12" t="n">
         <v>90446</v>
       </c>
-      <c r="E112" s="12" t="n">
+      <c r="E117" s="12" t="n">
         <v>82114</v>
       </c>
-      <c r="F112" s="12" t="n">
+      <c r="F117" s="12" t="n">
         <v>109531</v>
       </c>
-      <c r="G112" s="12" t="n">
+      <c r="G117" s="12" t="n">
         <v>116991</v>
       </c>
-      <c r="H112" s="12" t="n">
+      <c r="H117" s="12" t="n">
         <v>100019</v>
       </c>
-      <c r="I112" s="12" t="n">
+      <c r="I117" s="12" t="n">
         <v>99271</v>
       </c>
-      <c r="J112" s="12" t="n">
+      <c r="J117" s="12" t="n">
         <v>77776</v>
       </c>
-      <c r="K112" s="12" t="n">
+      <c r="K117" s="12" t="n">
         <v>110576</v>
       </c>
-      <c r="L112" s="12" t="n">
+      <c r="L117" s="12" t="n">
         <v>135499</v>
       </c>
-      <c r="M112" s="12" t="n">
+      <c r="M117" s="12" t="n">
         <v>123723</v>
       </c>
-      <c r="N112" s="12" t="n">
+      <c r="N117" s="12" t="n">
         <v>123744</v>
       </c>
-      <c r="T112" s="12" t="n">
+      <c r="T117" s="12" t="n">
         <v>97229</v>
       </c>
-      <c r="U112" s="12" t="n">
+      <c r="U117" s="12" t="n">
         <v>115685</v>
       </c>
-      <c r="V112" s="12" t="n">
+      <c r="V117" s="12" t="n">
         <v>90446</v>
       </c>
-      <c r="W112" s="12" t="n">
+      <c r="W117" s="12" t="n">
         <v>100019</v>
       </c>
-      <c r="X112" s="12" t="n">
+      <c r="X117" s="12" t="n">
         <v>135499</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="9" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="9" t="inlineStr">
         <is>
           <t>지배기업 소유주 지분</t>
         </is>
       </c>
-      <c r="C113" s="12" t="n">
+      <c r="C118" s="12" t="n">
         <v>87378</v>
       </c>
-      <c r="D113" s="12" t="n">
+      <c r="D118" s="12" t="n">
         <v>90446</v>
       </c>
-      <c r="E113" s="12" t="n">
+      <c r="E118" s="12" t="n">
         <v>82114</v>
       </c>
-      <c r="F113" s="12" t="n">
+      <c r="F118" s="12" t="n">
         <v>109531</v>
       </c>
-      <c r="G113" s="12" t="n">
+      <c r="G118" s="12" t="n">
         <v>116991</v>
       </c>
-      <c r="H113" s="12" t="n">
+      <c r="H118" s="12" t="n">
         <v>100019</v>
       </c>
-      <c r="I113" s="12" t="n">
+      <c r="I118" s="12" t="n">
         <v>99271</v>
       </c>
-      <c r="J113" s="12" t="n">
+      <c r="J118" s="12" t="n">
         <v>77776</v>
       </c>
-      <c r="K113" s="12" t="n">
+      <c r="K118" s="12" t="n">
         <v>110576</v>
       </c>
-      <c r="L113" s="12" t="n">
+      <c r="L118" s="12" t="n">
         <v>135499</v>
       </c>
-      <c r="M113" s="12" t="n">
+      <c r="M118" s="12" t="n">
         <v>123723</v>
       </c>
-      <c r="N113" s="12" t="n">
+      <c r="N118" s="12" t="n">
         <v>123744</v>
       </c>
-      <c r="T113" s="12" t="n">
+      <c r="T118" s="12" t="n">
         <v>97229</v>
       </c>
-      <c r="U113" s="12" t="n">
+      <c r="U118" s="12" t="n">
         <v>115685</v>
       </c>
-      <c r="V113" s="12" t="n">
+      <c r="V118" s="12" t="n">
         <v>90446</v>
       </c>
-      <c r="W113" s="12" t="n">
+      <c r="W118" s="12" t="n">
         <v>100019</v>
       </c>
-      <c r="X113" s="12" t="n">
+      <c r="X118" s="12" t="n">
         <v>135499</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="18" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="18" t="inlineStr">
         <is>
           <t>현금흐름표 · 전 항목</t>
         </is>
       </c>
-      <c r="B115" s="44" t="inlineStr">
+      <c r="B120" s="44" t="inlineStr">
         <is>
           <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
         </is>
       </c>
-      <c r="C115" s="18" t="n"/>
-      <c r="D115" s="18" t="n"/>
-      <c r="E115" s="18" t="n"/>
-      <c r="F115" s="18" t="n"/>
-      <c r="G115" s="18" t="n"/>
-      <c r="H115" s="18" t="n"/>
-      <c r="I115" s="18" t="n"/>
-      <c r="J115" s="18" t="n"/>
-      <c r="K115" s="18" t="n"/>
-      <c r="L115" s="18" t="n"/>
-      <c r="M115" s="18" t="n"/>
-      <c r="N115" s="18" t="n"/>
-      <c r="O115" s="18" t="n"/>
-      <c r="P115" s="18" t="n"/>
-      <c r="Q115" s="18" t="n"/>
-      <c r="R115" s="18" t="n"/>
-      <c r="S115" s="18" t="n"/>
-      <c r="T115" s="18" t="n"/>
-      <c r="U115" s="18" t="n"/>
-      <c r="V115" s="18" t="n"/>
-      <c r="W115" s="18" t="n"/>
-      <c r="X115" s="18" t="n"/>
-      <c r="Y115" s="18" t="n"/>
-      <c r="Z115" s="18" t="n"/>
-      <c r="AA115" s="18" t="n"/>
-      <c r="AB115" s="18" t="n"/>
-      <c r="AC115" s="18" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="5" t="inlineStr">
+      <c r="C120" s="18" t="n"/>
+      <c r="D120" s="18" t="n"/>
+      <c r="E120" s="18" t="n"/>
+      <c r="F120" s="18" t="n"/>
+      <c r="G120" s="18" t="n"/>
+      <c r="H120" s="18" t="n"/>
+      <c r="I120" s="18" t="n"/>
+      <c r="J120" s="18" t="n"/>
+      <c r="K120" s="18" t="n"/>
+      <c r="L120" s="18" t="n"/>
+      <c r="M120" s="18" t="n"/>
+      <c r="N120" s="18" t="n"/>
+      <c r="O120" s="18" t="n"/>
+      <c r="P120" s="18" t="n"/>
+      <c r="Q120" s="18" t="n"/>
+      <c r="R120" s="18" t="n"/>
+      <c r="S120" s="18" t="n"/>
+      <c r="T120" s="18" t="n"/>
+      <c r="U120" s="18" t="n"/>
+      <c r="V120" s="18" t="n"/>
+      <c r="W120" s="18" t="n"/>
+      <c r="X120" s="18" t="n"/>
+      <c r="Y120" s="18" t="n"/>
+      <c r="Z120" s="18" t="n"/>
+      <c r="AA120" s="18" t="n"/>
+      <c r="AB120" s="18" t="n"/>
+      <c r="AC120" s="18" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B116" s="5" t="inlineStr">
+      <c r="B121" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C116" s="5" t="inlineStr">
+      <c r="C121" s="5" t="inlineStr">
         <is>
           <t>2023.3Q</t>
         </is>
       </c>
-      <c r="D116" s="5" t="inlineStr">
+      <c r="D121" s="5" t="inlineStr">
         <is>
           <t>2023.4Q</t>
         </is>
       </c>
-      <c r="E116" s="5" t="inlineStr">
+      <c r="E121" s="5" t="inlineStr">
         <is>
           <t>2024.1Q</t>
         </is>
       </c>
-      <c r="F116" s="5" t="inlineStr">
+      <c r="F121" s="5" t="inlineStr">
         <is>
           <t>2024.2Q</t>
         </is>
       </c>
-      <c r="G116" s="5" t="inlineStr">
+      <c r="G121" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="H116" s="5" t="inlineStr">
+      <c r="H121" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="I116" s="5" t="inlineStr">
+      <c r="I121" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="J116" s="5" t="inlineStr">
+      <c r="J121" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="K116" s="5" t="inlineStr">
+      <c r="K121" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="L116" s="5" t="inlineStr">
+      <c r="L121" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="M116" s="5" t="inlineStr">
+      <c r="M121" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="N116" s="5" t="inlineStr">
+      <c r="N121" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="O116" s="5" t="inlineStr">
+      <c r="O121" s="5" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="P116" s="5" t="inlineStr">
+      <c r="P121" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="Q116" s="5" t="inlineStr">
+      <c r="Q121" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="R116" s="5" t="inlineStr">
+      <c r="R121" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="S116" s="5" t="inlineStr">
+      <c r="S121" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="T116" s="5" t="inlineStr">
+      <c r="T121" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="U116" s="5" t="inlineStr">
+      <c r="U121" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="V116" s="5" t="inlineStr">
+      <c r="V121" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="W116" s="5" t="inlineStr">
+      <c r="W121" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="X116" s="5" t="inlineStr">
+      <c r="X121" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="Y116" s="5" t="inlineStr">
+      <c r="Y121" s="5" t="inlineStr">
         <is>
           <t>2026(MW)</t>
         </is>
       </c>
-      <c r="Z116" s="5" t="inlineStr">
+      <c r="Z121" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="AA116" s="5" t="inlineStr">
+      <c r="AA121" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AB116" s="5" t="inlineStr">
+      <c r="AB121" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AC116" s="5" t="inlineStr">
+      <c r="AC121" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="20" t="inlineStr">
-        <is>
-          <t>영업활동 현금창출</t>
-        </is>
-      </c>
-      <c r="C117" s="22" t="n">
-        <v>345003</v>
-      </c>
-      <c r="D117" s="22" t="n">
-        <v>462722</v>
-      </c>
-      <c r="E117" s="22" t="n">
-        <v>110138</v>
-      </c>
-      <c r="F117" s="22" t="n">
-        <v>278669</v>
-      </c>
-      <c r="G117" s="22" t="n">
-        <v>448943</v>
-      </c>
-      <c r="H117" s="22" t="n">
-        <v>589546</v>
-      </c>
-      <c r="I117" s="22" t="n">
-        <v>147337</v>
-      </c>
-      <c r="J117" s="22" t="n">
-        <v>286336</v>
-      </c>
-      <c r="K117" s="22" t="n">
-        <v>471417</v>
-      </c>
-      <c r="L117" s="22" t="n">
-        <v>650935</v>
-      </c>
-      <c r="M117" s="22" t="n">
-        <v>170935</v>
-      </c>
-      <c r="N117" s="22" t="n">
-        <v>341970</v>
-      </c>
-      <c r="Q117" s="22" t="n">
-        <v>151857</v>
-      </c>
-      <c r="R117" s="22" t="n">
-        <v>249500</v>
-      </c>
-      <c r="S117" s="22" t="n">
-        <v>340228</v>
-      </c>
-      <c r="T117" s="22" t="n">
-        <v>470367</v>
-      </c>
-      <c r="U117" s="22" t="n">
-        <v>575345</v>
-      </c>
-      <c r="V117" s="22" t="n">
-        <v>462722</v>
-      </c>
-      <c r="W117" s="22" t="n">
-        <v>589546</v>
-      </c>
-      <c r="X117" s="22" t="n">
-        <v>650935</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="20" t="inlineStr">
-        <is>
-          <t>운전자본 감소</t>
-        </is>
-      </c>
-      <c r="C118" s="22" t="n">
-        <v>117878</v>
-      </c>
-      <c r="D118" s="22" t="n">
-        <v>130634</v>
-      </c>
-      <c r="E118" s="22" t="n">
-        <v>44108</v>
-      </c>
-      <c r="F118" s="22" t="n">
-        <v>-66963</v>
-      </c>
-      <c r="G118" s="22" t="n">
-        <v>-38011</v>
-      </c>
-      <c r="H118" s="22" t="n">
-        <v>-28843</v>
-      </c>
-      <c r="I118" s="22" t="n">
-        <v>40756</v>
-      </c>
-      <c r="J118" s="22" t="n">
-        <v>16081</v>
-      </c>
-      <c r="K118" s="22" t="n">
-        <v>-17502</v>
-      </c>
-      <c r="L118" s="22" t="n">
-        <v>-79651</v>
-      </c>
-      <c r="M118" s="22" t="n">
-        <v>56658</v>
-      </c>
-      <c r="N118" s="22" t="n">
-        <v>12437</v>
-      </c>
-      <c r="Q118" s="22" t="n">
-        <v>4486</v>
-      </c>
-      <c r="R118" s="22" t="n">
-        <v>6205</v>
-      </c>
-      <c r="S118" s="22" t="n">
-        <v>-64421</v>
-      </c>
-      <c r="T118" s="22" t="n">
-        <v>-83122</v>
-      </c>
-      <c r="U118" s="22" t="n">
-        <v>-183311</v>
-      </c>
-      <c r="V118" s="22" t="n">
-        <v>130634</v>
-      </c>
-      <c r="W118" s="22" t="n">
-        <v>-28843</v>
-      </c>
-      <c r="X118" s="22" t="n">
-        <v>-79651</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="20" t="inlineStr">
-        <is>
-          <t>확정급여제도 출연</t>
-        </is>
-      </c>
-      <c r="C119" s="22" t="n">
-        <v>-2241</v>
-      </c>
-      <c r="D119" s="22" t="n">
-        <v>-2887</v>
-      </c>
-      <c r="E119" s="22" t="n">
-        <v>-842</v>
-      </c>
-      <c r="F119" s="22" t="n">
-        <v>-1454</v>
-      </c>
-      <c r="G119" s="22" t="n">
-        <v>-2311</v>
-      </c>
-      <c r="H119" s="22" t="n">
-        <v>-2680</v>
-      </c>
-      <c r="I119" s="22" t="n">
-        <v>-607</v>
-      </c>
-      <c r="J119" s="22" t="n">
-        <v>-1188</v>
-      </c>
-      <c r="K119" s="22" t="n">
-        <v>-1734</v>
-      </c>
-      <c r="L119" s="22" t="n">
-        <v>-2254</v>
-      </c>
-      <c r="M119" s="22" t="n">
-        <v>-525</v>
-      </c>
-      <c r="N119" s="22" t="n">
-        <v>-1054</v>
-      </c>
-      <c r="Q119" s="22" t="n">
-        <v>-2652</v>
-      </c>
-      <c r="R119" s="22" t="n">
-        <v>-11540</v>
-      </c>
-      <c r="S119" s="22" t="n">
-        <v>-4656</v>
-      </c>
-      <c r="T119" s="22" t="n">
-        <v>-3665</v>
-      </c>
-      <c r="U119" s="22" t="n">
-        <v>-3739</v>
-      </c>
-      <c r="V119" s="22" t="n">
-        <v>-2887</v>
-      </c>
-      <c r="W119" s="22" t="n">
-        <v>-2680</v>
-      </c>
-      <c r="X119" s="22" t="n">
-        <v>-2254</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="20" t="inlineStr">
-        <is>
-          <t>충당금 지급</t>
-        </is>
-      </c>
-      <c r="C120" s="22" t="n">
-        <v>-1876</v>
-      </c>
-      <c r="D120" s="22" t="n">
-        <v>-2227</v>
-      </c>
-      <c r="E120" s="22" t="n">
-        <v>-1070</v>
-      </c>
-      <c r="F120" s="22" t="n">
-        <v>-2140</v>
-      </c>
-      <c r="G120" s="22" t="n">
-        <v>-3090</v>
-      </c>
-      <c r="H120" s="22" t="n">
-        <v>-3524</v>
-      </c>
-      <c r="I120" s="22" t="n">
-        <v>-310</v>
-      </c>
-      <c r="J120" s="22" t="n">
-        <v>-2353</v>
-      </c>
-      <c r="K120" s="22" t="n">
-        <v>-3561</v>
-      </c>
-      <c r="L120" s="22" t="n">
-        <v>-3881</v>
-      </c>
-      <c r="M120" s="22" t="n">
-        <v>-599</v>
-      </c>
-      <c r="N120" s="22" t="n">
-        <v>-1456</v>
-      </c>
-      <c r="Q120" s="22" t="n">
-        <v>-29</v>
-      </c>
-      <c r="R120" s="22" t="n">
-        <v>-2</v>
-      </c>
-      <c r="S120" s="22" t="n">
-        <v>-26</v>
-      </c>
-      <c r="T120" s="22" t="n">
-        <v>-656</v>
-      </c>
-      <c r="U120" s="22" t="n">
-        <v>-1634</v>
-      </c>
-      <c r="V120" s="22" t="n">
-        <v>-2227</v>
-      </c>
-      <c r="W120" s="22" t="n">
-        <v>-3524</v>
-      </c>
-      <c r="X120" s="22" t="n">
-        <v>-3881</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="20" t="inlineStr">
-        <is>
-          <t>기타영업활동</t>
-        </is>
-      </c>
-      <c r="C121" s="22" t="n">
-        <v>2711</v>
-      </c>
-      <c r="D121" s="22" t="n">
-        <v>-2244</v>
-      </c>
-      <c r="E121" s="22" t="n">
-        <v>-10413</v>
-      </c>
-      <c r="F121" s="22" t="n">
-        <v>3488</v>
-      </c>
-      <c r="G121" s="22" t="n">
-        <v>-9903</v>
-      </c>
-      <c r="H121" s="22" t="n">
-        <v>-6422</v>
-      </c>
-      <c r="I121" s="22" t="n">
-        <v>-13583</v>
-      </c>
-      <c r="J121" s="22" t="n">
-        <v>-5554</v>
-      </c>
-      <c r="K121" s="22" t="n">
-        <v>-745</v>
-      </c>
-      <c r="L121" s="22" t="n">
-        <v>12235</v>
-      </c>
-      <c r="M121" s="22" t="n">
-        <v>-15125</v>
-      </c>
-      <c r="N121" s="22" t="n">
-        <v>-13298</v>
-      </c>
-      <c r="Q121" s="22" t="n">
-        <v>-3022</v>
-      </c>
-      <c r="R121" s="22" t="n">
-        <v>-2741</v>
-      </c>
-      <c r="S121" s="22" t="n">
-        <v>694</v>
-      </c>
-      <c r="T121" s="22" t="n">
-        <v>776</v>
-      </c>
-      <c r="U121" s="22" t="n">
-        <v>9004</v>
-      </c>
-      <c r="V121" s="22" t="n">
-        <v>-2244</v>
-      </c>
-      <c r="W121" s="22" t="n">
-        <v>-6422</v>
-      </c>
-      <c r="X121" s="22" t="n">
-        <v>12235</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="20" t="inlineStr">
         <is>
-          <t>소계</t>
+          <t>영업활동 현금창출</t>
         </is>
       </c>
       <c r="C122" s="22" t="n">
-        <v>461476</v>
+        <v>345003</v>
       </c>
       <c r="D122" s="22" t="n">
-        <v>585998</v>
+        <v>462722</v>
       </c>
       <c r="E122" s="22" t="n">
-        <v>141920</v>
+        <v>110138</v>
       </c>
       <c r="F122" s="22" t="n">
-        <v>211601</v>
+        <v>278669</v>
       </c>
       <c r="G122" s="22" t="n">
-        <v>395629</v>
+        <v>448943</v>
       </c>
       <c r="H122" s="22" t="n">
-        <v>548078</v>
+        <v>589546</v>
       </c>
       <c r="I122" s="22" t="n">
-        <v>173593</v>
+        <v>147337</v>
       </c>
       <c r="J122" s="22" t="n">
-        <v>293323</v>
+        <v>286336</v>
       </c>
       <c r="K122" s="22" t="n">
-        <v>447876</v>
+        <v>471417</v>
       </c>
       <c r="L122" s="22" t="n">
-        <v>577384</v>
+        <v>650935</v>
       </c>
       <c r="M122" s="22" t="n">
-        <v>211343</v>
+        <v>170935</v>
       </c>
       <c r="N122" s="22" t="n">
-        <v>338600</v>
+        <v>341970</v>
       </c>
       <c r="Q122" s="22" t="n">
-        <v>150639</v>
+        <v>151857</v>
       </c>
       <c r="R122" s="22" t="n">
-        <v>241423</v>
+        <v>249500</v>
       </c>
       <c r="S122" s="22" t="n">
-        <v>271820</v>
+        <v>340228</v>
       </c>
       <c r="T122" s="22" t="n">
-        <v>383700</v>
+        <v>470367</v>
       </c>
       <c r="U122" s="22" t="n">
-        <v>395665</v>
+        <v>575345</v>
       </c>
       <c r="V122" s="22" t="n">
-        <v>585998</v>
+        <v>462722</v>
       </c>
       <c r="W122" s="22" t="n">
-        <v>548078</v>
+        <v>589546</v>
       </c>
       <c r="X122" s="22" t="n">
-        <v>577384</v>
+        <v>650935</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="20" t="inlineStr">
         <is>
-          <t>법인소득세 지급</t>
+          <t>운전자본 감소</t>
         </is>
       </c>
       <c r="C123" s="22" t="n">
-        <v>-175761</v>
+        <v>117878</v>
       </c>
       <c r="D123" s="22" t="n">
-        <v>-176074</v>
+        <v>130634</v>
       </c>
       <c r="E123" s="22" t="n">
-        <v>-41007</v>
+        <v>44108</v>
       </c>
       <c r="F123" s="22" t="n">
-        <v>-40038</v>
+        <v>-66963</v>
       </c>
       <c r="G123" s="22" t="n">
-        <v>-100423</v>
+        <v>-38011</v>
       </c>
       <c r="H123" s="22" t="n">
-        <v>-100477</v>
+        <v>-28843</v>
       </c>
       <c r="I123" s="22" t="n">
-        <v>-106915</v>
+        <v>40756</v>
       </c>
       <c r="J123" s="22" t="n">
-        <v>-107240</v>
+        <v>16081</v>
       </c>
       <c r="K123" s="22" t="n">
-        <v>-190703</v>
+        <v>-17502</v>
       </c>
       <c r="L123" s="22" t="n">
-        <v>-191104</v>
+        <v>-79651</v>
       </c>
       <c r="M123" s="22" t="n">
-        <v>-89303</v>
+        <v>56658</v>
       </c>
       <c r="N123" s="22" t="n">
-        <v>-89498</v>
+        <v>12437</v>
       </c>
       <c r="Q123" s="22" t="n">
-        <v>-31565</v>
+        <v>4486</v>
       </c>
       <c r="R123" s="22" t="n">
-        <v>-34782</v>
+        <v>6205</v>
       </c>
       <c r="S123" s="22" t="n">
-        <v>-66785</v>
+        <v>-64421</v>
       </c>
       <c r="T123" s="22" t="n">
-        <v>-104074</v>
+        <v>-83122</v>
       </c>
       <c r="U123" s="22" t="n">
-        <v>-152082</v>
+        <v>-183311</v>
       </c>
       <c r="V123" s="22" t="n">
-        <v>-176074</v>
+        <v>130634</v>
       </c>
       <c r="W123" s="22" t="n">
-        <v>-100477</v>
+        <v>-28843</v>
       </c>
       <c r="X123" s="22" t="n">
-        <v>-191104</v>
+        <v>-79651</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C124" s="12" t="n">
-        <v>285715</v>
-      </c>
-      <c r="D124" s="12" t="n">
-        <v>409925</v>
-      </c>
-      <c r="E124" s="12" t="n">
-        <v>100913</v>
-      </c>
-      <c r="F124" s="12" t="n">
-        <v>171563</v>
-      </c>
-      <c r="G124" s="12" t="n">
-        <v>295206</v>
-      </c>
-      <c r="H124" s="12" t="n">
-        <v>447600</v>
-      </c>
-      <c r="I124" s="12" t="n">
-        <v>66677</v>
-      </c>
-      <c r="J124" s="12" t="n">
-        <v>186084</v>
-      </c>
-      <c r="K124" s="12" t="n">
-        <v>257173</v>
-      </c>
-      <c r="L124" s="12" t="n">
-        <v>386280</v>
-      </c>
-      <c r="M124" s="12" t="n">
-        <v>122040</v>
-      </c>
-      <c r="N124" s="12" t="n">
-        <v>249102</v>
-      </c>
-      <c r="Q124" s="12" t="n">
-        <v>119074</v>
-      </c>
-      <c r="R124" s="12" t="n">
-        <v>206641</v>
-      </c>
-      <c r="S124" s="12" t="n">
-        <v>205035</v>
-      </c>
-      <c r="T124" s="12" t="n">
-        <v>279626</v>
-      </c>
-      <c r="U124" s="12" t="n">
-        <v>243582</v>
-      </c>
-      <c r="V124" s="12" t="n">
-        <v>409925</v>
-      </c>
-      <c r="W124" s="12" t="n">
-        <v>447600</v>
-      </c>
-      <c r="X124" s="12" t="n">
-        <v>386280</v>
+      <c r="A124" s="20" t="inlineStr">
+        <is>
+          <t>확정급여제도 출연</t>
+        </is>
+      </c>
+      <c r="C124" s="22" t="n">
+        <v>-2241</v>
+      </c>
+      <c r="D124" s="22" t="n">
+        <v>-2887</v>
+      </c>
+      <c r="E124" s="22" t="n">
+        <v>-842</v>
+      </c>
+      <c r="F124" s="22" t="n">
+        <v>-1454</v>
+      </c>
+      <c r="G124" s="22" t="n">
+        <v>-2311</v>
+      </c>
+      <c r="H124" s="22" t="n">
+        <v>-2680</v>
+      </c>
+      <c r="I124" s="22" t="n">
+        <v>-607</v>
+      </c>
+      <c r="J124" s="22" t="n">
+        <v>-1188</v>
+      </c>
+      <c r="K124" s="22" t="n">
+        <v>-1734</v>
+      </c>
+      <c r="L124" s="22" t="n">
+        <v>-2254</v>
+      </c>
+      <c r="M124" s="22" t="n">
+        <v>-525</v>
+      </c>
+      <c r="N124" s="22" t="n">
+        <v>-1054</v>
+      </c>
+      <c r="Q124" s="22" t="n">
+        <v>-2652</v>
+      </c>
+      <c r="R124" s="22" t="n">
+        <v>-11540</v>
+      </c>
+      <c r="S124" s="22" t="n">
+        <v>-4656</v>
+      </c>
+      <c r="T124" s="22" t="n">
+        <v>-3665</v>
+      </c>
+      <c r="U124" s="22" t="n">
+        <v>-3739</v>
+      </c>
+      <c r="V124" s="22" t="n">
+        <v>-2887</v>
+      </c>
+      <c r="W124" s="22" t="n">
+        <v>-2680</v>
+      </c>
+      <c r="X124" s="22" t="n">
+        <v>-2254</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="20" t="inlineStr">
         <is>
-          <t>유형자산 취득</t>
+          <t>충당금 지급</t>
         </is>
       </c>
       <c r="C125" s="22" t="n">
-        <v>-54150</v>
+        <v>-1876</v>
       </c>
       <c r="D125" s="22" t="n">
-        <v>-71948</v>
+        <v>-2227</v>
       </c>
       <c r="E125" s="22" t="n">
-        <v>-12377</v>
+        <v>-1070</v>
       </c>
       <c r="F125" s="22" t="n">
-        <v>-32871</v>
+        <v>-2140</v>
       </c>
       <c r="G125" s="22" t="n">
-        <v>-50159</v>
+        <v>-3090</v>
       </c>
       <c r="H125" s="22" t="n">
-        <v>-50415</v>
+        <v>-3524</v>
       </c>
       <c r="I125" s="22" t="n">
-        <v>-22035</v>
+        <v>-310</v>
       </c>
       <c r="J125" s="22" t="n">
-        <v>-48925</v>
+        <v>-2353</v>
       </c>
       <c r="K125" s="22" t="n">
-        <v>-58902</v>
+        <v>-3561</v>
       </c>
       <c r="L125" s="22" t="n">
-        <v>-76273</v>
+        <v>-3881</v>
       </c>
       <c r="M125" s="22" t="n">
-        <v>-12661</v>
+        <v>-599</v>
       </c>
       <c r="N125" s="22" t="n">
-        <v>-21228</v>
+        <v>-1456</v>
       </c>
       <c r="Q125" s="22" t="n">
-        <v>-71785</v>
+        <v>-29</v>
       </c>
       <c r="R125" s="22" t="n">
-        <v>-53009</v>
+        <v>-2</v>
       </c>
       <c r="S125" s="22" t="n">
-        <v>-57040</v>
+        <v>-26</v>
       </c>
       <c r="T125" s="22" t="n">
-        <v>-65969</v>
+        <v>-656</v>
       </c>
       <c r="U125" s="22" t="n">
-        <v>-62625</v>
+        <v>-1634</v>
       </c>
       <c r="V125" s="22" t="n">
-        <v>-71948</v>
+        <v>-2227</v>
       </c>
       <c r="W125" s="22" t="n">
-        <v>-50415</v>
+        <v>-3524</v>
       </c>
       <c r="X125" s="22" t="n">
-        <v>-76273</v>
+        <v>-3881</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="20" t="inlineStr">
         <is>
-          <t>무형자산 취득</t>
+          <t>기타영업활동</t>
         </is>
       </c>
       <c r="C126" s="22" t="n">
-        <v>-1890</v>
+        <v>2711</v>
       </c>
       <c r="D126" s="22" t="n">
-        <v>-2310</v>
+        <v>-2244</v>
       </c>
       <c r="E126" s="22" t="n">
-        <v>-62</v>
+        <v>-10413</v>
       </c>
       <c r="F126" s="22" t="n">
-        <v>-1690</v>
+        <v>3488</v>
       </c>
       <c r="G126" s="22" t="n">
-        <v>-2862</v>
+        <v>-9903</v>
       </c>
       <c r="H126" s="22" t="n">
-        <v>-3974</v>
+        <v>-6422</v>
       </c>
       <c r="I126" s="22" t="n">
-        <v>-469</v>
+        <v>-13583</v>
       </c>
       <c r="J126" s="22" t="n">
-        <v>-16230</v>
+        <v>-5554</v>
       </c>
       <c r="K126" s="22" t="n">
-        <v>-17327</v>
+        <v>-745</v>
       </c>
       <c r="L126" s="22" t="n">
-        <v>-35334</v>
+        <v>12235</v>
       </c>
       <c r="M126" s="22" t="n">
-        <v>-7864</v>
+        <v>-15125</v>
       </c>
       <c r="N126" s="22" t="n">
-        <v>-9891</v>
+        <v>-13298</v>
       </c>
       <c r="Q126" s="22" t="n">
-        <v>-5886</v>
+        <v>-3022</v>
       </c>
       <c r="R126" s="22" t="n">
-        <v>-8168</v>
+        <v>-2741</v>
       </c>
       <c r="S126" s="22" t="n">
-        <v>-4349</v>
+        <v>694</v>
       </c>
       <c r="T126" s="22" t="n">
-        <v>-6897</v>
+        <v>776</v>
       </c>
       <c r="U126" s="22" t="n">
-        <v>-8614</v>
+        <v>9004</v>
       </c>
       <c r="V126" s="22" t="n">
-        <v>-2310</v>
+        <v>-2244</v>
       </c>
       <c r="W126" s="22" t="n">
-        <v>-3974</v>
+        <v>-6422</v>
       </c>
       <c r="X126" s="22" t="n">
-        <v>-35334</v>
+        <v>12235</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="20" t="inlineStr">
         <is>
-          <t>유형자산 처분</t>
+          <t>소계</t>
         </is>
       </c>
       <c r="C127" s="22" t="n">
-        <v>1988</v>
+        <v>461476</v>
       </c>
       <c r="D127" s="22" t="n">
-        <v>19346</v>
+        <v>585998</v>
       </c>
       <c r="E127" s="22" t="n">
-        <v>-95</v>
+        <v>141920</v>
       </c>
       <c r="F127" s="22" t="n">
-        <v>-214</v>
+        <v>211601</v>
       </c>
       <c r="G127" s="22" t="n">
-        <v>-450</v>
+        <v>395629</v>
       </c>
       <c r="H127" s="22" t="n">
-        <v>-510</v>
+        <v>548078</v>
       </c>
       <c r="I127" s="22" t="n">
-        <v>-66</v>
+        <v>173593</v>
       </c>
       <c r="J127" s="22" t="n">
-        <v>7357</v>
+        <v>293323</v>
       </c>
       <c r="K127" s="22" t="n">
-        <v>7285</v>
+        <v>447876</v>
       </c>
       <c r="L127" s="22" t="n">
-        <v>7509</v>
+        <v>577384</v>
       </c>
       <c r="M127" s="22" t="n">
-        <v>-36</v>
+        <v>211343</v>
       </c>
       <c r="N127" s="22" t="n">
-        <v>-60</v>
+        <v>338600</v>
       </c>
       <c r="Q127" s="22" t="n">
-        <v>49</v>
+        <v>150639</v>
       </c>
       <c r="R127" s="22" t="n">
-        <v>119</v>
+        <v>241423</v>
       </c>
       <c r="S127" s="22" t="n">
-        <v>-22</v>
+        <v>271820</v>
       </c>
       <c r="T127" s="22" t="n">
-        <v>1042</v>
+        <v>383700</v>
       </c>
       <c r="U127" s="22" t="n">
-        <v>1048</v>
+        <v>395665</v>
       </c>
       <c r="V127" s="22" t="n">
-        <v>19346</v>
+        <v>585998</v>
       </c>
       <c r="W127" s="22" t="n">
-        <v>-510</v>
+        <v>548078</v>
       </c>
       <c r="X127" s="22" t="n">
-        <v>7509</v>
+        <v>577384</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="20" t="inlineStr">
         <is>
-          <t>무형자산 처분</t>
+          <t>법인소득세 지급</t>
         </is>
       </c>
       <c r="C128" s="22" t="n">
-        <v>15160</v>
+        <v>-175761</v>
       </c>
       <c r="D128" s="22" t="n">
-        <v>15160</v>
+        <v>-176074</v>
       </c>
       <c r="E128" s="22" t="n">
-        <v>0</v>
+        <v>-41007</v>
       </c>
       <c r="F128" s="22" t="n">
-        <v>544</v>
+        <v>-40038</v>
       </c>
       <c r="G128" s="22" t="n">
-        <v>1707</v>
+        <v>-100423</v>
       </c>
       <c r="H128" s="22" t="n">
-        <v>2289</v>
+        <v>-100477</v>
       </c>
       <c r="I128" s="22" t="n">
-        <v>28</v>
+        <v>-106915</v>
       </c>
       <c r="J128" s="22" t="n">
-        <v>28</v>
+        <v>-107240</v>
       </c>
       <c r="K128" s="22" t="n">
-        <v>28</v>
+        <v>-190703</v>
       </c>
       <c r="L128" s="22" t="n">
-        <v>28</v>
+        <v>-191104</v>
       </c>
       <c r="M128" s="22" t="n">
-        <v>0</v>
+        <v>-89303</v>
       </c>
       <c r="N128" s="22" t="n">
-        <v>14</v>
+        <v>-89498</v>
+      </c>
+      <c r="Q128" s="22" t="n">
+        <v>-31565</v>
+      </c>
+      <c r="R128" s="22" t="n">
+        <v>-34782</v>
+      </c>
+      <c r="S128" s="22" t="n">
+        <v>-66785</v>
+      </c>
+      <c r="T128" s="22" t="n">
+        <v>-104074</v>
       </c>
       <c r="U128" s="22" t="n">
-        <v>530</v>
+        <v>-152082</v>
       </c>
       <c r="V128" s="22" t="n">
-        <v>15160</v>
+        <v>-176074</v>
       </c>
       <c r="W128" s="22" t="n">
-        <v>2289</v>
+        <v>-100477</v>
       </c>
       <c r="X128" s="22" t="n">
-        <v>28</v>
+        <v>-191104</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="20" t="inlineStr">
-        <is>
-          <t>이자 및 배당금 수취</t>
-        </is>
-      </c>
-      <c r="C129" s="22" t="n">
-        <v>1047</v>
-      </c>
-      <c r="D129" s="22" t="n">
-        <v>1482</v>
-      </c>
-      <c r="E129" s="22" t="n">
-        <v>857</v>
-      </c>
-      <c r="F129" s="22" t="n">
-        <v>1462</v>
-      </c>
-      <c r="G129" s="22" t="n">
-        <v>2189</v>
-      </c>
-      <c r="H129" s="22" t="n">
-        <v>2784</v>
-      </c>
-      <c r="I129" s="22" t="n">
-        <v>715</v>
-      </c>
-      <c r="J129" s="22" t="n">
-        <v>1417</v>
-      </c>
-      <c r="K129" s="22" t="n">
-        <v>2521</v>
-      </c>
-      <c r="L129" s="22" t="n">
-        <v>3600</v>
-      </c>
-      <c r="M129" s="22" t="n">
-        <v>1507</v>
-      </c>
-      <c r="N129" s="22" t="n">
-        <v>2636</v>
-      </c>
-      <c r="Q129" s="22" t="n">
-        <v>200</v>
-      </c>
-      <c r="R129" s="22" t="n">
-        <v>197</v>
-      </c>
-      <c r="S129" s="22" t="n">
-        <v>100</v>
-      </c>
-      <c r="T129" s="22" t="n">
-        <v>133</v>
-      </c>
-      <c r="U129" s="22" t="n">
-        <v>281</v>
-      </c>
-      <c r="V129" s="22" t="n">
-        <v>1482</v>
-      </c>
-      <c r="W129" s="22" t="n">
-        <v>2784</v>
-      </c>
-      <c r="X129" s="22" t="n">
-        <v>3600</v>
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C129" s="12" t="n">
+        <v>285715</v>
+      </c>
+      <c r="D129" s="12" t="n">
+        <v>409925</v>
+      </c>
+      <c r="E129" s="12" t="n">
+        <v>100913</v>
+      </c>
+      <c r="F129" s="12" t="n">
+        <v>171563</v>
+      </c>
+      <c r="G129" s="12" t="n">
+        <v>295206</v>
+      </c>
+      <c r="H129" s="12" t="n">
+        <v>447600</v>
+      </c>
+      <c r="I129" s="12" t="n">
+        <v>66677</v>
+      </c>
+      <c r="J129" s="12" t="n">
+        <v>186084</v>
+      </c>
+      <c r="K129" s="12" t="n">
+        <v>257173</v>
+      </c>
+      <c r="L129" s="12" t="n">
+        <v>386280</v>
+      </c>
+      <c r="M129" s="12" t="n">
+        <v>122040</v>
+      </c>
+      <c r="N129" s="12" t="n">
+        <v>249102</v>
+      </c>
+      <c r="Q129" s="12" t="n">
+        <v>119074</v>
+      </c>
+      <c r="R129" s="12" t="n">
+        <v>206641</v>
+      </c>
+      <c r="S129" s="12" t="n">
+        <v>205035</v>
+      </c>
+      <c r="T129" s="12" t="n">
+        <v>279626</v>
+      </c>
+      <c r="U129" s="12" t="n">
+        <v>243582</v>
+      </c>
+      <c r="V129" s="12" t="n">
+        <v>409925</v>
+      </c>
+      <c r="W129" s="12" t="n">
+        <v>447600</v>
+      </c>
+      <c r="X129" s="12" t="n">
+        <v>386280</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="20" t="inlineStr">
         <is>
-          <t>유가증권 취득</t>
+          <t>유형자산 취득</t>
         </is>
       </c>
       <c r="C130" s="22" t="n">
-        <v>-419923</v>
+        <v>-54150</v>
       </c>
       <c r="D130" s="22" t="n">
-        <v>-545705</v>
+        <v>-71948</v>
       </c>
       <c r="E130" s="22" t="n">
-        <v>-190000</v>
+        <v>-12377</v>
       </c>
       <c r="F130" s="22" t="n">
-        <v>-480143</v>
+        <v>-32871</v>
       </c>
       <c r="G130" s="22" t="n">
-        <v>-725000</v>
+        <v>-50159</v>
       </c>
       <c r="H130" s="22" t="n">
-        <v>-945462</v>
+        <v>-50415</v>
       </c>
       <c r="I130" s="22" t="n">
-        <v>-320000</v>
+        <v>-22035</v>
       </c>
       <c r="J130" s="22" t="n">
-        <v>-589985</v>
+        <v>-48925</v>
       </c>
       <c r="K130" s="22" t="n">
-        <v>-895460</v>
+        <v>-58902</v>
       </c>
       <c r="L130" s="22" t="n">
-        <v>-1227509</v>
+        <v>-76273</v>
       </c>
       <c r="M130" s="22" t="n">
-        <v>-260468</v>
+        <v>-12661</v>
       </c>
       <c r="N130" s="22" t="n">
-        <v>-590452</v>
+        <v>-21228</v>
       </c>
       <c r="Q130" s="22" t="n">
-        <v>-263503</v>
+        <v>-71785</v>
       </c>
       <c r="R130" s="22" t="n">
-        <v>-256768</v>
+        <v>-53009</v>
       </c>
       <c r="S130" s="22" t="n">
-        <v>-248143</v>
+        <v>-57040</v>
       </c>
       <c r="T130" s="22" t="n">
-        <v>-362761</v>
+        <v>-65969</v>
       </c>
       <c r="U130" s="22" t="n">
-        <v>-518681</v>
+        <v>-62625</v>
       </c>
       <c r="V130" s="22" t="n">
-        <v>-545705</v>
+        <v>-71948</v>
       </c>
       <c r="W130" s="22" t="n">
-        <v>-945462</v>
+        <v>-50415</v>
       </c>
       <c r="X130" s="22" t="n">
-        <v>-1227509</v>
+        <v>-76273</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="20" t="inlineStr">
         <is>
-          <t>유가증권 처분</t>
+          <t>무형자산 취득</t>
         </is>
       </c>
       <c r="C131" s="22" t="n">
-        <v>414752</v>
+        <v>-1890</v>
       </c>
       <c r="D131" s="22" t="n">
-        <v>546620</v>
+        <v>-2310</v>
       </c>
       <c r="E131" s="22" t="n">
-        <v>169483</v>
+        <v>-62</v>
       </c>
       <c r="F131" s="22" t="n">
-        <v>340090</v>
+        <v>-1690</v>
       </c>
       <c r="G131" s="22" t="n">
-        <v>565390</v>
+        <v>-2862</v>
       </c>
       <c r="H131" s="22" t="n">
-        <v>771015</v>
+        <v>-3974</v>
       </c>
       <c r="I131" s="22" t="n">
-        <v>255000</v>
+        <v>-469</v>
       </c>
       <c r="J131" s="22" t="n">
-        <v>515630</v>
+        <v>-16230</v>
       </c>
       <c r="K131" s="22" t="n">
-        <v>925630</v>
+        <v>-17327</v>
       </c>
       <c r="L131" s="22" t="n">
-        <v>1130645</v>
+        <v>-35334</v>
       </c>
       <c r="M131" s="22" t="n">
-        <v>381447</v>
+        <v>-7864</v>
       </c>
       <c r="N131" s="22" t="n">
-        <v>571450</v>
+        <v>-9891</v>
       </c>
       <c r="Q131" s="22" t="n">
-        <v>264711</v>
+        <v>-5886</v>
       </c>
       <c r="R131" s="22" t="n">
-        <v>230158</v>
+        <v>-8168</v>
       </c>
       <c r="S131" s="22" t="n">
-        <v>211000</v>
+        <v>-4349</v>
       </c>
       <c r="T131" s="22" t="n">
-        <v>325000</v>
+        <v>-6897</v>
       </c>
       <c r="U131" s="22" t="n">
-        <v>442768</v>
+        <v>-8614</v>
       </c>
       <c r="V131" s="22" t="n">
-        <v>546620</v>
+        <v>-2310</v>
       </c>
       <c r="W131" s="22" t="n">
-        <v>771015</v>
+        <v>-3974</v>
       </c>
       <c r="X131" s="22" t="n">
-        <v>1130645</v>
+        <v>-35334</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 취득</t>
+          <t>유형자산 처분</t>
         </is>
       </c>
       <c r="C132" s="22" t="n">
-        <v>-256</v>
+        <v>1988</v>
       </c>
       <c r="D132" s="22" t="n">
-        <v>-278</v>
+        <v>19346</v>
       </c>
       <c r="E132" s="22" t="n">
-        <v>-50</v>
+        <v>-95</v>
       </c>
       <c r="F132" s="22" t="n">
-        <v>-68</v>
+        <v>-214</v>
       </c>
       <c r="G132" s="22" t="n">
-        <v>-1277</v>
+        <v>-450</v>
       </c>
       <c r="H132" s="22" t="n">
-        <v>-3092</v>
+        <v>-510</v>
       </c>
       <c r="I132" s="22" t="n">
+        <v>-66</v>
+      </c>
+      <c r="J132" s="22" t="n">
+        <v>7357</v>
+      </c>
+      <c r="K132" s="22" t="n">
+        <v>7285</v>
+      </c>
+      <c r="L132" s="22" t="n">
+        <v>7509</v>
+      </c>
+      <c r="M132" s="22" t="n">
+        <v>-36</v>
+      </c>
+      <c r="N132" s="22" t="n">
         <v>-60</v>
       </c>
-      <c r="J132" s="22" t="n">
-        <v>-2761</v>
-      </c>
-      <c r="K132" s="22" t="n">
-        <v>-3325</v>
-      </c>
-      <c r="L132" s="22" t="n">
-        <v>-4258</v>
-      </c>
-      <c r="M132" s="22" t="n">
-        <v>-5</v>
-      </c>
-      <c r="N132" s="22" t="n">
-        <v>-394</v>
-      </c>
       <c r="Q132" s="22" t="n">
-        <v>-709</v>
+        <v>49</v>
       </c>
       <c r="R132" s="22" t="n">
-        <v>-1013</v>
+        <v>119</v>
       </c>
       <c r="S132" s="22" t="n">
-        <v>-177</v>
+        <v>-22</v>
       </c>
       <c r="T132" s="22" t="n">
-        <v>-9503</v>
+        <v>1042</v>
       </c>
       <c r="U132" s="22" t="n">
-        <v>-321</v>
+        <v>1048</v>
       </c>
       <c r="V132" s="22" t="n">
-        <v>-278</v>
+        <v>19346</v>
       </c>
       <c r="W132" s="22" t="n">
-        <v>-3092</v>
+        <v>-510</v>
       </c>
       <c r="X132" s="22" t="n">
-        <v>-4258</v>
+        <v>7509</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 처분</t>
+          <t>무형자산 처분</t>
         </is>
       </c>
       <c r="C133" s="22" t="n">
-        <v>340</v>
+        <v>15160</v>
       </c>
       <c r="D133" s="22" t="n">
-        <v>342</v>
+        <v>15160</v>
       </c>
       <c r="E133" s="22" t="n">
         <v>0</v>
       </c>
       <c r="F133" s="22" t="n">
+        <v>544</v>
+      </c>
+      <c r="G133" s="22" t="n">
+        <v>1707</v>
+      </c>
+      <c r="H133" s="22" t="n">
+        <v>2289</v>
+      </c>
+      <c r="I133" s="22" t="n">
+        <v>28</v>
+      </c>
+      <c r="J133" s="22" t="n">
+        <v>28</v>
+      </c>
+      <c r="K133" s="22" t="n">
+        <v>28</v>
+      </c>
+      <c r="L133" s="22" t="n">
+        <v>28</v>
+      </c>
+      <c r="M133" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G133" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H133" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I133" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J133" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L133" s="22" t="n">
-        <v>318</v>
-      </c>
-      <c r="M133" s="22" t="n">
-        <v>11852</v>
-      </c>
       <c r="N133" s="22" t="n">
-        <v>11876</v>
-      </c>
-      <c r="Q133" s="22" t="n">
-        <v>2863</v>
-      </c>
-      <c r="R133" s="22" t="n">
-        <v>6743</v>
-      </c>
-      <c r="S133" s="22" t="n">
-        <v>319</v>
-      </c>
-      <c r="T133" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="U133" s="22" t="n">
+        <v>530</v>
+      </c>
+      <c r="V133" s="22" t="n">
+        <v>15160</v>
+      </c>
+      <c r="W133" s="22" t="n">
+        <v>2289</v>
+      </c>
+      <c r="X133" s="22" t="n">
         <v>28</v>
-      </c>
-      <c r="U133" s="22" t="n">
-        <v>151</v>
-      </c>
-      <c r="V133" s="22" t="n">
-        <v>342</v>
-      </c>
-      <c r="W133" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X133" s="22" t="n">
-        <v>318</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="20" t="inlineStr">
         <is>
-          <t>기타투자활동</t>
-        </is>
+          <t>이자 및 배당금 수취</t>
+        </is>
+      </c>
+      <c r="C134" s="22" t="n">
+        <v>1047</v>
+      </c>
+      <c r="D134" s="22" t="n">
+        <v>1482</v>
+      </c>
+      <c r="E134" s="22" t="n">
+        <v>857</v>
+      </c>
+      <c r="F134" s="22" t="n">
+        <v>1462</v>
+      </c>
+      <c r="G134" s="22" t="n">
+        <v>2189</v>
+      </c>
+      <c r="H134" s="22" t="n">
+        <v>2784</v>
       </c>
       <c r="I134" s="22" t="n">
-        <v>0</v>
+        <v>715</v>
+      </c>
+      <c r="J134" s="22" t="n">
+        <v>1417</v>
+      </c>
+      <c r="K134" s="22" t="n">
+        <v>2521</v>
+      </c>
+      <c r="L134" s="22" t="n">
+        <v>3600</v>
       </c>
       <c r="M134" s="22" t="n">
-        <v>24</v>
+        <v>1507</v>
+      </c>
+      <c r="N134" s="22" t="n">
+        <v>2636</v>
       </c>
       <c r="Q134" s="22" t="n">
-        <v>-0</v>
+        <v>200</v>
       </c>
       <c r="R134" s="22" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="S134" s="22" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="T134" s="22" t="n">
+        <v>133</v>
+      </c>
+      <c r="U134" s="22" t="n">
+        <v>281</v>
+      </c>
+      <c r="V134" s="22" t="n">
+        <v>1482</v>
+      </c>
+      <c r="W134" s="22" t="n">
+        <v>2784</v>
+      </c>
+      <c r="X134" s="22" t="n">
+        <v>3600</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C135" s="12" t="n">
-        <v>-42934</v>
-      </c>
-      <c r="D135" s="12" t="n">
-        <v>-37290</v>
-      </c>
-      <c r="E135" s="12" t="n">
-        <v>-32244</v>
-      </c>
-      <c r="F135" s="12" t="n">
-        <v>-172890</v>
-      </c>
-      <c r="G135" s="12" t="n">
-        <v>-210462</v>
-      </c>
-      <c r="H135" s="12" t="n">
-        <v>-227365</v>
-      </c>
-      <c r="I135" s="12" t="n">
-        <v>-86886</v>
-      </c>
-      <c r="J135" s="12" t="n">
-        <v>-133469</v>
-      </c>
-      <c r="K135" s="12" t="n">
-        <v>-39549</v>
-      </c>
-      <c r="L135" s="12" t="n">
-        <v>-201273</v>
-      </c>
-      <c r="M135" s="12" t="n">
-        <v>113796</v>
-      </c>
-      <c r="N135" s="12" t="n">
-        <v>-36049</v>
-      </c>
-      <c r="Q135" s="12" t="n">
-        <v>-74060</v>
-      </c>
-      <c r="R135" s="12" t="n">
-        <v>-81741</v>
-      </c>
-      <c r="S135" s="12" t="n">
-        <v>-98312</v>
-      </c>
-      <c r="T135" s="12" t="n">
-        <v>-118927</v>
-      </c>
-      <c r="U135" s="12" t="n">
-        <v>-145465</v>
-      </c>
-      <c r="V135" s="12" t="n">
-        <v>-37290</v>
-      </c>
-      <c r="W135" s="12" t="n">
-        <v>-227365</v>
-      </c>
-      <c r="X135" s="12" t="n">
-        <v>-201273</v>
+      <c r="A135" s="20" t="inlineStr">
+        <is>
+          <t>유가증권 취득</t>
+        </is>
+      </c>
+      <c r="C135" s="22" t="n">
+        <v>-419923</v>
+      </c>
+      <c r="D135" s="22" t="n">
+        <v>-545705</v>
+      </c>
+      <c r="E135" s="22" t="n">
+        <v>-190000</v>
+      </c>
+      <c r="F135" s="22" t="n">
+        <v>-480143</v>
+      </c>
+      <c r="G135" s="22" t="n">
+        <v>-725000</v>
+      </c>
+      <c r="H135" s="22" t="n">
+        <v>-945462</v>
+      </c>
+      <c r="I135" s="22" t="n">
+        <v>-320000</v>
+      </c>
+      <c r="J135" s="22" t="n">
+        <v>-589985</v>
+      </c>
+      <c r="K135" s="22" t="n">
+        <v>-895460</v>
+      </c>
+      <c r="L135" s="22" t="n">
+        <v>-1227509</v>
+      </c>
+      <c r="M135" s="22" t="n">
+        <v>-260468</v>
+      </c>
+      <c r="N135" s="22" t="n">
+        <v>-590452</v>
+      </c>
+      <c r="Q135" s="22" t="n">
+        <v>-263503</v>
+      </c>
+      <c r="R135" s="22" t="n">
+        <v>-256768</v>
+      </c>
+      <c r="S135" s="22" t="n">
+        <v>-248143</v>
+      </c>
+      <c r="T135" s="22" t="n">
+        <v>-362761</v>
+      </c>
+      <c r="U135" s="22" t="n">
+        <v>-518681</v>
+      </c>
+      <c r="V135" s="22" t="n">
+        <v>-545705</v>
+      </c>
+      <c r="W135" s="22" t="n">
+        <v>-945462</v>
+      </c>
+      <c r="X135" s="22" t="n">
+        <v>-1227509</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="20" t="inlineStr">
         <is>
-          <t>비지배지분 취득</t>
-        </is>
+          <t>유가증권 처분</t>
+        </is>
+      </c>
+      <c r="C136" s="22" t="n">
+        <v>414752</v>
+      </c>
+      <c r="D136" s="22" t="n">
+        <v>546620</v>
+      </c>
+      <c r="E136" s="22" t="n">
+        <v>169483</v>
+      </c>
+      <c r="F136" s="22" t="n">
+        <v>340090</v>
+      </c>
+      <c r="G136" s="22" t="n">
+        <v>565390</v>
+      </c>
+      <c r="H136" s="22" t="n">
+        <v>771015</v>
+      </c>
+      <c r="I136" s="22" t="n">
+        <v>255000</v>
+      </c>
+      <c r="J136" s="22" t="n">
+        <v>515630</v>
+      </c>
+      <c r="K136" s="22" t="n">
+        <v>925630</v>
+      </c>
+      <c r="L136" s="22" t="n">
+        <v>1130645</v>
+      </c>
+      <c r="M136" s="22" t="n">
+        <v>381447</v>
+      </c>
+      <c r="N136" s="22" t="n">
+        <v>571450</v>
       </c>
       <c r="Q136" s="22" t="n">
-        <v>0</v>
+        <v>264711</v>
       </c>
       <c r="R136" s="22" t="n">
-        <v>-2307</v>
+        <v>230158</v>
       </c>
       <c r="S136" s="22" t="n">
-        <v>0</v>
+        <v>211000</v>
+      </c>
+      <c r="T136" s="22" t="n">
+        <v>325000</v>
+      </c>
+      <c r="U136" s="22" t="n">
+        <v>442768</v>
+      </c>
+      <c r="V136" s="22" t="n">
+        <v>546620</v>
+      </c>
+      <c r="W136" s="22" t="n">
+        <v>771015</v>
+      </c>
+      <c r="X136" s="22" t="n">
+        <v>1130645</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="20" t="inlineStr">
         <is>
-          <t>이자 지급</t>
+          <t>투자유가증권 취득</t>
         </is>
       </c>
       <c r="C137" s="22" t="n">
+        <v>-256</v>
+      </c>
+      <c r="D137" s="22" t="n">
+        <v>-278</v>
+      </c>
+      <c r="E137" s="22" t="n">
+        <v>-50</v>
+      </c>
+      <c r="F137" s="22" t="n">
+        <v>-68</v>
+      </c>
+      <c r="G137" s="22" t="n">
+        <v>-1277</v>
+      </c>
+      <c r="H137" s="22" t="n">
+        <v>-3092</v>
+      </c>
+      <c r="I137" s="22" t="n">
         <v>-60</v>
       </c>
-      <c r="D137" s="22" t="n">
-        <v>-81</v>
-      </c>
-      <c r="E137" s="22" t="n">
-        <v>-21</v>
-      </c>
-      <c r="F137" s="22" t="n">
-        <v>-45</v>
-      </c>
-      <c r="G137" s="22" t="n">
-        <v>-70</v>
-      </c>
-      <c r="H137" s="22" t="n">
-        <v>-94</v>
-      </c>
-      <c r="I137" s="22" t="n">
-        <v>-52</v>
-      </c>
       <c r="J137" s="22" t="n">
-        <v>-165</v>
+        <v>-2761</v>
       </c>
       <c r="K137" s="22" t="n">
-        <v>-286</v>
+        <v>-3325</v>
       </c>
       <c r="L137" s="22" t="n">
-        <v>-429</v>
+        <v>-4258</v>
       </c>
       <c r="M137" s="22" t="n">
-        <v>-144</v>
+        <v>-5</v>
       </c>
       <c r="N137" s="22" t="n">
-        <v>-285</v>
+        <v>-394</v>
       </c>
       <c r="Q137" s="22" t="n">
-        <v>-5</v>
+        <v>-709</v>
       </c>
       <c r="R137" s="22" t="n">
-        <v>-27</v>
+        <v>-1013</v>
       </c>
       <c r="S137" s="22" t="n">
-        <v>-34</v>
+        <v>-177</v>
       </c>
       <c r="T137" s="22" t="n">
-        <v>-48</v>
+        <v>-9503</v>
       </c>
       <c r="U137" s="22" t="n">
-        <v>-58</v>
+        <v>-321</v>
       </c>
       <c r="V137" s="22" t="n">
-        <v>-81</v>
+        <v>-278</v>
       </c>
       <c r="W137" s="22" t="n">
-        <v>-94</v>
+        <v>-3092</v>
       </c>
       <c r="X137" s="22" t="n">
-        <v>-429</v>
+        <v>-4258</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="20" t="inlineStr">
         <is>
-          <t>리스부채 지급</t>
+          <t>투자유가증권 처분</t>
         </is>
       </c>
       <c r="C138" s="22" t="n">
-        <v>-5908</v>
+        <v>340</v>
       </c>
       <c r="D138" s="22" t="n">
-        <v>-7868</v>
+        <v>342</v>
       </c>
       <c r="E138" s="22" t="n">
-        <v>-1962</v>
+        <v>0</v>
       </c>
       <c r="F138" s="22" t="n">
-        <v>-4014</v>
+        <v>0</v>
       </c>
       <c r="G138" s="22" t="n">
-        <v>-6089</v>
+        <v>0</v>
       </c>
       <c r="H138" s="22" t="n">
-        <v>-8148</v>
+        <v>0</v>
       </c>
       <c r="I138" s="22" t="n">
-        <v>-2033</v>
+        <v>0</v>
       </c>
       <c r="J138" s="22" t="n">
-        <v>-3957</v>
-      </c>
-      <c r="K138" s="22" t="n">
-        <v>-5932</v>
+        <v>0</v>
       </c>
       <c r="L138" s="22" t="n">
-        <v>-8176</v>
+        <v>318</v>
       </c>
       <c r="M138" s="22" t="n">
-        <v>-2512</v>
+        <v>11852</v>
       </c>
       <c r="N138" s="22" t="n">
-        <v>-4793</v>
+        <v>11876</v>
       </c>
       <c r="Q138" s="22" t="n">
+        <v>2863</v>
+      </c>
+      <c r="R138" s="22" t="n">
+        <v>6743</v>
+      </c>
+      <c r="S138" s="22" t="n">
+        <v>319</v>
+      </c>
+      <c r="T138" s="22" t="n">
+        <v>28</v>
+      </c>
+      <c r="U138" s="22" t="n">
+        <v>151</v>
+      </c>
+      <c r="V138" s="22" t="n">
+        <v>342</v>
+      </c>
+      <c r="W138" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="R138" s="22" t="n">
-        <v>-8861</v>
-      </c>
-      <c r="S138" s="22" t="n">
-        <v>-8432</v>
-      </c>
-      <c r="T138" s="22" t="n">
-        <v>-9031</v>
-      </c>
-      <c r="U138" s="22" t="n">
-        <v>-7599</v>
-      </c>
-      <c r="V138" s="22" t="n">
-        <v>-7868</v>
-      </c>
-      <c r="W138" s="22" t="n">
-        <v>-8148</v>
-      </c>
       <c r="X138" s="22" t="n">
-        <v>-8176</v>
+        <v>318</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="20" t="inlineStr">
         <is>
-          <t>배당금 지급 - 지배기업 지분</t>
-        </is>
-      </c>
-      <c r="C139" s="22" t="n">
-        <v>-131226</v>
-      </c>
-      <c r="D139" s="22" t="n">
-        <v>-131594</v>
-      </c>
-      <c r="E139" s="22" t="n">
-        <v>-64960</v>
-      </c>
-      <c r="F139" s="22" t="n">
-        <v>-65500</v>
-      </c>
-      <c r="G139" s="22" t="n">
-        <v>-132959</v>
-      </c>
-      <c r="H139" s="22" t="n">
-        <v>-133249</v>
+          <t>기타투자활동</t>
+        </is>
       </c>
       <c r="I139" s="22" t="n">
-        <v>-93408</v>
-      </c>
-      <c r="J139" s="22" t="n">
-        <v>-93846</v>
-      </c>
-      <c r="K139" s="22" t="n">
-        <v>-299542</v>
-      </c>
-      <c r="L139" s="22" t="n">
-        <v>-299419</v>
+        <v>0</v>
       </c>
       <c r="M139" s="22" t="n">
-        <v>-241990</v>
-      </c>
-      <c r="N139" s="22" t="n">
-        <v>-241925</v>
+        <v>24</v>
       </c>
       <c r="Q139" s="22" t="n">
-        <v>-35010</v>
+        <v>-0</v>
       </c>
       <c r="R139" s="22" t="n">
-        <v>-56370</v>
+        <v>0</v>
       </c>
       <c r="S139" s="22" t="n">
-        <v>-91442</v>
-      </c>
-      <c r="T139" s="22" t="n">
-        <v>-98644</v>
-      </c>
-      <c r="U139" s="22" t="n">
-        <v>-138220</v>
-      </c>
-      <c r="V139" s="22" t="n">
-        <v>-131594</v>
-      </c>
-      <c r="W139" s="22" t="n">
-        <v>-133249</v>
-      </c>
-      <c r="X139" s="22" t="n">
-        <v>-299419</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="20" t="inlineStr">
-        <is>
-          <t>배당금 지급 - 비지배지분</t>
-        </is>
-      </c>
-      <c r="Q140" s="22" t="n">
-        <v>-791</v>
-      </c>
-      <c r="R140" s="22" t="n">
-        <v>0</v>
+      <c r="A140" s="9" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C140" s="12" t="n">
+        <v>-42934</v>
+      </c>
+      <c r="D140" s="12" t="n">
+        <v>-37290</v>
+      </c>
+      <c r="E140" s="12" t="n">
+        <v>-32244</v>
+      </c>
+      <c r="F140" s="12" t="n">
+        <v>-172890</v>
+      </c>
+      <c r="G140" s="12" t="n">
+        <v>-210462</v>
+      </c>
+      <c r="H140" s="12" t="n">
+        <v>-227365</v>
+      </c>
+      <c r="I140" s="12" t="n">
+        <v>-86886</v>
+      </c>
+      <c r="J140" s="12" t="n">
+        <v>-133469</v>
+      </c>
+      <c r="K140" s="12" t="n">
+        <v>-39549</v>
+      </c>
+      <c r="L140" s="12" t="n">
+        <v>-201273</v>
+      </c>
+      <c r="M140" s="12" t="n">
+        <v>113796</v>
+      </c>
+      <c r="N140" s="12" t="n">
+        <v>-36049</v>
+      </c>
+      <c r="Q140" s="12" t="n">
+        <v>-74060</v>
+      </c>
+      <c r="R140" s="12" t="n">
+        <v>-81741</v>
+      </c>
+      <c r="S140" s="12" t="n">
+        <v>-98312</v>
+      </c>
+      <c r="T140" s="12" t="n">
+        <v>-118927</v>
+      </c>
+      <c r="U140" s="12" t="n">
+        <v>-145465</v>
+      </c>
+      <c r="V140" s="12" t="n">
+        <v>-37290</v>
+      </c>
+      <c r="W140" s="12" t="n">
+        <v>-227365</v>
+      </c>
+      <c r="X140" s="12" t="n">
+        <v>-201273</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="20" t="inlineStr">
         <is>
-          <t>스톡옵션 행사</t>
-        </is>
-      </c>
-      <c r="C141" s="22" t="n">
-        <v>167</v>
-      </c>
-      <c r="D141" s="22" t="n">
-        <v>217</v>
-      </c>
-      <c r="E141" s="22" t="n">
-        <v>75</v>
-      </c>
-      <c r="F141" s="22" t="n">
-        <v>94</v>
-      </c>
-      <c r="G141" s="22" t="n">
-        <v>152</v>
-      </c>
-      <c r="H141" s="22" t="n">
-        <v>168</v>
-      </c>
-      <c r="I141" s="22" t="n">
-        <v>115</v>
-      </c>
-      <c r="J141" s="22" t="n">
-        <v>126</v>
-      </c>
-      <c r="K141" s="22" t="n">
-        <v>130</v>
-      </c>
-      <c r="L141" s="22" t="n">
-        <v>142</v>
-      </c>
-      <c r="M141" s="22" t="n">
-        <v>62</v>
-      </c>
-      <c r="N141" s="22" t="n">
-        <v>62</v>
+          <t>비지배지분 취득</t>
+        </is>
       </c>
       <c r="Q141" s="22" t="n">
-        <v>996</v>
+        <v>0</v>
       </c>
       <c r="R141" s="22" t="n">
-        <v>735</v>
+        <v>-2307</v>
       </c>
       <c r="S141" s="22" t="n">
-        <v>440</v>
-      </c>
-      <c r="T141" s="22" t="n">
-        <v>322</v>
-      </c>
-      <c r="U141" s="22" t="n">
-        <v>241</v>
-      </c>
-      <c r="V141" s="22" t="n">
-        <v>217</v>
-      </c>
-      <c r="W141" s="22" t="n">
-        <v>168</v>
-      </c>
-      <c r="X141" s="22" t="n">
-        <v>142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="20" t="inlineStr">
         <is>
-          <t>자기주식 감소</t>
+          <t>이자 지급</t>
         </is>
       </c>
       <c r="C142" s="22" t="n">
-        <v>-3</v>
+        <v>-60</v>
       </c>
       <c r="D142" s="22" t="n">
+        <v>-81</v>
+      </c>
+      <c r="E142" s="22" t="n">
+        <v>-21</v>
+      </c>
+      <c r="F142" s="22" t="n">
+        <v>-45</v>
+      </c>
+      <c r="G142" s="22" t="n">
+        <v>-70</v>
+      </c>
+      <c r="H142" s="22" t="n">
+        <v>-94</v>
+      </c>
+      <c r="I142" s="22" t="n">
+        <v>-52</v>
+      </c>
+      <c r="J142" s="22" t="n">
+        <v>-165</v>
+      </c>
+      <c r="K142" s="22" t="n">
+        <v>-286</v>
+      </c>
+      <c r="L142" s="22" t="n">
+        <v>-429</v>
+      </c>
+      <c r="M142" s="22" t="n">
+        <v>-144</v>
+      </c>
+      <c r="N142" s="22" t="n">
+        <v>-285</v>
+      </c>
+      <c r="Q142" s="22" t="n">
         <v>-5</v>
       </c>
-      <c r="E142" s="22" t="n">
-        <v>-3</v>
-      </c>
-      <c r="F142" s="22" t="n">
-        <v>-5</v>
-      </c>
-      <c r="G142" s="22" t="n">
-        <v>-9</v>
-      </c>
-      <c r="H142" s="22" t="n">
-        <v>-10</v>
-      </c>
-      <c r="I142" s="22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J142" s="22" t="n">
-        <v>-2</v>
-      </c>
-      <c r="K142" s="22" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L142" s="22" t="n">
-        <v>-6</v>
-      </c>
-      <c r="M142" s="22" t="n">
-        <v>-2</v>
-      </c>
-      <c r="N142" s="22" t="n">
-        <v>-3932</v>
-      </c>
-      <c r="Q142" s="22" t="n">
-        <v>-19</v>
-      </c>
       <c r="R142" s="22" t="n">
-        <v>-25</v>
+        <v>-27</v>
       </c>
       <c r="S142" s="22" t="n">
-        <v>-30</v>
+        <v>-34</v>
       </c>
       <c r="T142" s="22" t="n">
-        <v>-8</v>
+        <v>-48</v>
       </c>
       <c r="U142" s="22" t="n">
-        <v>-5</v>
+        <v>-58</v>
       </c>
       <c r="V142" s="22" t="n">
-        <v>-5</v>
+        <v>-81</v>
       </c>
       <c r="W142" s="22" t="n">
-        <v>-10</v>
+        <v>-94</v>
       </c>
       <c r="X142" s="22" t="n">
-        <v>-6</v>
+        <v>-429</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="20" t="inlineStr">
         <is>
-          <t>기타재무활동</t>
-        </is>
+          <t>리스부채 지급</t>
+        </is>
+      </c>
+      <c r="C143" s="22" t="n">
+        <v>-5908</v>
       </c>
       <c r="D143" s="22" t="n">
+        <v>-7868</v>
+      </c>
+      <c r="E143" s="22" t="n">
+        <v>-1962</v>
+      </c>
+      <c r="F143" s="22" t="n">
+        <v>-4014</v>
+      </c>
+      <c r="G143" s="22" t="n">
+        <v>-6089</v>
+      </c>
+      <c r="H143" s="22" t="n">
+        <v>-8148</v>
+      </c>
+      <c r="I143" s="22" t="n">
+        <v>-2033</v>
+      </c>
+      <c r="J143" s="22" t="n">
+        <v>-3957</v>
+      </c>
+      <c r="K143" s="22" t="n">
+        <v>-5932</v>
+      </c>
+      <c r="L143" s="22" t="n">
+        <v>-8176</v>
+      </c>
+      <c r="M143" s="22" t="n">
+        <v>-2512</v>
+      </c>
+      <c r="N143" s="22" t="n">
+        <v>-4793</v>
+      </c>
+      <c r="Q143" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H143" s="22" t="n">
-        <v>328</v>
-      </c>
-      <c r="L143" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q143" s="22" t="n">
-        <v>-187</v>
-      </c>
       <c r="R143" s="22" t="n">
-        <v>-16</v>
+        <v>-8861</v>
       </c>
       <c r="S143" s="22" t="n">
-        <v>0</v>
+        <v>-8432</v>
+      </c>
+      <c r="T143" s="22" t="n">
+        <v>-9031</v>
+      </c>
+      <c r="U143" s="22" t="n">
+        <v>-7599</v>
       </c>
       <c r="V143" s="22" t="n">
-        <v>0</v>
+        <v>-7868</v>
       </c>
       <c r="W143" s="22" t="n">
-        <v>328</v>
+        <v>-8148</v>
       </c>
       <c r="X143" s="22" t="n">
-        <v>0</v>
+        <v>-8176</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="9" t="inlineStr">
-        <is>
-          <t>재무활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C144" s="12" t="n">
-        <v>-137031</v>
-      </c>
-      <c r="D144" s="12" t="n">
-        <v>-139331</v>
-      </c>
-      <c r="E144" s="12" t="n">
-        <v>-66872</v>
-      </c>
-      <c r="F144" s="12" t="n">
-        <v>-69469</v>
-      </c>
-      <c r="G144" s="12" t="n">
-        <v>-138975</v>
-      </c>
-      <c r="H144" s="12" t="n">
-        <v>-141006</v>
-      </c>
-      <c r="I144" s="12" t="n">
-        <v>-95378</v>
-      </c>
-      <c r="J144" s="12" t="n">
-        <v>-97843</v>
-      </c>
-      <c r="K144" s="12" t="n">
-        <v>-305632</v>
-      </c>
-      <c r="L144" s="12" t="n">
-        <v>-307886</v>
-      </c>
-      <c r="M144" s="12" t="n">
-        <v>-244584</v>
-      </c>
-      <c r="N144" s="12" t="n">
-        <v>-250874</v>
-      </c>
-      <c r="Q144" s="12" t="n">
-        <v>-35014</v>
-      </c>
-      <c r="R144" s="12" t="n">
-        <v>-66872</v>
-      </c>
-      <c r="S144" s="12" t="n">
-        <v>-99497</v>
-      </c>
-      <c r="T144" s="12" t="n">
-        <v>-107408</v>
-      </c>
-      <c r="U144" s="12" t="n">
-        <v>-145641</v>
-      </c>
-      <c r="V144" s="12" t="n">
-        <v>-139331</v>
-      </c>
-      <c r="W144" s="12" t="n">
-        <v>-141006</v>
-      </c>
-      <c r="X144" s="12" t="n">
-        <v>-307886</v>
+      <c r="A144" s="20" t="inlineStr">
+        <is>
+          <t>배당금 지급 - 지배기업 지분</t>
+        </is>
+      </c>
+      <c r="C144" s="22" t="n">
+        <v>-131226</v>
+      </c>
+      <c r="D144" s="22" t="n">
+        <v>-131594</v>
+      </c>
+      <c r="E144" s="22" t="n">
+        <v>-64960</v>
+      </c>
+      <c r="F144" s="22" t="n">
+        <v>-65500</v>
+      </c>
+      <c r="G144" s="22" t="n">
+        <v>-132959</v>
+      </c>
+      <c r="H144" s="22" t="n">
+        <v>-133249</v>
+      </c>
+      <c r="I144" s="22" t="n">
+        <v>-93408</v>
+      </c>
+      <c r="J144" s="22" t="n">
+        <v>-93846</v>
+      </c>
+      <c r="K144" s="22" t="n">
+        <v>-299542</v>
+      </c>
+      <c r="L144" s="22" t="n">
+        <v>-299419</v>
+      </c>
+      <c r="M144" s="22" t="n">
+        <v>-241990</v>
+      </c>
+      <c r="N144" s="22" t="n">
+        <v>-241925</v>
+      </c>
+      <c r="Q144" s="22" t="n">
+        <v>-35010</v>
+      </c>
+      <c r="R144" s="22" t="n">
+        <v>-56370</v>
+      </c>
+      <c r="S144" s="22" t="n">
+        <v>-91442</v>
+      </c>
+      <c r="T144" s="22" t="n">
+        <v>-98644</v>
+      </c>
+      <c r="U144" s="22" t="n">
+        <v>-138220</v>
+      </c>
+      <c r="V144" s="22" t="n">
+        <v>-131594</v>
+      </c>
+      <c r="W144" s="22" t="n">
+        <v>-133249</v>
+      </c>
+      <c r="X144" s="22" t="n">
+        <v>-299419</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="20" t="inlineStr">
         <is>
-          <t>현금성자산 환산차이</t>
-        </is>
-      </c>
-      <c r="C145" s="22" t="n">
-        <v>3422</v>
-      </c>
-      <c r="D145" s="22" t="n">
-        <v>3202</v>
-      </c>
-      <c r="E145" s="22" t="n">
-        <v>2391</v>
-      </c>
-      <c r="F145" s="22" t="n">
-        <v>5884</v>
-      </c>
-      <c r="G145" s="22" t="n">
-        <v>-486</v>
-      </c>
-      <c r="H145" s="22" t="n">
-        <v>2299</v>
-      </c>
-      <c r="I145" s="22" t="n">
-        <v>-1196</v>
-      </c>
-      <c r="J145" s="22" t="n">
-        <v>2114</v>
-      </c>
-      <c r="K145" s="22" t="n">
-        <v>4238</v>
-      </c>
-      <c r="L145" s="22" t="n">
-        <v>9279</v>
-      </c>
-      <c r="M145" s="22" t="n">
-        <v>130</v>
-      </c>
-      <c r="N145" s="22" t="n">
-        <v>1658</v>
+          <t>배당금 지급 - 비지배지분</t>
+        </is>
       </c>
       <c r="Q145" s="22" t="n">
-        <v>-2215</v>
+        <v>-791</v>
       </c>
       <c r="R145" s="22" t="n">
-        <v>-947</v>
-      </c>
-      <c r="S145" s="22" t="n">
-        <v>1166</v>
-      </c>
-      <c r="T145" s="22" t="n">
-        <v>2128</v>
-      </c>
-      <c r="U145" s="22" t="n">
-        <v>1939</v>
-      </c>
-      <c r="V145" s="22" t="n">
-        <v>3202</v>
-      </c>
-      <c r="W145" s="22" t="n">
-        <v>2299</v>
-      </c>
-      <c r="X145" s="22" t="n">
-        <v>9279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="20" t="inlineStr">
         <is>
+          <t>스톡옵션 행사</t>
+        </is>
+      </c>
+      <c r="C146" s="22" t="n">
+        <v>167</v>
+      </c>
+      <c r="D146" s="22" t="n">
+        <v>217</v>
+      </c>
+      <c r="E146" s="22" t="n">
+        <v>75</v>
+      </c>
+      <c r="F146" s="22" t="n">
+        <v>94</v>
+      </c>
+      <c r="G146" s="22" t="n">
+        <v>152</v>
+      </c>
+      <c r="H146" s="22" t="n">
+        <v>168</v>
+      </c>
+      <c r="I146" s="22" t="n">
+        <v>115</v>
+      </c>
+      <c r="J146" s="22" t="n">
+        <v>126</v>
+      </c>
+      <c r="K146" s="22" t="n">
+        <v>130</v>
+      </c>
+      <c r="L146" s="22" t="n">
+        <v>142</v>
+      </c>
+      <c r="M146" s="22" t="n">
+        <v>62</v>
+      </c>
+      <c r="N146" s="22" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q146" s="22" t="n">
+        <v>996</v>
+      </c>
+      <c r="R146" s="22" t="n">
+        <v>735</v>
+      </c>
+      <c r="S146" s="22" t="n">
+        <v>440</v>
+      </c>
+      <c r="T146" s="22" t="n">
+        <v>322</v>
+      </c>
+      <c r="U146" s="22" t="n">
+        <v>241</v>
+      </c>
+      <c r="V146" s="22" t="n">
+        <v>217</v>
+      </c>
+      <c r="W146" s="22" t="n">
+        <v>168</v>
+      </c>
+      <c r="X146" s="22" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="20" t="inlineStr">
+        <is>
+          <t>자기주식 감소</t>
+        </is>
+      </c>
+      <c r="C147" s="22" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D147" s="22" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E147" s="22" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F147" s="22" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G147" s="22" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H147" s="22" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I147" s="22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J147" s="22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K147" s="22" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L147" s="22" t="n">
+        <v>-6</v>
+      </c>
+      <c r="M147" s="22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N147" s="22" t="n">
+        <v>-3932</v>
+      </c>
+      <c r="Q147" s="22" t="n">
+        <v>-19</v>
+      </c>
+      <c r="R147" s="22" t="n">
+        <v>-25</v>
+      </c>
+      <c r="S147" s="22" t="n">
+        <v>-30</v>
+      </c>
+      <c r="T147" s="22" t="n">
+        <v>-8</v>
+      </c>
+      <c r="U147" s="22" t="n">
+        <v>-5</v>
+      </c>
+      <c r="V147" s="22" t="n">
+        <v>-5</v>
+      </c>
+      <c r="W147" s="22" t="n">
+        <v>-10</v>
+      </c>
+      <c r="X147" s="22" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="20" t="inlineStr">
+        <is>
+          <t>기타재무활동</t>
+        </is>
+      </c>
+      <c r="D148" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" s="22" t="n">
+        <v>328</v>
+      </c>
+      <c r="L148" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q148" s="22" t="n">
+        <v>-187</v>
+      </c>
+      <c r="R148" s="22" t="n">
+        <v>-16</v>
+      </c>
+      <c r="S148" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V148" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W148" s="22" t="n">
+        <v>328</v>
+      </c>
+      <c r="X148" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C149" s="12" t="n">
+        <v>-137031</v>
+      </c>
+      <c r="D149" s="12" t="n">
+        <v>-139331</v>
+      </c>
+      <c r="E149" s="12" t="n">
+        <v>-66872</v>
+      </c>
+      <c r="F149" s="12" t="n">
+        <v>-69469</v>
+      </c>
+      <c r="G149" s="12" t="n">
+        <v>-138975</v>
+      </c>
+      <c r="H149" s="12" t="n">
+        <v>-141006</v>
+      </c>
+      <c r="I149" s="12" t="n">
+        <v>-95378</v>
+      </c>
+      <c r="J149" s="12" t="n">
+        <v>-97843</v>
+      </c>
+      <c r="K149" s="12" t="n">
+        <v>-305632</v>
+      </c>
+      <c r="L149" s="12" t="n">
+        <v>-307886</v>
+      </c>
+      <c r="M149" s="12" t="n">
+        <v>-244584</v>
+      </c>
+      <c r="N149" s="12" t="n">
+        <v>-250874</v>
+      </c>
+      <c r="Q149" s="12" t="n">
+        <v>-35014</v>
+      </c>
+      <c r="R149" s="12" t="n">
+        <v>-66872</v>
+      </c>
+      <c r="S149" s="12" t="n">
+        <v>-99497</v>
+      </c>
+      <c r="T149" s="12" t="n">
+        <v>-107408</v>
+      </c>
+      <c r="U149" s="12" t="n">
+        <v>-145641</v>
+      </c>
+      <c r="V149" s="12" t="n">
+        <v>-139331</v>
+      </c>
+      <c r="W149" s="12" t="n">
+        <v>-141006</v>
+      </c>
+      <c r="X149" s="12" t="n">
+        <v>-307886</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="20" t="inlineStr">
+        <is>
+          <t>현금성자산 환산차이</t>
+        </is>
+      </c>
+      <c r="C150" s="22" t="n">
+        <v>3422</v>
+      </c>
+      <c r="D150" s="22" t="n">
+        <v>3202</v>
+      </c>
+      <c r="E150" s="22" t="n">
+        <v>2391</v>
+      </c>
+      <c r="F150" s="22" t="n">
+        <v>5884</v>
+      </c>
+      <c r="G150" s="22" t="n">
+        <v>-486</v>
+      </c>
+      <c r="H150" s="22" t="n">
+        <v>2299</v>
+      </c>
+      <c r="I150" s="22" t="n">
+        <v>-1196</v>
+      </c>
+      <c r="J150" s="22" t="n">
+        <v>2114</v>
+      </c>
+      <c r="K150" s="22" t="n">
+        <v>4238</v>
+      </c>
+      <c r="L150" s="22" t="n">
+        <v>9279</v>
+      </c>
+      <c r="M150" s="22" t="n">
+        <v>130</v>
+      </c>
+      <c r="N150" s="22" t="n">
+        <v>1658</v>
+      </c>
+      <c r="Q150" s="22" t="n">
+        <v>-2215</v>
+      </c>
+      <c r="R150" s="22" t="n">
+        <v>-947</v>
+      </c>
+      <c r="S150" s="22" t="n">
+        <v>1166</v>
+      </c>
+      <c r="T150" s="22" t="n">
+        <v>2128</v>
+      </c>
+      <c r="U150" s="22" t="n">
+        <v>1939</v>
+      </c>
+      <c r="V150" s="22" t="n">
+        <v>3202</v>
+      </c>
+      <c r="W150" s="22" t="n">
+        <v>2299</v>
+      </c>
+      <c r="X150" s="22" t="n">
+        <v>9279</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="20" t="inlineStr">
+        <is>
           <t>현금및현금성자산 증감액</t>
         </is>
       </c>
-      <c r="C146" s="22" t="n">
+      <c r="C151" s="22" t="n">
         <v>109172</v>
       </c>
-      <c r="D146" s="22" t="n">
+      <c r="D151" s="22" t="n">
         <v>236505</v>
       </c>
-      <c r="E146" s="22" t="n">
+      <c r="E151" s="22" t="n">
         <v>4189</v>
       </c>
-      <c r="F146" s="22" t="n">
+      <c r="F151" s="22" t="n">
         <v>-64913</v>
       </c>
-      <c r="G146" s="22" t="n">
+      <c r="G151" s="22" t="n">
         <v>-54716</v>
       </c>
-      <c r="H146" s="22" t="n">
+      <c r="H151" s="22" t="n">
         <v>81528</v>
       </c>
-      <c r="I146" s="22" t="n">
+      <c r="I151" s="22" t="n">
         <v>-116783</v>
       </c>
-      <c r="J146" s="22" t="n">
+      <c r="J151" s="22" t="n">
         <v>-43114</v>
       </c>
-      <c r="K146" s="22" t="n">
+      <c r="K151" s="22" t="n">
         <v>-83770</v>
       </c>
-      <c r="L146" s="22" t="n">
+      <c r="L151" s="22" t="n">
         <v>-113600</v>
       </c>
-      <c r="M146" s="22" t="n">
+      <c r="M151" s="22" t="n">
         <v>-8618</v>
       </c>
-      <c r="N146" s="22" t="n">
+      <c r="N151" s="22" t="n">
         <v>-36163</v>
       </c>
-      <c r="Q146" s="22" t="n">
+      <c r="Q151" s="22" t="n">
         <v>7785</v>
       </c>
-      <c r="R146" s="22" t="n">
+      <c r="R151" s="22" t="n">
         <v>57081</v>
       </c>
-      <c r="S146" s="22" t="n">
+      <c r="S151" s="22" t="n">
         <v>8393</v>
       </c>
-      <c r="T146" s="22" t="n">
+      <c r="T151" s="22" t="n">
         <v>55419</v>
       </c>
-      <c r="U146" s="22" t="n">
+      <c r="U151" s="22" t="n">
         <v>-45584</v>
       </c>
-      <c r="V146" s="22" t="n">
+      <c r="V151" s="22" t="n">
         <v>236505</v>
       </c>
-      <c r="W146" s="22" t="n">
+      <c r="W151" s="22" t="n">
         <v>81528</v>
       </c>
-      <c r="X146" s="22" t="n">
+      <c r="X151" s="22" t="n">
         <v>-113600</v>
       </c>
     </row>
@@ -9517,7 +9860,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -9541,27 +9884,27 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>2024.4Q</t>
+          <t>2025.2Q</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>2025.1Q</t>
+          <t>2025.3Q</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>2025.2Q</t>
+          <t>2025.4Q</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>2025.3Q</t>
+          <t>2026.1Q</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>2025.4Q</t>
+          <t>2026.2Q</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
@@ -9616,13 +9959,19 @@
       </c>
       <c r="B5" s="10" t="n"/>
       <c r="C5" s="11" t="n">
-        <v>1606043</v>
-      </c>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="12" t="n"/>
-      <c r="F5" s="12" t="n"/>
+        <v>1619532</v>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>1517730</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>1740758</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>1539441</v>
+      </c>
       <c r="G5" s="12" t="n">
-        <v>1740758</v>
+        <v>1704189</v>
       </c>
       <c r="H5" s="11" t="n">
         <v>1063661</v>
@@ -9648,13 +9997,19 @@
       </c>
       <c r="B6" s="10" t="n"/>
       <c r="C6" s="21" t="n">
-        <v>540202</v>
-      </c>
-      <c r="D6" s="22" t="n"/>
-      <c r="E6" s="22" t="n"/>
-      <c r="F6" s="22" t="n"/>
+        <v>497088</v>
+      </c>
+      <c r="D6" s="22" t="n">
+        <v>456432</v>
+      </c>
+      <c r="E6" s="22" t="n">
+        <v>426602</v>
+      </c>
+      <c r="F6" s="22" t="n">
+        <v>417984</v>
+      </c>
       <c r="G6" s="22" t="n">
-        <v>426602</v>
+        <v>390439</v>
       </c>
       <c r="H6" s="21" t="n">
         <v>267753</v>
@@ -9698,13 +10053,19 @@
       </c>
       <c r="B8" s="10" t="n"/>
       <c r="C8" s="21" t="n">
-        <v>334256</v>
-      </c>
-      <c r="D8" s="22" t="n"/>
-      <c r="E8" s="22" t="n"/>
-      <c r="F8" s="22" t="n"/>
+        <v>316747</v>
+      </c>
+      <c r="D8" s="22" t="n">
+        <v>353649</v>
+      </c>
+      <c r="E8" s="22" t="n">
+        <v>442876</v>
+      </c>
+      <c r="F8" s="22" t="n">
+        <v>352747</v>
+      </c>
       <c r="G8" s="22" t="n">
-        <v>442876</v>
+        <v>381845</v>
       </c>
       <c r="H8" s="21" t="n">
         <v>355081</v>
@@ -9730,13 +10091,19 @@
       </c>
       <c r="B9" s="10" t="n"/>
       <c r="C9" s="21" t="n">
-        <v>240067</v>
-      </c>
-      <c r="D9" s="22" t="n"/>
-      <c r="E9" s="22" t="n"/>
-      <c r="F9" s="22" t="n"/>
+        <v>235526</v>
+      </c>
+      <c r="D9" s="22" t="n">
+        <v>246326</v>
+      </c>
+      <c r="E9" s="22" t="n">
+        <v>276848</v>
+      </c>
+      <c r="F9" s="22" t="n">
+        <v>288289</v>
+      </c>
       <c r="G9" s="22" t="n">
-        <v>276848</v>
+        <v>317580</v>
       </c>
       <c r="H9" s="21" t="n">
         <v>208838</v>
@@ -9814,13 +10181,19 @@
       </c>
       <c r="B11" s="10" t="n"/>
       <c r="C11" s="11" t="n">
-        <v>602330</v>
-      </c>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
+        <v>658814</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>665859</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>727837</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>725660</v>
+      </c>
       <c r="G11" s="12" t="n">
-        <v>727837</v>
+        <v>745725</v>
       </c>
       <c r="H11" s="11" t="n">
         <v>475033</v>
@@ -9846,13 +10219,19 @@
       </c>
       <c r="B12" s="10" t="n"/>
       <c r="C12" s="21" t="n">
-        <v>433129</v>
-      </c>
-      <c r="D12" s="22" t="n"/>
-      <c r="E12" s="22" t="n"/>
-      <c r="F12" s="22" t="n"/>
+        <v>456755</v>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>449610</v>
+      </c>
+      <c r="E12" s="22" t="n">
+        <v>456578</v>
+      </c>
+      <c r="F12" s="22" t="n">
+        <v>459516</v>
+      </c>
       <c r="G12" s="22" t="n">
-        <v>456578</v>
+        <v>481623</v>
       </c>
       <c r="H12" s="21" t="n">
         <v>338841</v>
@@ -9878,13 +10257,19 @@
       </c>
       <c r="B13" s="10" t="n"/>
       <c r="C13" s="21" t="n">
-        <v>17868</v>
-      </c>
-      <c r="D13" s="22" t="n"/>
-      <c r="E13" s="22" t="n"/>
-      <c r="F13" s="22" t="n"/>
+        <v>33292</v>
+      </c>
+      <c r="D13" s="22" t="n">
+        <v>34164</v>
+      </c>
+      <c r="E13" s="22" t="n">
+        <v>54539</v>
+      </c>
+      <c r="F13" s="22" t="n">
+        <v>58495</v>
+      </c>
       <c r="G13" s="22" t="n">
-        <v>54539</v>
+        <v>59277</v>
       </c>
       <c r="H13" s="21" t="n">
         <v>21974</v>
@@ -9980,13 +10365,19 @@
       </c>
       <c r="B16" s="10" t="n"/>
       <c r="C16" s="11" t="n">
-        <v>2208373</v>
-      </c>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12" t="n"/>
+        <v>2278347</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>2183588</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>2468595</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>2265101</v>
+      </c>
       <c r="G16" s="12" t="n">
-        <v>2468595</v>
+        <v>2449914</v>
       </c>
       <c r="H16" s="11" t="n">
         <v>1538694</v>
@@ -10030,13 +10421,19 @@
       </c>
       <c r="B18" s="10" t="n"/>
       <c r="C18" s="11" t="n">
-        <v>290357</v>
-      </c>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
+        <v>268276</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>267423</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>411077</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>327702</v>
+      </c>
       <c r="G18" s="12" t="n">
-        <v>411077</v>
+        <v>392189</v>
       </c>
       <c r="H18" s="11" t="n">
         <v>327422</v>
@@ -10062,13 +10459,19 @@
       </c>
       <c r="B19" s="10" t="n"/>
       <c r="C19" s="21" t="n">
-        <v>65353</v>
-      </c>
-      <c r="D19" s="22" t="n"/>
-      <c r="E19" s="22" t="n"/>
-      <c r="F19" s="22" t="n"/>
+        <v>78417</v>
+      </c>
+      <c r="D19" s="22" t="n">
+        <v>78897</v>
+      </c>
+      <c r="E19" s="22" t="n">
+        <v>127247</v>
+      </c>
+      <c r="F19" s="22" t="n">
+        <v>107524</v>
+      </c>
       <c r="G19" s="22" t="n">
-        <v>127247</v>
+        <v>160700</v>
       </c>
       <c r="H19" s="21" t="n">
         <v>152266</v>
@@ -10182,13 +10585,19 @@
       </c>
       <c r="B23" s="10" t="n"/>
       <c r="C23" s="11" t="n">
-        <v>16516</v>
-      </c>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="12" t="n"/>
-      <c r="F23" s="12" t="n"/>
+        <v>24943</v>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>26058</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>31785</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>29684</v>
+      </c>
       <c r="G23" s="12" t="n">
-        <v>31785</v>
+        <v>30063</v>
       </c>
       <c r="H23" s="11" t="n">
         <v>23255</v>
@@ -10302,13 +10711,19 @@
       </c>
       <c r="B27" s="10" t="n"/>
       <c r="C27" s="11" t="n">
-        <v>306873</v>
-      </c>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="12" t="n"/>
-      <c r="F27" s="12" t="n"/>
+        <v>293219</v>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>293481</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>442862</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>357386</v>
+      </c>
       <c r="G27" s="12" t="n">
-        <v>442862</v>
+        <v>422251</v>
       </c>
       <c r="H27" s="11" t="n">
         <v>350677</v>
@@ -10456,13 +10871,19 @@
       </c>
       <c r="B31" s="10" t="n"/>
       <c r="C31" s="11" t="n">
-        <v>1901499</v>
-      </c>
-      <c r="D31" s="12" t="n"/>
-      <c r="E31" s="12" t="n"/>
-      <c r="F31" s="12" t="n"/>
+        <v>1985127</v>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>1890107</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>2025732</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>1907715</v>
+      </c>
       <c r="G31" s="12" t="n">
-        <v>2025732</v>
+        <v>2027663</v>
       </c>
       <c r="H31" s="11" t="n">
         <v>1188017</v>
@@ -10542,13 +10963,19 @@
       </c>
       <c r="B35" s="10" t="n"/>
       <c r="C35" s="11" t="n">
-        <v>1901499</v>
-      </c>
-      <c r="D35" s="12" t="n"/>
-      <c r="E35" s="12" t="n"/>
-      <c r="F35" s="12" t="n"/>
+        <v>1985127</v>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>1890107</v>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>2025732</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>1907715</v>
+      </c>
       <c r="G35" s="12" t="n">
-        <v>2025732</v>
+        <v>2027663</v>
       </c>
       <c r="H35" s="11" t="n">
         <v>1188017</v>
@@ -10596,19 +11023,19 @@
       </c>
       <c r="B37" s="10" t="n"/>
       <c r="C37" s="11" t="n">
-        <v>447600</v>
+        <v>462121</v>
       </c>
       <c r="D37" s="12" t="n">
-        <v>413364</v>
+        <v>409567</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>462121</v>
+        <v>386280</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>409567</v>
+        <v>441643</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>386280</v>
+        <v>449298</v>
       </c>
       <c r="H37" s="11" t="n">
         <v>279626</v>
@@ -10638,19 +11065,19 @@
         </is>
       </c>
       <c r="C38" s="21" t="n">
-        <v>54389</v>
+        <v>84983</v>
       </c>
       <c r="D38" s="22" t="n">
-        <v>64454</v>
+        <v>77597</v>
       </c>
       <c r="E38" s="22" t="n">
-        <v>84983</v>
+        <v>111607</v>
       </c>
       <c r="F38" s="22" t="n">
-        <v>77597</v>
+        <v>109628</v>
       </c>
       <c r="G38" s="22" t="n">
-        <v>111607</v>
+        <v>77571</v>
       </c>
       <c r="H38" s="21" t="n">
         <v>72866</v>
@@ -10728,19 +11155,19 @@
         </is>
       </c>
       <c r="C40" s="21" t="n">
-        <v>133249</v>
+        <v>161595</v>
       </c>
       <c r="D40" s="22" t="n">
-        <v>161697</v>
+        <v>299832</v>
       </c>
       <c r="E40" s="22" t="n">
-        <v>161595</v>
+        <v>299419</v>
       </c>
       <c r="F40" s="22" t="n">
-        <v>299832</v>
+        <v>448001</v>
       </c>
       <c r="G40" s="22" t="n">
-        <v>299419</v>
+        <v>447498</v>
       </c>
       <c r="H40" s="21" t="n">
         <v>98644</v>
@@ -10799,7 +11226,7 @@
       <c r="L42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="46" t="inlineStr">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -10851,7 +11278,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="46" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -10903,7 +11330,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -10955,7 +11382,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="46" t="inlineStr">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -11007,7 +11434,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="46" t="inlineStr">
+      <c r="A47" s="47" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -11059,7 +11486,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="46" t="inlineStr">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -11070,23 +11497,23 @@
         </is>
       </c>
       <c r="C48" s="32">
-        <f>IFERROR((IF(COUNT('연간'!E16:H16)&lt;4,"",SUM('연간'!E16:H16)))/(IF(COUNT('연간'!E38:H38)&lt;4,"",SUM('연간'!E38:H38))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!G16:J16)&lt;4,"",SUM('연간'!G16:J16)))/(IF(COUNT('연간'!G38:J38)&lt;4,"",SUM('연간'!G38:J38))),"")</f>
         <v/>
       </c>
       <c r="D48" s="33">
-        <f>IFERROR((IF(COUNT('연간'!F16:I16)&lt;4,"",SUM('연간'!F16:I16)))/(IF(COUNT('연간'!F38:I38)&lt;4,"",SUM('연간'!F38:I38))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!H16:K16)&lt;4,"",SUM('연간'!H16:K16)))/(IF(COUNT('연간'!H38:K38)&lt;4,"",SUM('연간'!H38:K38))),"")</f>
         <v/>
       </c>
       <c r="E48" s="33">
-        <f>IFERROR((IF(COUNT('연간'!G16:J16)&lt;4,"",SUM('연간'!G16:J16)))/(IF(COUNT('연간'!G38:J38)&lt;4,"",SUM('연간'!G38:J38))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!I16:L16)&lt;4,"",SUM('연간'!I16:L16)))/(IF(COUNT('연간'!I38:L38)&lt;4,"",SUM('연간'!I38:L38))),"")</f>
         <v/>
       </c>
       <c r="F48" s="33">
-        <f>IFERROR((IF(COUNT('연간'!H16:K16)&lt;4,"",SUM('연간'!H16:K16)))/(IF(COUNT('연간'!H38:K38)&lt;4,"",SUM('연간'!H38:K38))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!J16:M16)&lt;4,"",SUM('연간'!J16:M16)))/(IF(COUNT('연간'!J38:M38)&lt;4,"",SUM('연간'!J38:M38))),"")</f>
         <v/>
       </c>
       <c r="G48" s="33">
-        <f>IFERROR((IF(COUNT('연간'!I16:L16)&lt;4,"",SUM('연간'!I16:L16)))/(IF(COUNT('연간'!I38:L38)&lt;4,"",SUM('연간'!I38:L38))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!K16:N16)&lt;4,"",SUM('연간'!K16:N16)))/(IF(COUNT('연간'!K38:N38)&lt;4,"",SUM('연간'!K38:N38))),"")</f>
         <v/>
       </c>
       <c r="H48" s="32">
@@ -11111,7 +11538,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="46" t="inlineStr">
+      <c r="A49" s="47" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -11121,43 +11548,43 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="47">
-        <f>IFERROR(IF((IF(COUNT('연간'!E44:H44)&lt;4,"",SUM('연간'!E44:H44)))&lt;=0,"적자",C28/(IF(COUNT('연간'!E44:H44)&lt;4,"",SUM('연간'!E44:H44)))),"")</f>
-        <v/>
-      </c>
-      <c r="D49" s="48">
-        <f>IFERROR(IF((IF(COUNT('연간'!F44:I44)&lt;4,"",SUM('연간'!F44:I44)))&lt;=0,"적자",D28/(IF(COUNT('연간'!F44:I44)&lt;4,"",SUM('연간'!F44:I44)))),"")</f>
-        <v/>
-      </c>
-      <c r="E49" s="48">
-        <f>IFERROR(IF((IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))&lt;=0,"적자",E28/(IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))),"")</f>
-        <v/>
-      </c>
-      <c r="F49" s="48">
-        <f>IFERROR(IF((IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))&lt;=0,"적자",F28/(IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))),"")</f>
-        <v/>
-      </c>
-      <c r="G49" s="48">
-        <f>IFERROR(IF((IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))&lt;=0,"적자",G28/(IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))),"")</f>
-        <v/>
-      </c>
-      <c r="H49" s="47">
+      <c r="C49" s="48">
+        <f>IFERROR(IF((IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))),"")</f>
+        <v/>
+      </c>
+      <c r="D49" s="49">
+        <f>IFERROR(IF((IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))),"")</f>
+        <v/>
+      </c>
+      <c r="E49" s="49">
+        <f>IFERROR(IF((IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))),"")</f>
+        <v/>
+      </c>
+      <c r="F49" s="49">
+        <f>IFERROR(IF((IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))),"")</f>
+        <v/>
+      </c>
+      <c r="G49" s="49">
+        <f>IFERROR(IF((IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))),"")</f>
+        <v/>
+      </c>
+      <c r="H49" s="48">
         <f>IFERROR(IF(('연간'!T44)&lt;=0,"적자",H28/('연간'!T44)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="48">
+      <c r="I49" s="49">
         <f>IFERROR(IF(('연간'!U44)&lt;=0,"적자",I28/('연간'!U44)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="48">
+      <c r="J49" s="49">
         <f>IFERROR(IF(('연간'!V44)&lt;=0,"적자",J28/('연간'!V44)),"")</f>
         <v/>
       </c>
-      <c r="K49" s="48">
+      <c r="K49" s="49">
         <f>IFERROR(IF(('연간'!W44)&lt;=0,"적자",K28/('연간'!W44)),"")</f>
         <v/>
       </c>
-      <c r="L49" s="48">
+      <c r="L49" s="49">
         <f>IFERROR(IF(('연간'!X44)&lt;=0,"적자",L28/('연간'!X44)),"")</f>
         <v/>
       </c>
@@ -11181,7 +11608,7 @@
       <c r="L50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="46" t="inlineStr">
+      <c r="A51" s="47" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -11192,23 +11619,23 @@
         </is>
       </c>
       <c r="C51" s="37">
-        <f>IFERROR((IF(COUNT('연간'!E44:H44)&lt;4,"",SUM('연간'!E44:H44)))/C31,"")</f>
+        <f>IFERROR((IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))/C31,"")</f>
         <v/>
       </c>
       <c r="D51" s="38">
-        <f>IFERROR((IF(COUNT('연간'!F44:I44)&lt;4,"",SUM('연간'!F44:I44)))/D31,"")</f>
+        <f>IFERROR((IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))/D31,"")</f>
         <v/>
       </c>
       <c r="E51" s="38">
-        <f>IFERROR((IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))/E31,"")</f>
+        <f>IFERROR((IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))/E31,"")</f>
         <v/>
       </c>
       <c r="F51" s="38">
-        <f>IFERROR((IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))/F31,"")</f>
+        <f>IFERROR((IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))/F31,"")</f>
         <v/>
       </c>
       <c r="G51" s="38">
-        <f>IFERROR((IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))/G31,"")</f>
+        <f>IFERROR((IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))/G31,"")</f>
         <v/>
       </c>
       <c r="H51" s="37">
@@ -11233,7 +11660,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="46" t="inlineStr">
+      <c r="A52" s="47" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -11244,23 +11671,23 @@
         </is>
       </c>
       <c r="C52" s="37">
-        <f>IFERROR((IF(COUNT('연간'!E43:H43)&lt;4,"",SUM('연간'!E43:H43)))/C16,"")</f>
+        <f>IFERROR((IF(COUNT('연간'!G43:J43)&lt;4,"",SUM('연간'!G43:J43)))/C16,"")</f>
         <v/>
       </c>
       <c r="D52" s="38">
-        <f>IFERROR((IF(COUNT('연간'!F43:I43)&lt;4,"",SUM('연간'!F43:I43)))/D16,"")</f>
+        <f>IFERROR((IF(COUNT('연간'!H43:K43)&lt;4,"",SUM('연간'!H43:K43)))/D16,"")</f>
         <v/>
       </c>
       <c r="E52" s="38">
-        <f>IFERROR((IF(COUNT('연간'!G43:J43)&lt;4,"",SUM('연간'!G43:J43)))/E16,"")</f>
+        <f>IFERROR((IF(COUNT('연간'!I43:L43)&lt;4,"",SUM('연간'!I43:L43)))/E16,"")</f>
         <v/>
       </c>
       <c r="F52" s="38">
-        <f>IFERROR((IF(COUNT('연간'!H43:K43)&lt;4,"",SUM('연간'!H43:K43)))/F16,"")</f>
+        <f>IFERROR((IF(COUNT('연간'!J43:M43)&lt;4,"",SUM('연간'!J43:M43)))/F16,"")</f>
         <v/>
       </c>
       <c r="G52" s="38">
-        <f>IFERROR((IF(COUNT('연간'!I43:L43)&lt;4,"",SUM('연간'!I43:L43)))/G16,"")</f>
+        <f>IFERROR((IF(COUNT('연간'!K43:N43)&lt;4,"",SUM('연간'!K43:N43)))/G16,"")</f>
         <v/>
       </c>
       <c r="H52" s="37">
@@ -11285,7 +11712,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="46" t="inlineStr">
+      <c r="A53" s="47" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -11296,23 +11723,23 @@
         </is>
       </c>
       <c r="C53" s="37">
-        <f>IFERROR((IF(COUNT('연간'!E16:H16)&lt;4,"",SUM('연간'!E16:H16)))*(1-0.3)/(C35+C29),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!G16:J16)&lt;4,"",SUM('연간'!G16:J16)))*(1-0.3)/(C35+C29),"")</f>
         <v/>
       </c>
       <c r="D53" s="38">
-        <f>IFERROR((IF(COUNT('연간'!F16:I16)&lt;4,"",SUM('연간'!F16:I16)))*(1-0.3)/(D35+D29),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!H16:K16)&lt;4,"",SUM('연간'!H16:K16)))*(1-0.3)/(D35+D29),"")</f>
         <v/>
       </c>
       <c r="E53" s="38">
-        <f>IFERROR((IF(COUNT('연간'!G16:J16)&lt;4,"",SUM('연간'!G16:J16)))*(1-0.3)/(E35+E29),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!I16:L16)&lt;4,"",SUM('연간'!I16:L16)))*(1-0.3)/(E35+E29),"")</f>
         <v/>
       </c>
       <c r="F53" s="38">
-        <f>IFERROR((IF(COUNT('연간'!H16:K16)&lt;4,"",SUM('연간'!H16:K16)))*(1-0.3)/(F35+F29),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!J16:M16)&lt;4,"",SUM('연간'!J16:M16)))*(1-0.3)/(F35+F29),"")</f>
         <v/>
       </c>
       <c r="G53" s="38">
-        <f>IFERROR((IF(COUNT('연간'!I16:L16)&lt;4,"",SUM('연간'!I16:L16)))*(1-0.3)/(G35+G29),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!K16:N16)&lt;4,"",SUM('연간'!K16:N16)))*(1-0.3)/(G35+G29),"")</f>
         <v/>
       </c>
       <c r="H53" s="37">
@@ -11337,7 +11764,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="46" t="inlineStr">
+      <c r="A54" s="47" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -11348,23 +11775,23 @@
         </is>
       </c>
       <c r="C54" s="37">
-        <f>IFERROR((IF(COUNT('연간'!E12:H12)&lt;4,"",SUM('연간'!E12:H12)))/(IF(COUNT('연간'!E4:H4)&lt;4,"",SUM('연간'!E4:H4))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!G12:J12)&lt;4,"",SUM('연간'!G12:J12)))/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4))),"")</f>
         <v/>
       </c>
       <c r="D54" s="38">
-        <f>IFERROR((IF(COUNT('연간'!F12:I12)&lt;4,"",SUM('연간'!F12:I12)))/(IF(COUNT('연간'!F4:I4)&lt;4,"",SUM('연간'!F4:I4))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!H12:K12)&lt;4,"",SUM('연간'!H12:K12)))/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4))),"")</f>
         <v/>
       </c>
       <c r="E54" s="38">
-        <f>IFERROR((IF(COUNT('연간'!G12:J12)&lt;4,"",SUM('연간'!G12:J12)))/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!I12:L12)&lt;4,"",SUM('연간'!I12:L12)))/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4))),"")</f>
         <v/>
       </c>
       <c r="F54" s="38">
-        <f>IFERROR((IF(COUNT('연간'!H12:K12)&lt;4,"",SUM('연간'!H12:K12)))/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!J12:M12)&lt;4,"",SUM('연간'!J12:M12)))/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4))),"")</f>
         <v/>
       </c>
       <c r="G54" s="38">
-        <f>IFERROR((IF(COUNT('연간'!I12:L12)&lt;4,"",SUM('연간'!I12:L12)))/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!K12:N12)&lt;4,"",SUM('연간'!K12:N12)))/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4))),"")</f>
         <v/>
       </c>
       <c r="H54" s="37">
@@ -11389,7 +11816,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="46" t="inlineStr">
+      <c r="A55" s="47" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -11400,23 +11827,23 @@
         </is>
       </c>
       <c r="C55" s="37">
-        <f>IFERROR((IF(COUNT('연간'!E16:H16)&lt;4,"",SUM('연간'!E16:H16)))/(IF(COUNT('연간'!E4:H4)&lt;4,"",SUM('연간'!E4:H4))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!G16:J16)&lt;4,"",SUM('연간'!G16:J16)))/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4))),"")</f>
         <v/>
       </c>
       <c r="D55" s="38">
-        <f>IFERROR((IF(COUNT('연간'!F16:I16)&lt;4,"",SUM('연간'!F16:I16)))/(IF(COUNT('연간'!F4:I4)&lt;4,"",SUM('연간'!F4:I4))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!H16:K16)&lt;4,"",SUM('연간'!H16:K16)))/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4))),"")</f>
         <v/>
       </c>
       <c r="E55" s="38">
-        <f>IFERROR((IF(COUNT('연간'!G16:J16)&lt;4,"",SUM('연간'!G16:J16)))/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!I16:L16)&lt;4,"",SUM('연간'!I16:L16)))/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4))),"")</f>
         <v/>
       </c>
       <c r="F55" s="38">
-        <f>IFERROR((IF(COUNT('연간'!H16:K16)&lt;4,"",SUM('연간'!H16:K16)))/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!J16:M16)&lt;4,"",SUM('연간'!J16:M16)))/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4))),"")</f>
         <v/>
       </c>
       <c r="G55" s="38">
-        <f>IFERROR((IF(COUNT('연간'!I16:L16)&lt;4,"",SUM('연간'!I16:L16)))/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!K16:N16)&lt;4,"",SUM('연간'!K16:N16)))/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4))),"")</f>
         <v/>
       </c>
       <c r="H55" s="37">
@@ -11441,7 +11868,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="46" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -11452,23 +11879,23 @@
         </is>
       </c>
       <c r="C56" s="37">
-        <f>IFERROR((IF(COUNT('연간'!E43:H43)&lt;4,"",SUM('연간'!E43:H43)))/(IF(COUNT('연간'!E4:H4)&lt;4,"",SUM('연간'!E4:H4))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!G43:J43)&lt;4,"",SUM('연간'!G43:J43)))/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4))),"")</f>
         <v/>
       </c>
       <c r="D56" s="38">
-        <f>IFERROR((IF(COUNT('연간'!F43:I43)&lt;4,"",SUM('연간'!F43:I43)))/(IF(COUNT('연간'!F4:I4)&lt;4,"",SUM('연간'!F4:I4))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!H43:K43)&lt;4,"",SUM('연간'!H43:K43)))/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4))),"")</f>
         <v/>
       </c>
       <c r="E56" s="38">
-        <f>IFERROR((IF(COUNT('연간'!G43:J43)&lt;4,"",SUM('연간'!G43:J43)))/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!I43:L43)&lt;4,"",SUM('연간'!I43:L43)))/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4))),"")</f>
         <v/>
       </c>
       <c r="F56" s="38">
-        <f>IFERROR((IF(COUNT('연간'!H43:K43)&lt;4,"",SUM('연간'!H43:K43)))/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!J43:M43)&lt;4,"",SUM('연간'!J43:M43)))/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4))),"")</f>
         <v/>
       </c>
       <c r="G56" s="38">
-        <f>IFERROR((IF(COUNT('연간'!I43:L43)&lt;4,"",SUM('연간'!I43:L43)))/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!K43:N43)&lt;4,"",SUM('연간'!K43:N43)))/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4))),"")</f>
         <v/>
       </c>
       <c r="H56" s="37">
@@ -11511,7 +11938,7 @@
       <c r="L57" s="25" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="46" t="inlineStr">
+      <c r="A58" s="47" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -11522,23 +11949,23 @@
         </is>
       </c>
       <c r="C58" s="32">
-        <f>IFERROR((IF(COUNT('연간'!E4:H4)&lt;4,"",SUM('연간'!E4:H4)))/C16,"")</f>
+        <f>IFERROR((IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))/C16,"")</f>
         <v/>
       </c>
       <c r="D58" s="33">
-        <f>IFERROR((IF(COUNT('연간'!F4:I4)&lt;4,"",SUM('연간'!F4:I4)))/D16,"")</f>
+        <f>IFERROR((IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))/D16,"")</f>
         <v/>
       </c>
       <c r="E58" s="33">
-        <f>IFERROR((IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))/E16,"")</f>
+        <f>IFERROR((IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))/E16,"")</f>
         <v/>
       </c>
       <c r="F58" s="33">
-        <f>IFERROR((IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))/F16,"")</f>
+        <f>IFERROR((IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))/F16,"")</f>
         <v/>
       </c>
       <c r="G58" s="33">
-        <f>IFERROR((IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))/G16,"")</f>
+        <f>IFERROR((IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))/G16,"")</f>
         <v/>
       </c>
       <c r="H58" s="32">
@@ -11563,7 +11990,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="46" t="inlineStr">
+      <c r="A59" s="47" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -11573,49 +12000,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="49">
-        <f>IFERROR(C8/(IF(COUNT('연간'!E4:H4)&lt;4,"",SUM('연간'!E4:H4)))*365,"")</f>
-        <v/>
-      </c>
-      <c r="D59" s="50">
-        <f>IFERROR(D8/(IF(COUNT('연간'!F4:I4)&lt;4,"",SUM('연간'!F4:I4)))*365,"")</f>
-        <v/>
-      </c>
-      <c r="E59" s="50">
-        <f>IFERROR(E8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
-        <v/>
-      </c>
-      <c r="F59" s="50">
-        <f>IFERROR(F8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
-        <v/>
-      </c>
-      <c r="G59" s="50">
-        <f>IFERROR(G8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
-        <v/>
-      </c>
-      <c r="H59" s="49">
+      <c r="C59" s="50">
+        <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
+        <v/>
+      </c>
+      <c r="D59" s="51">
+        <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
+        <v/>
+      </c>
+      <c r="E59" s="51">
+        <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
+        <v/>
+      </c>
+      <c r="F59" s="51">
+        <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
+        <v/>
+      </c>
+      <c r="G59" s="51">
+        <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
+        <v/>
+      </c>
+      <c r="H59" s="50">
         <f>IFERROR(H8/('연간'!T4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="50">
+      <c r="I59" s="51">
         <f>IFERROR(I8/('연간'!U4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="50">
+      <c r="J59" s="51">
         <f>IFERROR(J8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="K59" s="50">
+      <c r="K59" s="51">
         <f>IFERROR(K8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="L59" s="50">
+      <c r="L59" s="51">
         <f>IFERROR(L8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="46" t="inlineStr">
+      <c r="A60" s="47" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -11625,49 +12052,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="49">
-        <f>IFERROR(C9/(IF(COUNT('연간'!E11:H11)&lt;4,"",SUM('연간'!E11:H11)))*365,"")</f>
-        <v/>
-      </c>
-      <c r="D60" s="50">
-        <f>IFERROR(D9/(IF(COUNT('연간'!F11:I11)&lt;4,"",SUM('연간'!F11:I11)))*365,"")</f>
-        <v/>
-      </c>
-      <c r="E60" s="50">
-        <f>IFERROR(E9/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
-        <v/>
-      </c>
-      <c r="F60" s="50">
-        <f>IFERROR(F9/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
-        <v/>
-      </c>
-      <c r="G60" s="50">
-        <f>IFERROR(G9/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
-        <v/>
-      </c>
-      <c r="H60" s="49">
+      <c r="C60" s="50">
+        <f>IFERROR(C9/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
+        <v/>
+      </c>
+      <c r="D60" s="51">
+        <f>IFERROR(D9/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
+        <v/>
+      </c>
+      <c r="E60" s="51">
+        <f>IFERROR(E9/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
+        <v/>
+      </c>
+      <c r="F60" s="51">
+        <f>IFERROR(F9/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
+        <v/>
+      </c>
+      <c r="G60" s="51">
+        <f>IFERROR(G9/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
+        <v/>
+      </c>
+      <c r="H60" s="50">
         <f>IFERROR(H9/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="50">
+      <c r="I60" s="51">
         <f>IFERROR(I9/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="50">
+      <c r="J60" s="51">
         <f>IFERROR(J9/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K60" s="50">
+      <c r="K60" s="51">
         <f>IFERROR(K9/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L60" s="50">
+      <c r="L60" s="51">
         <f>IFERROR(L9/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="46" t="inlineStr">
+      <c r="A61" s="47" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -11677,49 +12104,49 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="49">
-        <f>IFERROR(C19/(IF(COUNT('연간'!E11:H11)&lt;4,"",SUM('연간'!E11:H11)))*365,"")</f>
-        <v/>
-      </c>
-      <c r="D61" s="50">
-        <f>IFERROR(D19/(IF(COUNT('연간'!F11:I11)&lt;4,"",SUM('연간'!F11:I11)))*365,"")</f>
-        <v/>
-      </c>
-      <c r="E61" s="50">
-        <f>IFERROR(E19/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
-        <v/>
-      </c>
-      <c r="F61" s="50">
-        <f>IFERROR(F19/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
-        <v/>
-      </c>
-      <c r="G61" s="50">
-        <f>IFERROR(G19/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
-        <v/>
-      </c>
-      <c r="H61" s="49">
+      <c r="C61" s="50">
+        <f>IFERROR(C19/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
+        <v/>
+      </c>
+      <c r="D61" s="51">
+        <f>IFERROR(D19/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
+        <v/>
+      </c>
+      <c r="E61" s="51">
+        <f>IFERROR(E19/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
+        <v/>
+      </c>
+      <c r="F61" s="51">
+        <f>IFERROR(F19/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
+        <v/>
+      </c>
+      <c r="G61" s="51">
+        <f>IFERROR(G19/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
+        <v/>
+      </c>
+      <c r="H61" s="50">
         <f>IFERROR(H19/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="50">
+      <c r="I61" s="51">
         <f>IFERROR(I19/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="50">
+      <c r="J61" s="51">
         <f>IFERROR(J19/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K61" s="50">
+      <c r="K61" s="51">
         <f>IFERROR(K19/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L61" s="50">
+      <c r="L61" s="51">
         <f>IFERROR(L19/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="46" t="inlineStr">
+      <c r="A62" s="47" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -11729,43 +12156,43 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="50">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="50">
+      <c r="D62" s="51">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="50">
+      <c r="E62" s="51">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="50">
+      <c r="F62" s="51">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="50">
+      <c r="G62" s="51">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="49">
+      <c r="H62" s="50">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="50">
+      <c r="I62" s="51">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="50">
+      <c r="J62" s="51">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
-      <c r="K62" s="50">
+      <c r="K62" s="51">
         <f>IF(OR(K59="",K60="",K61=""),"",IFERROR(K59+K60-K61,""))</f>
         <v/>
       </c>
-      <c r="L62" s="50">
+      <c r="L62" s="51">
         <f>IF(OR(L59="",L60="",L61=""),"",IFERROR(L59+L60-L61,""))</f>
         <v/>
       </c>
@@ -11789,7 +12216,7 @@
       <c r="L63" s="25" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="46" t="inlineStr">
+      <c r="A64" s="47" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -11800,23 +12227,23 @@
         </is>
       </c>
       <c r="C64" s="32">
-        <f>IF(C37="","",IFERROR(C37/(IF(COUNT('연간'!E43:H43)&lt;4,"",SUM('연간'!E43:H43))),""))</f>
+        <f>IF(C37="","",IFERROR(C37/(IF(COUNT('연간'!G43:J43)&lt;4,"",SUM('연간'!G43:J43))),""))</f>
         <v/>
       </c>
       <c r="D64" s="33">
-        <f>IF(D37="","",IFERROR(D37/(IF(COUNT('연간'!F43:I43)&lt;4,"",SUM('연간'!F43:I43))),""))</f>
+        <f>IF(D37="","",IFERROR(D37/(IF(COUNT('연간'!H43:K43)&lt;4,"",SUM('연간'!H43:K43))),""))</f>
         <v/>
       </c>
       <c r="E64" s="33">
-        <f>IF(E37="","",IFERROR(E37/(IF(COUNT('연간'!G43:J43)&lt;4,"",SUM('연간'!G43:J43))),""))</f>
+        <f>IF(E37="","",IFERROR(E37/(IF(COUNT('연간'!I43:L43)&lt;4,"",SUM('연간'!I43:L43))),""))</f>
         <v/>
       </c>
       <c r="F64" s="33">
-        <f>IF(F37="","",IFERROR(F37/(IF(COUNT('연간'!H43:K43)&lt;4,"",SUM('연간'!H43:K43))),""))</f>
+        <f>IF(F37="","",IFERROR(F37/(IF(COUNT('연간'!J43:M43)&lt;4,"",SUM('연간'!J43:M43))),""))</f>
         <v/>
       </c>
       <c r="G64" s="33">
-        <f>IF(G37="","",IFERROR(G37/(IF(COUNT('연간'!I43:L43)&lt;4,"",SUM('연간'!I43:L43))),""))</f>
+        <f>IF(G37="","",IFERROR(G37/(IF(COUNT('연간'!K43:N43)&lt;4,"",SUM('연간'!K43:N43))),""))</f>
         <v/>
       </c>
       <c r="H64" s="32">
@@ -11841,7 +12268,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="46" t="inlineStr">
+      <c r="A65" s="47" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -11852,23 +12279,23 @@
         </is>
       </c>
       <c r="C65" s="37">
-        <f>IF(C39="","",IFERROR(C39/(IF(COUNT('연간'!E4:H4)&lt;4,"",SUM('연간'!E4:H4))),""))</f>
+        <f>IF(C39="","",IFERROR(C39/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4))),""))</f>
         <v/>
       </c>
       <c r="D65" s="38">
-        <f>IF(D39="","",IFERROR(D39/(IF(COUNT('연간'!F4:I4)&lt;4,"",SUM('연간'!F4:I4))),""))</f>
+        <f>IF(D39="","",IFERROR(D39/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4))),""))</f>
         <v/>
       </c>
       <c r="E65" s="38">
-        <f>IF(E39="","",IFERROR(E39/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4))),""))</f>
+        <f>IF(E39="","",IFERROR(E39/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4))),""))</f>
         <v/>
       </c>
       <c r="F65" s="38">
-        <f>IF(F39="","",IFERROR(F39/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4))),""))</f>
+        <f>IF(F39="","",IFERROR(F39/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4))),""))</f>
         <v/>
       </c>
       <c r="G65" s="38">
-        <f>IF(G39="","",IFERROR(G39/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4))),""))</f>
+        <f>IF(G39="","",IFERROR(G39/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4))),""))</f>
         <v/>
       </c>
       <c r="H65" s="37">
@@ -11893,7 +12320,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="46" t="inlineStr">
+      <c r="A66" s="47" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -11904,23 +12331,23 @@
         </is>
       </c>
       <c r="C66" s="37">
-        <f>IF(C38="","",IFERROR(C38/(IF(COUNT('연간'!E4:H4)&lt;4,"",SUM('연간'!E4:H4))),""))</f>
+        <f>IF(C38="","",IFERROR(C38/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4))),""))</f>
         <v/>
       </c>
       <c r="D66" s="38">
-        <f>IF(D38="","",IFERROR(D38/(IF(COUNT('연간'!F4:I4)&lt;4,"",SUM('연간'!F4:I4))),""))</f>
+        <f>IF(D38="","",IFERROR(D38/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4))),""))</f>
         <v/>
       </c>
       <c r="E66" s="38">
-        <f>IF(E38="","",IFERROR(E38/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4))),""))</f>
+        <f>IF(E38="","",IFERROR(E38/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4))),""))</f>
         <v/>
       </c>
       <c r="F66" s="38">
-        <f>IF(F38="","",IFERROR(F38/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4))),""))</f>
+        <f>IF(F38="","",IFERROR(F38/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4))),""))</f>
         <v/>
       </c>
       <c r="G66" s="38">
-        <f>IF(G38="","",IFERROR(G38/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4))),""))</f>
+        <f>IF(G38="","",IFERROR(G38/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4))),""))</f>
         <v/>
       </c>
       <c r="H66" s="37">
@@ -11945,7 +12372,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="46" t="inlineStr">
+      <c r="A67" s="47" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -11956,23 +12383,23 @@
         </is>
       </c>
       <c r="C67" s="37">
-        <f>IF(C40="","",IFERROR(C40/(IF(COUNT('연간'!E44:H44)&lt;4,"",SUM('연간'!E44:H44))),""))</f>
+        <f>IF(C40="","",IFERROR(C40/(IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44))),""))</f>
         <v/>
       </c>
       <c r="D67" s="38">
-        <f>IF(D40="","",IFERROR(D40/(IF(COUNT('연간'!F44:I44)&lt;4,"",SUM('연간'!F44:I44))),""))</f>
+        <f>IF(D40="","",IFERROR(D40/(IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44))),""))</f>
         <v/>
       </c>
       <c r="E67" s="38">
-        <f>IF(E40="","",IFERROR(E40/(IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44))),""))</f>
+        <f>IF(E40="","",IFERROR(E40/(IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44))),""))</f>
         <v/>
       </c>
       <c r="F67" s="38">
-        <f>IF(F40="","",IFERROR(F40/(IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44))),""))</f>
+        <f>IF(F40="","",IFERROR(F40/(IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44))),""))</f>
         <v/>
       </c>
       <c r="G67" s="38">
-        <f>IF(G40="","",IFERROR(G40/(IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44))),""))</f>
+        <f>IF(G40="","",IFERROR(G40/(IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44))),""))</f>
         <v/>
       </c>
       <c r="H67" s="37">
@@ -12031,27 +12458,27 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>2024.4Q</t>
+          <t>2025.2Q</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>2025.1Q</t>
+          <t>2025.3Q</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>2025.2Q</t>
+          <t>2025.4Q</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>2025.3Q</t>
+          <t>2026.1Q</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>2025.4Q</t>
+          <t>2026.2Q</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
@@ -12087,10 +12514,19 @@
         </is>
       </c>
       <c r="C71" s="22" t="n">
-        <v>433129</v>
+        <v>456755</v>
+      </c>
+      <c r="D71" s="22" t="n">
+        <v>449610</v>
+      </c>
+      <c r="E71" s="22" t="n">
+        <v>456578</v>
+      </c>
+      <c r="F71" s="22" t="n">
+        <v>459516</v>
       </c>
       <c r="G71" s="22" t="n">
-        <v>456578</v>
+        <v>481623</v>
       </c>
       <c r="H71" s="22" t="n">
         <v>338841</v>
@@ -12115,10 +12551,19 @@
         </is>
       </c>
       <c r="C72" s="22" t="n">
-        <v>8425</v>
+        <v>14591</v>
+      </c>
+      <c r="D72" s="22" t="n">
+        <v>13540</v>
+      </c>
+      <c r="E72" s="22" t="n">
+        <v>22903</v>
+      </c>
+      <c r="F72" s="22" t="n">
+        <v>22163</v>
       </c>
       <c r="G72" s="22" t="n">
-        <v>22903</v>
+        <v>21854</v>
       </c>
       <c r="H72" s="22" t="n">
         <v>13266</v>
@@ -12143,10 +12588,19 @@
         </is>
       </c>
       <c r="C73" s="22" t="n">
-        <v>17868</v>
+        <v>33292</v>
+      </c>
+      <c r="D73" s="22" t="n">
+        <v>34164</v>
+      </c>
+      <c r="E73" s="22" t="n">
+        <v>54539</v>
+      </c>
+      <c r="F73" s="22" t="n">
+        <v>58495</v>
       </c>
       <c r="G73" s="22" t="n">
-        <v>54539</v>
+        <v>59277</v>
       </c>
       <c r="H73" s="22" t="n">
         <v>21974</v>
@@ -12184,10 +12638,19 @@
         </is>
       </c>
       <c r="C75" s="22" t="n">
-        <v>69835</v>
+        <v>72019</v>
+      </c>
+      <c r="D75" s="22" t="n">
+        <v>82885</v>
+      </c>
+      <c r="E75" s="22" t="n">
+        <v>88304</v>
+      </c>
+      <c r="F75" s="22" t="n">
+        <v>89422</v>
       </c>
       <c r="G75" s="22" t="n">
-        <v>88304</v>
+        <v>84689</v>
       </c>
       <c r="H75" s="22" t="n">
         <v>56287</v>
@@ -12212,10 +12675,19 @@
         </is>
       </c>
       <c r="C76" s="22" t="n">
-        <v>13978</v>
+        <v>14031</v>
+      </c>
+      <c r="D76" s="22" t="n">
+        <v>14024</v>
+      </c>
+      <c r="E76" s="22" t="n">
+        <v>26249</v>
+      </c>
+      <c r="F76" s="22" t="n">
+        <v>26472</v>
       </c>
       <c r="G76" s="22" t="n">
-        <v>26249</v>
+        <v>26693</v>
       </c>
       <c r="H76" s="22" t="n">
         <v>1327</v>
@@ -12240,10 +12712,19 @@
         </is>
       </c>
       <c r="C77" s="22" t="n">
-        <v>59094</v>
+        <v>68127</v>
+      </c>
+      <c r="D77" s="22" t="n">
+        <v>71635</v>
+      </c>
+      <c r="E77" s="22" t="n">
+        <v>79263</v>
+      </c>
+      <c r="F77" s="22" t="n">
+        <v>69592</v>
       </c>
       <c r="G77" s="22" t="n">
-        <v>79263</v>
+        <v>71590</v>
       </c>
       <c r="H77" s="22" t="n">
         <v>40944</v>
@@ -12268,10 +12749,19 @@
         </is>
       </c>
       <c r="C78" s="22" t="n">
-        <v>602330</v>
+        <v>658814</v>
+      </c>
+      <c r="D78" s="22" t="n">
+        <v>665859</v>
+      </c>
+      <c r="E78" s="22" t="n">
+        <v>727837</v>
+      </c>
+      <c r="F78" s="22" t="n">
+        <v>725660</v>
       </c>
       <c r="G78" s="22" t="n">
-        <v>727837</v>
+        <v>745725</v>
       </c>
       <c r="H78" s="22" t="n">
         <v>475033</v>
@@ -12296,10 +12786,19 @@
         </is>
       </c>
       <c r="C79" s="22" t="n">
-        <v>240067</v>
+        <v>235526</v>
+      </c>
+      <c r="D79" s="22" t="n">
+        <v>246326</v>
+      </c>
+      <c r="E79" s="22" t="n">
+        <v>276848</v>
+      </c>
+      <c r="F79" s="22" t="n">
+        <v>288289</v>
       </c>
       <c r="G79" s="22" t="n">
-        <v>276848</v>
+        <v>317580</v>
       </c>
       <c r="H79" s="22" t="n">
         <v>208838</v>
@@ -12324,10 +12823,19 @@
         </is>
       </c>
       <c r="C80" s="22" t="n">
-        <v>334256</v>
+        <v>316747</v>
+      </c>
+      <c r="D80" s="22" t="n">
+        <v>353649</v>
+      </c>
+      <c r="E80" s="22" t="n">
+        <v>442876</v>
+      </c>
+      <c r="F80" s="22" t="n">
+        <v>352747</v>
       </c>
       <c r="G80" s="22" t="n">
-        <v>442876</v>
+        <v>381845</v>
       </c>
       <c r="H80" s="22" t="n">
         <v>355081</v>
@@ -12352,10 +12860,19 @@
         </is>
       </c>
       <c r="C81" s="22" t="n">
-        <v>896</v>
+        <v>210</v>
+      </c>
+      <c r="D81" s="22" t="n">
+        <v>205</v>
+      </c>
+      <c r="E81" s="22" t="n">
+        <v>236</v>
+      </c>
+      <c r="F81" s="22" t="n">
+        <v>194</v>
       </c>
       <c r="G81" s="22" t="n">
-        <v>236</v>
+        <v>57</v>
       </c>
       <c r="H81" s="22" t="n">
         <v>928</v>
@@ -12380,10 +12897,19 @@
         </is>
       </c>
       <c r="C82" s="22" t="n">
-        <v>456143</v>
+        <v>530521</v>
+      </c>
+      <c r="D82" s="22" t="n">
+        <v>426015</v>
+      </c>
+      <c r="E82" s="22" t="n">
+        <v>553094</v>
+      </c>
+      <c r="F82" s="22" t="n">
+        <v>432111</v>
       </c>
       <c r="G82" s="22" t="n">
-        <v>553094</v>
+        <v>572134</v>
       </c>
       <c r="H82" s="22" t="n">
         <v>204217</v>
@@ -12408,10 +12934,19 @@
         </is>
       </c>
       <c r="C83" s="22" t="n">
-        <v>540202</v>
+        <v>497088</v>
+      </c>
+      <c r="D83" s="22" t="n">
+        <v>456432</v>
+      </c>
+      <c r="E83" s="22" t="n">
+        <v>426602</v>
+      </c>
+      <c r="F83" s="22" t="n">
+        <v>417984</v>
       </c>
       <c r="G83" s="22" t="n">
-        <v>426602</v>
+        <v>390439</v>
       </c>
       <c r="H83" s="22" t="n">
         <v>267753</v>
@@ -12436,10 +12971,19 @@
         </is>
       </c>
       <c r="C84" s="22" t="n">
-        <v>34479</v>
+        <v>39441</v>
+      </c>
+      <c r="D84" s="22" t="n">
+        <v>35103</v>
+      </c>
+      <c r="E84" s="22" t="n">
+        <v>41104</v>
+      </c>
+      <c r="F84" s="22" t="n">
+        <v>48117</v>
       </c>
       <c r="G84" s="22" t="n">
-        <v>41104</v>
+        <v>42134</v>
       </c>
       <c r="H84" s="22" t="n">
         <v>26844</v>
@@ -12464,10 +13008,19 @@
         </is>
       </c>
       <c r="C85" s="12" t="n">
-        <v>1606043</v>
+        <v>1619532</v>
+      </c>
+      <c r="D85" s="12" t="n">
+        <v>1517730</v>
+      </c>
+      <c r="E85" s="12" t="n">
+        <v>1740758</v>
+      </c>
+      <c r="F85" s="12" t="n">
+        <v>1539441</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>1740758</v>
+        <v>1704189</v>
       </c>
       <c r="H85" s="12" t="n">
         <v>1063661</v>
@@ -12492,10 +13045,19 @@
         </is>
       </c>
       <c r="C86" s="22" t="n">
-        <v>2208373</v>
+        <v>2278347</v>
+      </c>
+      <c r="D86" s="22" t="n">
+        <v>2183588</v>
+      </c>
+      <c r="E86" s="22" t="n">
+        <v>2468595</v>
+      </c>
+      <c r="F86" s="22" t="n">
+        <v>2265101</v>
       </c>
       <c r="G86" s="22" t="n">
-        <v>2468595</v>
+        <v>2449914</v>
       </c>
       <c r="H86" s="22" t="n">
         <v>1538694</v>
@@ -12520,10 +13082,19 @@
         </is>
       </c>
       <c r="C87" s="22" t="n">
-        <v>5076</v>
+        <v>5217</v>
+      </c>
+      <c r="D87" s="22" t="n">
+        <v>4551</v>
+      </c>
+      <c r="E87" s="22" t="n">
+        <v>4015</v>
+      </c>
+      <c r="F87" s="22" t="n">
+        <v>3434</v>
       </c>
       <c r="G87" s="22" t="n">
-        <v>4015</v>
+        <v>4104</v>
       </c>
       <c r="H87" s="22" t="n">
         <v>7614</v>
@@ -12548,10 +13119,19 @@
         </is>
       </c>
       <c r="C88" s="22" t="n">
-        <v>3935</v>
+        <v>4220</v>
+      </c>
+      <c r="D88" s="22" t="n">
+        <v>4378</v>
+      </c>
+      <c r="E88" s="22" t="n">
+        <v>4245</v>
+      </c>
+      <c r="F88" s="22" t="n">
+        <v>4724</v>
       </c>
       <c r="G88" s="22" t="n">
-        <v>4245</v>
+        <v>4898</v>
       </c>
       <c r="H88" s="22" t="n">
         <v>2945</v>
@@ -12576,10 +13156,19 @@
         </is>
       </c>
       <c r="C89" s="22" t="n">
-        <v>2188</v>
+        <v>2303</v>
+      </c>
+      <c r="D89" s="22" t="n">
+        <v>5026</v>
+      </c>
+      <c r="E89" s="22" t="n">
+        <v>4610</v>
+      </c>
+      <c r="F89" s="22" t="n">
+        <v>4020</v>
       </c>
       <c r="G89" s="22" t="n">
-        <v>4610</v>
+        <v>3368</v>
       </c>
       <c r="H89" s="22" t="n">
         <v>2101</v>
@@ -12604,10 +13193,19 @@
         </is>
       </c>
       <c r="C90" s="22" t="n">
-        <v>5319</v>
+        <v>13203</v>
+      </c>
+      <c r="D90" s="22" t="n">
+        <v>12103</v>
+      </c>
+      <c r="E90" s="22" t="n">
+        <v>18914</v>
+      </c>
+      <c r="F90" s="22" t="n">
+        <v>17506</v>
       </c>
       <c r="G90" s="22" t="n">
-        <v>18914</v>
+        <v>17693</v>
       </c>
       <c r="H90" s="22" t="n">
         <v>10595</v>
@@ -12632,10 +13230,19 @@
         </is>
       </c>
       <c r="C91" s="22" t="n">
-        <v>16516</v>
+        <v>24943</v>
+      </c>
+      <c r="D91" s="22" t="n">
+        <v>26058</v>
+      </c>
+      <c r="E91" s="22" t="n">
+        <v>31785</v>
+      </c>
+      <c r="F91" s="22" t="n">
+        <v>29684</v>
       </c>
       <c r="G91" s="22" t="n">
-        <v>31785</v>
+        <v>30063</v>
       </c>
       <c r="H91" s="22" t="n">
         <v>23255</v>
@@ -12660,10 +13267,19 @@
         </is>
       </c>
       <c r="C92" s="22" t="n">
-        <v>108732</v>
+        <v>71797</v>
+      </c>
+      <c r="D92" s="22" t="n">
+        <v>43365</v>
+      </c>
+      <c r="E92" s="22" t="n">
+        <v>91004</v>
+      </c>
+      <c r="F92" s="22" t="n">
+        <v>51675</v>
       </c>
       <c r="G92" s="22" t="n">
-        <v>91004</v>
+        <v>101149</v>
       </c>
       <c r="H92" s="22" t="n">
         <v>86312</v>
@@ -12688,10 +13304,19 @@
         </is>
       </c>
       <c r="C93" s="22" t="n">
-        <v>2974</v>
+        <v>1033</v>
+      </c>
+      <c r="D93" s="22" t="n">
+        <v>3695</v>
+      </c>
+      <c r="E93" s="22" t="n">
+        <v>3356</v>
+      </c>
+      <c r="F93" s="22" t="n">
+        <v>3371</v>
       </c>
       <c r="G93" s="22" t="n">
-        <v>3356</v>
+        <v>2659</v>
       </c>
       <c r="H93" s="22" t="n">
         <v>2695</v>
@@ -12716,10 +13341,19 @@
         </is>
       </c>
       <c r="C94" s="22" t="n">
-        <v>65353</v>
+        <v>78417</v>
+      </c>
+      <c r="D94" s="22" t="n">
+        <v>78897</v>
+      </c>
+      <c r="E94" s="22" t="n">
+        <v>127247</v>
+      </c>
+      <c r="F94" s="22" t="n">
+        <v>107524</v>
       </c>
       <c r="G94" s="22" t="n">
-        <v>127247</v>
+        <v>160700</v>
       </c>
       <c r="H94" s="22" t="n">
         <v>152266</v>
@@ -12744,10 +13378,19 @@
         </is>
       </c>
       <c r="C95" s="22" t="n">
-        <v>113298</v>
+        <v>117029</v>
+      </c>
+      <c r="D95" s="22" t="n">
+        <v>141466</v>
+      </c>
+      <c r="E95" s="22" t="n">
+        <v>189469</v>
+      </c>
+      <c r="F95" s="22" t="n">
+        <v>165132</v>
       </c>
       <c r="G95" s="22" t="n">
-        <v>189469</v>
+        <v>127681</v>
       </c>
       <c r="H95" s="22" t="n">
         <v>86149</v>
@@ -12772,10 +13415,19 @@
         </is>
       </c>
       <c r="C96" s="22" t="n">
-        <v>290357</v>
+        <v>268276</v>
+      </c>
+      <c r="D96" s="22" t="n">
+        <v>267423</v>
+      </c>
+      <c r="E96" s="22" t="n">
+        <v>411077</v>
+      </c>
+      <c r="F96" s="22" t="n">
+        <v>327702</v>
       </c>
       <c r="G96" s="22" t="n">
-        <v>411077</v>
+        <v>392189</v>
       </c>
       <c r="H96" s="22" t="n">
         <v>327422</v>
@@ -12800,10 +13452,19 @@
         </is>
       </c>
       <c r="C97" s="22" t="n">
-        <v>306873</v>
+        <v>293219</v>
+      </c>
+      <c r="D97" s="22" t="n">
+        <v>293481</v>
+      </c>
+      <c r="E97" s="22" t="n">
+        <v>442862</v>
+      </c>
+      <c r="F97" s="22" t="n">
+        <v>357386</v>
       </c>
       <c r="G97" s="22" t="n">
-        <v>442862</v>
+        <v>422251</v>
       </c>
       <c r="H97" s="22" t="n">
         <v>350677</v>
@@ -12828,10 +13489,19 @@
         </is>
       </c>
       <c r="C98" s="22" t="n">
-        <v>1901499</v>
+        <v>1985127</v>
+      </c>
+      <c r="D98" s="22" t="n">
+        <v>1890107</v>
+      </c>
+      <c r="E98" s="22" t="n">
+        <v>2025732</v>
+      </c>
+      <c r="F98" s="22" t="n">
+        <v>1907715</v>
       </c>
       <c r="G98" s="22" t="n">
-        <v>2025732</v>
+        <v>2027663</v>
       </c>
       <c r="H98" s="22" t="n">
         <v>1188017</v>
@@ -12856,10 +13526,19 @@
         </is>
       </c>
       <c r="C99" s="22" t="n">
-        <v>1901499</v>
+        <v>1985127</v>
+      </c>
+      <c r="D99" s="22" t="n">
+        <v>1890107</v>
+      </c>
+      <c r="E99" s="22" t="n">
+        <v>2025732</v>
+      </c>
+      <c r="F99" s="22" t="n">
+        <v>1907715</v>
       </c>
       <c r="G99" s="22" t="n">
-        <v>2025732</v>
+        <v>2027663</v>
       </c>
       <c r="H99" s="22" t="n">
         <v>1188017</v>
@@ -12884,10 +13563,19 @@
         </is>
       </c>
       <c r="C100" s="22" t="n">
-        <v>1901499</v>
+        <v>1985127</v>
+      </c>
+      <c r="D100" s="22" t="n">
+        <v>1890107</v>
+      </c>
+      <c r="E100" s="22" t="n">
+        <v>2025732</v>
+      </c>
+      <c r="F100" s="22" t="n">
+        <v>1907715</v>
       </c>
       <c r="G100" s="22" t="n">
-        <v>2025732</v>
+        <v>2027663</v>
       </c>
       <c r="H100" s="22" t="n">
         <v>1188017</v>
@@ -12912,10 +13600,19 @@
         </is>
       </c>
       <c r="C101" s="22" t="n">
-        <v>2208373</v>
+        <v>2278347</v>
+      </c>
+      <c r="D101" s="22" t="n">
+        <v>2183588</v>
+      </c>
+      <c r="E101" s="22" t="n">
+        <v>2468595</v>
+      </c>
+      <c r="F101" s="22" t="n">
+        <v>2265101</v>
       </c>
       <c r="G101" s="22" t="n">
-        <v>2468595</v>
+        <v>2449914</v>
       </c>
       <c r="H101" s="22" t="n">
         <v>1538694</v>
@@ -13029,24 +13726,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="52" t="inlineStr">
+      <c r="A3" s="53" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="52" t="inlineStr">
+      <c r="B3" s="53" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="52" t="inlineStr">
+      <c r="C3" s="53" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
